--- a/localization/translations.xlsx
+++ b/localization/translations.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Переводы" sheetId="1" r:id="Re490b7bd213a4afe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Переводы" sheetId="1" r:id="R03036dd6d17d462c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -40,7 +40,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -50,6 +50,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF416B2B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F7EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2B8"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -190,7 +200,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="95">
+  <x:cellXfs count="110">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -472,6 +482,51 @@
     <x:xf numFmtId="0" fontId="4" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -480,8 +535,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:H2818" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H2818"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:H2829" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H2829"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Раздел"/>
     <x:tableColumn id="2" name="ID (не менять)"/>
@@ -67503,10 +67558,230 @@
       <x:c r="G2818" s="93" t="str"/>
       <x:c r="H2818" s="94" t="str"/>
     </x:row>
+    <x:row r="2819" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2819" s="101" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2819" s="101" t="str">
+        <x:v>shell.skipCalculator</x:v>
+      </x:c>
+      <x:c r="C2819" s="101" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2819" s="102" t="str"/>
+      <x:c r="E2819" s="102" t="str">
+        <x:v>Skip to calculator</x:v>
+      </x:c>
+      <x:c r="F2819" s="102" t="str"/>
+      <x:c r="G2819" s="102" t="str"/>
+      <x:c r="H2819" s="103" t="str">
+        <x:v>Перейти к калькулятору</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2820" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2820" s="104" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2820" s="104" t="str">
+        <x:v>updates.title</x:v>
+      </x:c>
+      <x:c r="C2820" s="104" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2820" s="105" t="str"/>
+      <x:c r="E2820" s="105" t="str">
+        <x:v>What's new</x:v>
+      </x:c>
+      <x:c r="F2820" s="105" t="str"/>
+      <x:c r="G2820" s="105" t="str"/>
+      <x:c r="H2820" s="106" t="str">
+        <x:v>Что нового</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2821" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2821" s="104" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2821" s="104" t="str">
+        <x:v>updates.close</x:v>
+      </x:c>
+      <x:c r="C2821" s="104" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2821" s="105" t="str"/>
+      <x:c r="E2821" s="105" t="str">
+        <x:v>Close updates</x:v>
+      </x:c>
+      <x:c r="F2821" s="105" t="str"/>
+      <x:c r="G2821" s="105" t="str"/>
+      <x:c r="H2821" s="106" t="str">
+        <x:v>Закрыть обновления</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2822" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2822" s="104" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2822" s="104" t="str">
+        <x:v>updates.version</x:v>
+      </x:c>
+      <x:c r="C2822" s="104" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2822" s="105" t="str"/>
+      <x:c r="E2822" s="105" t="str">
+        <x:v>Legacy engine: {legacyEngine} · Remaked UI: {ui}</x:v>
+      </x:c>
+      <x:c r="F2822" s="105" t="str"/>
+      <x:c r="G2822" s="105" t="str"/>
+      <x:c r="H2822" s="106" t="str">
+        <x:v>Legacy engine: {legacyEngine} · Remaked UI: {ui}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2823" ht="36" hidden="0" customHeight="1">
+      <x:c r="A2823" s="104" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2823" s="104" t="str">
+        <x:v>updates.keyboard</x:v>
+      </x:c>
+      <x:c r="C2823" s="104" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2823" s="105" t="str"/>
+      <x:c r="E2823" s="105" t="str">
+        <x:v>Keyboard navigation: skip straight to the calculator, keep focus inside open dialogs, and return to the opener with Escape.</x:v>
+      </x:c>
+      <x:c r="F2823" s="105" t="str"/>
+      <x:c r="G2823" s="105" t="str"/>
+      <x:c r="H2823" s="106" t="str">
+        <x:v>Управление клавиатурой: переходите сразу к калькулятору, оставайтесь внутри открытого окна и возвращайтесь к кнопке открытия через Escape.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2824" ht="48" hidden="0" customHeight="1">
+      <x:c r="A2824" s="104" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2824" s="104" t="str">
+        <x:v>updates.translations</x:v>
+      </x:c>
+      <x:c r="C2824" s="104" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2824" s="105" t="str"/>
+      <x:c r="E2824" s="105" t="str">
+        <x:v>Translate the Modern interface, game names, labels and skill descriptions in one Excel workbook. Upload it to GitHub to publish an update.</x:v>
+      </x:c>
+      <x:c r="F2824" s="105" t="str"/>
+      <x:c r="G2824" s="105" t="str"/>
+      <x:c r="H2824" s="106" t="str">
+        <x:v>Переводите современный интерфейс, игровые названия, подписи и описания навыков в одной Excel-таблице. Загрузите её на GitHub, чтобы опубликовать обновление.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2825" ht="36" hidden="0" customHeight="1">
+      <x:c r="A2825" s="104" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2825" s="104" t="str">
+        <x:v>updates.builds</x:v>
+      </x:c>
+      <x:c r="C2825" s="104" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2825" s="105" t="str"/>
+      <x:c r="E2825" s="105" t="str">
+        <x:v>Search compatible equipment and Souls, save named builds locally, and compare their calculated stats without changing your current character.</x:v>
+      </x:c>
+      <x:c r="F2825" s="105" t="str"/>
+      <x:c r="G2825" s="105" t="str"/>
+      <x:c r="H2825" s="106" t="str">
+        <x:v>Ищите подходящую экипировку и Souls, сохраняйте билды в браузере и сравнивайте рассчитанные характеристики без изменения текущего персонажа.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2826" ht="36" hidden="0" customHeight="1">
+      <x:c r="A2826" s="104" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2826" s="104" t="str">
+        <x:v>updates.offline</x:v>
+      </x:c>
+      <x:c r="C2826" s="104" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2826" s="105" t="str"/>
+      <x:c r="E2826" s="105" t="str">
+        <x:v>Install the site or use Modern and Legacy modes offline after the first successful load. Save your work before accepting an update.</x:v>
+      </x:c>
+      <x:c r="F2826" s="105" t="str"/>
+      <x:c r="G2826" s="105" t="str"/>
+      <x:c r="H2826" s="106" t="str">
+        <x:v>Установите сайт или используйте Modern и Legacy офлайн после первой успешной загрузки. Сохраните работу перед обновлением.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2827" ht="36" hidden="0" customHeight="1">
+      <x:c r="A2827" s="104" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2827" s="104" t="str">
+        <x:v>updates.preservation</x:v>
+      </x:c>
+      <x:c r="C2827" s="104" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2827" s="105" t="str"/>
+      <x:c r="E2827" s="105" t="str">
+        <x:v>The Legacy 2.00 engine remains the calculation source. This is an unofficial community project. Build storage is local to this browser.</x:v>
+      </x:c>
+      <x:c r="F2827" s="105" t="str"/>
+      <x:c r="G2827" s="105" t="str"/>
+      <x:c r="H2827" s="106" t="str">
+        <x:v>Источником расчётов остаётся движок Legacy 2.00. Это неофициальный проект сообщества. Билды хранятся только в этом браузере.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2828" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2828" s="104" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2828" s="104" t="str">
+        <x:v>updates.fullChangelog</x:v>
+      </x:c>
+      <x:c r="C2828" s="104" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2828" s="105" t="str"/>
+      <x:c r="E2828" s="105" t="str">
+        <x:v>Full changelog</x:v>
+      </x:c>
+      <x:c r="F2828" s="105" t="str"/>
+      <x:c r="G2828" s="105" t="str"/>
+      <x:c r="H2828" s="106" t="str">
+        <x:v>Полный список изменений</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2829" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2829" s="107" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2829" s="107" t="str">
+        <x:v>updates.report</x:v>
+      </x:c>
+      <x:c r="C2829" s="107" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2829" s="108" t="str"/>
+      <x:c r="E2829" s="108" t="str">
+        <x:v>Report a problem</x:v>
+      </x:c>
+      <x:c r="F2829" s="108" t="str"/>
+      <x:c r="G2829" s="108" t="str"/>
+      <x:c r="H2829" s="109" t="str">
+        <x:v>Сообщить о проблеме</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d2948c84ff34ebe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf227ad6dce8741f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/localization/translations.xlsx
+++ b/localization/translations.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Переводы" sheetId="1" r:id="R03036dd6d17d462c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Переводы" sheetId="1" r:id="R2dca05788e9d4091"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -40,7 +40,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="17">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -50,6 +50,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF416B2B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F7EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2B8"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -200,7 +210,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="110">
+  <x:cellXfs count="125">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -527,6 +537,51 @@
     <x:xf numFmtId="0" fontId="4" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -535,8 +590,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:H2829" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H2829"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:H2838" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H2838"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Раздел"/>
     <x:tableColumn id="2" name="ID (не менять)"/>
@@ -67778,10 +67833,190 @@
         <x:v>Сообщить о проблеме</x:v>
       </x:c>
     </x:row>
+    <x:row r="2830" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2830" s="116" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2830" s="116" t="str">
+        <x:v>builds.share</x:v>
+      </x:c>
+      <x:c r="C2830" s="116" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2830" s="117" t="str"/>
+      <x:c r="E2830" s="117" t="str">
+        <x:v>Share build</x:v>
+      </x:c>
+      <x:c r="F2830" s="117" t="str"/>
+      <x:c r="G2830" s="117" t="str"/>
+      <x:c r="H2830" s="118" t="str">
+        <x:v>Поделиться билдом</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2831" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2831" s="119" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2831" s="119" t="str">
+        <x:v>builds.shareLink</x:v>
+      </x:c>
+      <x:c r="C2831" s="119" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2831" s="120" t="str"/>
+      <x:c r="E2831" s="120" t="str">
+        <x:v>Build sharing link</x:v>
+      </x:c>
+      <x:c r="F2831" s="120" t="str"/>
+      <x:c r="G2831" s="120" t="str"/>
+      <x:c r="H2831" s="121" t="str">
+        <x:v>Ссылка на билд</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2832" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2832" s="119" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2832" s="119" t="str">
+        <x:v>builds.shareCopied</x:v>
+      </x:c>
+      <x:c r="C2832" s="119" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2832" s="120" t="str"/>
+      <x:c r="E2832" s="120" t="str">
+        <x:v>Build link copied.</x:v>
+      </x:c>
+      <x:c r="F2832" s="120" t="str"/>
+      <x:c r="G2832" s="120" t="str"/>
+      <x:c r="H2832" s="121" t="str">
+        <x:v>Ссылка на билд скопирована.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2833" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2833" s="119" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2833" s="119" t="str">
+        <x:v>builds.shareManual</x:v>
+      </x:c>
+      <x:c r="C2833" s="119" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2833" s="120" t="str"/>
+      <x:c r="E2833" s="120" t="str">
+        <x:v>Copy the link below to share your build.</x:v>
+      </x:c>
+      <x:c r="F2833" s="120" t="str"/>
+      <x:c r="G2833" s="120" t="str"/>
+      <x:c r="H2833" s="121" t="str">
+        <x:v>Скопируйте ссылку ниже, чтобы поделиться билдом.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2834" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2834" s="119" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2834" s="119" t="str">
+        <x:v>builds.sharedLoaded</x:v>
+      </x:c>
+      <x:c r="C2834" s="119" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2834" s="120" t="str"/>
+      <x:c r="E2834" s="120" t="str">
+        <x:v>Shared build loaded</x:v>
+      </x:c>
+      <x:c r="F2834" s="120" t="str"/>
+      <x:c r="G2834" s="120" t="str"/>
+      <x:c r="H2834" s="121" t="str">
+        <x:v>Билд из ссылки загружен</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2835" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2835" s="119" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2835" s="119" t="str">
+        <x:v>builds.invalidShare</x:v>
+      </x:c>
+      <x:c r="C2835" s="119" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2835" s="120" t="str"/>
+      <x:c r="E2835" s="120" t="str">
+        <x:v>Invalid share link; current build kept</x:v>
+      </x:c>
+      <x:c r="F2835" s="120" t="str"/>
+      <x:c r="G2835" s="120" t="str"/>
+      <x:c r="H2835" s="121" t="str">
+        <x:v>Некорректная ссылка; текущий билд сохранён</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2836" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2836" s="119" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2836" s="119" t="str">
+        <x:v>search.details</x:v>
+      </x:c>
+      <x:c r="C2836" s="119" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2836" s="120" t="str"/>
+      <x:c r="E2836" s="120" t="str">
+        <x:v>Details</x:v>
+      </x:c>
+      <x:c r="F2836" s="120" t="str"/>
+      <x:c r="G2836" s="120" t="str"/>
+      <x:c r="H2836" s="121" t="str">
+        <x:v>Характеристики</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2837" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2837" s="119" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2837" s="119" t="str">
+        <x:v>search.sockets</x:v>
+      </x:c>
+      <x:c r="C2837" s="119" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2837" s="120" t="str"/>
+      <x:c r="E2837" s="120" t="str">
+        <x:v>Soul sockets: {count}</x:v>
+      </x:c>
+      <x:c r="F2837" s="120" t="str"/>
+      <x:c r="G2837" s="120" t="str"/>
+      <x:c r="H2837" s="121" t="str">
+        <x:v>Ячеек Soul: {count}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2838" ht="24" hidden="0" customHeight="1">
+      <x:c r="A2838" s="122" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2838" s="122" t="str">
+        <x:v>search.itemSource</x:v>
+      </x:c>
+      <x:c r="C2838" s="122" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2838" s="123" t="str"/>
+      <x:c r="E2838" s="123" t="str">
+        <x:v>Item descriptions from Legacy 2.00; not calculated build deltas.</x:v>
+      </x:c>
+      <x:c r="F2838" s="123" t="str"/>
+      <x:c r="G2838" s="123" t="str"/>
+      <x:c r="H2838" s="124" t="str">
+        <x:v>Описание предмета из Legacy 2.00; это не расчёт изменений характеристик билда.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf227ad6dce8741f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2307a5e74eb4215"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/localization/translations.xlsx
+++ b/localization/translations.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Переводы" sheetId="1" r:id="R2dca05788e9d4091"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Переводы" sheetId="1" r:id="R04e8a8caf1d84324"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -40,7 +40,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="19">
+  <x:fills count="21">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -50,6 +50,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF416B2B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F7EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2B8"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -210,7 +220,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="125">
+  <x:cellXfs count="140">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -582,6 +592,51 @@
     <x:xf numFmtId="0" fontId="4" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -590,8 +645,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:H2838" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H2838"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:H2843" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H2843"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Раздел"/>
     <x:tableColumn id="2" name="ID (не менять)"/>
@@ -68013,10 +68068,104 @@
         <x:v>Описание предмета из Legacy 2.00; это не расчёт изменений характеристик билда.</x:v>
       </x:c>
     </x:row>
+    <x:row r="2839" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2839" s="131" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2839" s="131" t="str">
+        <x:v>skills.adeptness</x:v>
+      </x:c>
+      <x:c r="C2839" s="131" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2839" s="132" t="str"/>
+      <x:c r="E2839" s="132" t="str">
+        <x:v>Adeptness</x:v>
+      </x:c>
+      <x:c r="F2839" s="132" t="str"/>
+      <x:c r="G2839" s="132" t="str"/>
+      <x:c r="H2839" s="133" t="str"/>
+    </x:row>
+    <x:row r="2840" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2840" s="134" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2840" s="134" t="str">
+        <x:v>skills.potential</x:v>
+      </x:c>
+      <x:c r="C2840" s="134" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2840" s="135" t="str"/>
+      <x:c r="E2840" s="135" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="F2840" s="135" t="str"/>
+      <x:c r="G2840" s="135" t="str"/>
+      <x:c r="H2840" s="136" t="str"/>
+    </x:row>
+    <x:row r="2841" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2841" s="134" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2841" s="134" t="str">
+        <x:v>skills.largerSteps</x:v>
+      </x:c>
+      <x:c r="C2841" s="134" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2841" s="135" t="str"/>
+      <x:c r="E2841" s="135" t="str">
+        <x:v>Larger steps</x:v>
+      </x:c>
+      <x:c r="F2841" s="135" t="str"/>
+      <x:c r="G2841" s="135" t="str"/>
+      <x:c r="H2841" s="136" t="str">
+        <x:v>Крупные шаги</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2842" ht="36" hidden="0" customHeight="1">
+      <x:c r="A2842" s="134" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2842" s="134" t="str">
+        <x:v>skills.help</x:v>
+      </x:c>
+      <x:c r="C2842" s="134" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2842" s="135" t="str"/>
+      <x:c r="E2842" s="135" t="str">
+        <x:v>Adeptness uses Skill points. Potential uses its own point pool beside Level. Limits and costs follow the Legacy engine.</x:v>
+      </x:c>
+      <x:c r="F2842" s="135" t="str"/>
+      <x:c r="G2842" s="135" t="str"/>
+      <x:c r="H2842" s="136" t="str">
+        <x:v>Adeptness использует очки Skill. Potential использует свой запас очков рядом с уровнем. Ограничения и стоимость определяет движок Legacy.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2843" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2843" s="137" t="str">
+        <x:v>Интерфейс</x:v>
+      </x:c>
+      <x:c r="B2843" s="137" t="str">
+        <x:v>skills.indicator</x:v>
+      </x:c>
+      <x:c r="C2843" s="137" t="str">
+        <x:v>Интерфейс сайта</x:v>
+      </x:c>
+      <x:c r="D2843" s="138" t="str"/>
+      <x:c r="E2843" s="138" t="str">
+        <x:v>Legacy next-point indicator: </x:v>
+      </x:c>
+      <x:c r="F2843" s="138" t="str"/>
+      <x:c r="G2843" s="138" t="str"/>
+      <x:c r="H2843" s="139" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2307a5e74eb4215"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92c0af64477a4a78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/localization/translations.xlsx
+++ b/localization/translations.xlsx
@@ -320,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -875,6 +875,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -883,8 +889,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2876" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I2876"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2883" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I2883"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Раздел"/>
     <tableColumn id="2" name="ID (не менять)"/>
@@ -71940,6 +71946,153 @@
       </c>
       <c r="I2876" t="str" s="143"/>
     </row>
+    <row r="2877" ht="52" customHeight="1">
+      <c r="A2877" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2877" t="str" s="23">
+        <v>calculator.inputInvalid</v>
+      </c>
+      <c r="C2877" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2877" t="str" s="24"/>
+      <c r="E2877" s="186" t="str">
+        <v>Enter a whole number within this field’s limits. Esc cancels your edit.</v>
+      </c>
+      <c r="F2877" s="24" t="str"/>
+      <c r="G2877" s="24" t="str"/>
+      <c r="H2877" s="187" t="str">
+        <v>Введите целое число в пределах поля. Esc отменяет ввод.</v>
+      </c>
+      <c r="I2877" s="143" t="str"/>
+    </row>
+    <row r="2878" ht="52" customHeight="1">
+      <c r="A2878" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2878" t="str" s="23">
+        <v>calculator.inputBudget</v>
+      </c>
+      <c r="C2878" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2878" t="str" s="24"/>
+      <c r="E2878" s="186" t="str">
+        <v>Not enough attribute points. The field shows the value the engine could allocate.</v>
+      </c>
+      <c r="F2878" s="24" t="str"/>
+      <c r="G2878" s="24" t="str"/>
+      <c r="H2878" s="187" t="str">
+        <v>Не хватает очков характеристик. В поле показано значение, на которое хватило очков.</v>
+      </c>
+      <c r="I2878" s="143" t="str"/>
+    </row>
+    <row r="2879" ht="52" customHeight="1">
+      <c r="A2879" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2879" t="str" s="23">
+        <v>calculator.levelInputHelp</v>
+      </c>
+      <c r="C2879" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2879" t="str" s="24"/>
+      <c r="E2879" s="186" t="str">
+        <v>Level 1–55. Press Enter or leave the field to apply; Esc cancels.</v>
+      </c>
+      <c r="F2879" s="24" t="str"/>
+      <c r="G2879" s="24" t="str"/>
+      <c r="H2879" s="187" t="str">
+        <v>Уровень 1–55. Enter или выход из поля применяет значение; Esc отменяет.</v>
+      </c>
+      <c r="I2879" s="143" t="str"/>
+    </row>
+    <row r="2880" ht="82" customHeight="1">
+      <c r="A2880" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2880" t="str" s="23">
+        <v>calculator.attributeInputHelp</v>
+      </c>
+      <c r="C2880" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2880" t="str" s="24"/>
+      <c r="E2880" s="186" t="str">
+        <v>Base attribute before equipment bonuses. Race minimum, maximum 99 and available points apply. Enter applies; Esc cancels.</v>
+      </c>
+      <c r="F2880" s="24" t="str"/>
+      <c r="G2880" s="24" t="str"/>
+      <c r="H2880" s="187" t="str">
+        <v>Базовая характеристика без бонусов экипировки. Минимум зависит от расы, максимум 99; нужны свободные очки. Enter применяет, Esc отменяет.</v>
+      </c>
+      <c r="I2880" s="143" t="str"/>
+    </row>
+    <row r="2881" ht="52" customHeight="1">
+      <c r="A2881" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2881" t="str" s="23">
+        <v>calculator.totalWithBonuses</v>
+      </c>
+      <c r="C2881" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2881" t="str" s="24"/>
+      <c r="E2881" s="186" t="str">
+        <v>Total including equipment and other bonuses</v>
+      </c>
+      <c r="F2881" s="24" t="str"/>
+      <c r="G2881" s="24" t="str"/>
+      <c r="H2881" s="187" t="str">
+        <v>Итог с бонусами экипировки и другими эффектами</v>
+      </c>
+      <c r="I2881" s="143" t="str"/>
+    </row>
+    <row r="2882" ht="52" customHeight="1">
+      <c r="A2882" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2882" t="str" s="23">
+        <v>compare.hideIdentical</v>
+      </c>
+      <c r="C2882" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2882" t="str" s="24"/>
+      <c r="E2882" s="186" t="str">
+        <v>Hide identical stats</v>
+      </c>
+      <c r="F2882" s="24" t="str"/>
+      <c r="G2882" s="24" t="str"/>
+      <c r="H2882" s="187" t="str">
+        <v>Скрыть одинаковые характеристики</v>
+      </c>
+      <c r="I2882" s="143" t="str"/>
+    </row>
+    <row r="2883" ht="52" customHeight="1">
+      <c r="A2883" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2883" t="str" s="23">
+        <v>compare.allIdentical</v>
+      </c>
+      <c r="C2883" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2883" t="str" s="24"/>
+      <c r="E2883" s="186" t="str">
+        <v>All displayed stats are identical.</v>
+      </c>
+      <c r="F2883" s="24" t="str"/>
+      <c r="G2883" s="24" t="str"/>
+      <c r="H2883" s="187" t="str">
+        <v>Все показанные характеристики одинаковы.</v>
+      </c>
+      <c r="I2883" s="143" t="str"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/localization/translations.xlsx
+++ b/localization/translations.xlsx
@@ -320,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -881,6 +881,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -889,8 +895,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2883" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I2883"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2888" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I2888"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Раздел"/>
     <tableColumn id="2" name="ID (не менять)"/>
@@ -72093,6 +72099,111 @@
       </c>
       <c r="I2883" s="143" t="str"/>
     </row>
+    <row r="2884" ht="52" customHeight="1">
+      <c r="A2884" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2884" t="str" s="23">
+        <v>workbench.character</v>
+      </c>
+      <c r="C2884" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2884" t="str" s="24"/>
+      <c r="E2884" s="188" t="str">
+        <v>Character</v>
+      </c>
+      <c r="F2884" s="24" t="str"/>
+      <c r="G2884" s="24" t="str"/>
+      <c r="H2884" s="189" t="str">
+        <v>Персонаж</v>
+      </c>
+      <c r="I2884" s="143" t="str"/>
+    </row>
+    <row r="2885" ht="52" customHeight="1">
+      <c r="A2885" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2885" t="str" s="23">
+        <v>workbench.skills</v>
+      </c>
+      <c r="C2885" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2885" t="str" s="24"/>
+      <c r="E2885" s="188" t="str">
+        <v>Skills</v>
+      </c>
+      <c r="F2885" s="24" t="str"/>
+      <c r="G2885" s="24" t="str"/>
+      <c r="H2885" s="189" t="str">
+        <v>Умения</v>
+      </c>
+      <c r="I2885" s="143" t="str"/>
+    </row>
+    <row r="2886" ht="52" customHeight="1">
+      <c r="A2886" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2886" t="str" s="23">
+        <v>workbench.effects</v>
+      </c>
+      <c r="C2886" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2886" t="str" s="24"/>
+      <c r="E2886" s="188" t="str">
+        <v>Effects</v>
+      </c>
+      <c r="F2886" s="24" t="str"/>
+      <c r="G2886" s="24" t="str"/>
+      <c r="H2886" s="189" t="str">
+        <v>Эффекты</v>
+      </c>
+      <c r="I2886" s="143" t="str"/>
+    </row>
+    <row r="2887" ht="52" customHeight="1">
+      <c r="A2887" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2887" t="str" s="23">
+        <v>workbench.baseStats</v>
+      </c>
+      <c r="C2887" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2887" t="str" s="24"/>
+      <c r="E2887" s="188" t="str">
+        <v>Base stats</v>
+      </c>
+      <c r="F2887" s="24" t="str"/>
+      <c r="G2887" s="24" t="str"/>
+      <c r="H2887" s="189" t="str">
+        <v>Базовые характеристики</v>
+      </c>
+      <c r="I2887" s="143" t="str"/>
+    </row>
+    <row r="2888" ht="52" customHeight="1">
+      <c r="A2888" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2888" t="str" s="23">
+        <v>workbench.results</v>
+      </c>
+      <c r="C2888" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2888" t="str" s="24"/>
+      <c r="E2888" s="188" t="str">
+        <v>Calculated stats</v>
+      </c>
+      <c r="F2888" s="24" t="str"/>
+      <c r="G2888" s="24" t="str"/>
+      <c r="H2888" s="189" t="str">
+        <v>Результаты расчёта</v>
+      </c>
+      <c r="I2888" s="143" t="str"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/localization/translations.xlsx
+++ b/localization/translations.xlsx
@@ -320,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -887,6 +887,18 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -895,8 +907,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2888" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I2888"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2894" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I2894"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Раздел"/>
     <tableColumn id="2" name="ID (не менять)"/>
@@ -72204,6 +72216,132 @@
       </c>
       <c r="I2888" s="143" t="str"/>
     </row>
+    <row r="2889" ht="52" customHeight="1">
+      <c r="A2889" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2889" t="str" s="23">
+        <v>calculator.inputMaximum</v>
+      </c>
+      <c r="C2889" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2889" t="str" s="24"/>
+      <c r="E2889" s="190" t="str">
+        <v>{field}: maximum {max}. Esc cancels your edit.</v>
+      </c>
+      <c r="F2889" s="24" t="str"/>
+      <c r="G2889" s="24" t="str"/>
+      <c r="H2889" s="191" t="str">
+        <v>Максимальное значение поля «{field}» — {max}. Esc отменяет ввод.</v>
+      </c>
+      <c r="I2889" s="143" t="str"/>
+    </row>
+    <row r="2890" ht="52" customHeight="1">
+      <c r="A2890" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2890" t="str" s="23">
+        <v>calculator.inputMinimum</v>
+      </c>
+      <c r="C2890" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2890" t="str" s="24"/>
+      <c r="E2890" s="190" t="str">
+        <v>{field}: minimum {min}. Esc cancels your edit.</v>
+      </c>
+      <c r="F2890" s="24" t="str"/>
+      <c r="G2890" s="24" t="str"/>
+      <c r="H2890" s="191" t="str">
+        <v>Минимальное значение поля «{field}» — {min}. Esc отменяет ввод.</v>
+      </c>
+      <c r="I2890" s="143" t="str"/>
+    </row>
+    <row r="2891" ht="52" customHeight="1">
+      <c r="A2891" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2891" t="str" s="23">
+        <v>calculator.inputWholeNumber</v>
+      </c>
+      <c r="C2891" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2891" t="str" s="24"/>
+      <c r="E2891" s="190" t="str">
+        <v>{field}: enter a whole number from {min} to {max}. Esc cancels your edit.</v>
+      </c>
+      <c r="F2891" s="24" t="str"/>
+      <c r="G2891" s="24" t="str"/>
+      <c r="H2891" s="191" t="str">
+        <v>Для поля «{field}» введите целое число от {min} до {max}. Esc отменяет ввод.</v>
+      </c>
+      <c r="I2891" s="143" t="str"/>
+    </row>
+    <row r="2892" ht="52" customHeight="1">
+      <c r="A2892" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2892" t="str" s="23">
+        <v>calculator.inputRequired</v>
+      </c>
+      <c r="C2892" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2892" t="str" s="24"/>
+      <c r="E2892" s="190" t="str">
+        <v>{field}: enter a value from {min} to {max}. Esc cancels your edit.</v>
+      </c>
+      <c r="F2892" s="24" t="str"/>
+      <c r="G2892" s="24" t="str"/>
+      <c r="H2892" s="191" t="str">
+        <v>Заполните поле «{field}»: целое число от {min} до {max}. Esc отменяет ввод.</v>
+      </c>
+      <c r="I2892" s="143" t="str"/>
+    </row>
+    <row r="2893" ht="52" customHeight="1">
+      <c r="A2893" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2893" t="str" s="23">
+        <v>calculator.inputBudgetForField</v>
+      </c>
+      <c r="C2893" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2893" t="str" s="24"/>
+      <c r="E2893" s="190" t="str">
+        <v>{field}: not enough attribute points. Applied value: {value}.</v>
+      </c>
+      <c r="F2893" s="24" t="str"/>
+      <c r="G2893" s="24" t="str"/>
+      <c r="H2893" s="191" t="str">
+        <v>Для поля «{field}» не хватает очков характеристик. Применено значение: {value}.</v>
+      </c>
+      <c r="I2893" s="143" t="str"/>
+    </row>
+    <row r="2894" ht="52" customHeight="1">
+      <c r="A2894" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2894" t="str" s="23">
+        <v>skills.listDisabled</v>
+      </c>
+      <c r="C2894" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2894" t="str" s="24"/>
+      <c r="E2894" s="192" t="str">
+        <v>The skill list is switched off. Enable it to show available and learned skills.</v>
+      </c>
+      <c r="F2894" s="24" t="str"/>
+      <c r="G2894" s="24" t="str"/>
+      <c r="H2894" s="193" t="str">
+        <v>Список умений выключен. Включите его, чтобы увидеть доступные и изученные умения.</v>
+      </c>
+      <c r="I2894" s="143" t="str"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/localization/translations.xlsx
+++ b/localization/translations.xlsx
@@ -320,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -881,6 +881,24 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -889,8 +907,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2883" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I2883"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2894" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I2894"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Раздел"/>
     <tableColumn id="2" name="ID (не менять)"/>
@@ -72093,6 +72111,237 @@
       </c>
       <c r="I2883" s="143" t="str"/>
     </row>
+    <row r="2884" ht="52" customHeight="1">
+      <c r="A2884" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2884" t="str" s="23">
+        <v>workbench.character</v>
+      </c>
+      <c r="C2884" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2884" t="str" s="24"/>
+      <c r="E2884" s="188" t="str">
+        <v>Character</v>
+      </c>
+      <c r="F2884" s="24" t="str"/>
+      <c r="G2884" s="24" t="str"/>
+      <c r="H2884" s="189" t="str">
+        <v>Персонаж</v>
+      </c>
+      <c r="I2884" s="143" t="str"/>
+    </row>
+    <row r="2885" ht="52" customHeight="1">
+      <c r="A2885" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2885" t="str" s="23">
+        <v>workbench.skills</v>
+      </c>
+      <c r="C2885" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2885" t="str" s="24"/>
+      <c r="E2885" s="188" t="str">
+        <v>Skills</v>
+      </c>
+      <c r="F2885" s="24" t="str"/>
+      <c r="G2885" s="24" t="str"/>
+      <c r="H2885" s="189" t="str">
+        <v>Умения</v>
+      </c>
+      <c r="I2885" s="143" t="str"/>
+    </row>
+    <row r="2886" ht="52" customHeight="1">
+      <c r="A2886" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2886" t="str" s="23">
+        <v>workbench.effects</v>
+      </c>
+      <c r="C2886" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2886" t="str" s="24"/>
+      <c r="E2886" s="188" t="str">
+        <v>Effects</v>
+      </c>
+      <c r="F2886" s="24" t="str"/>
+      <c r="G2886" s="24" t="str"/>
+      <c r="H2886" s="189" t="str">
+        <v>Эффекты</v>
+      </c>
+      <c r="I2886" s="143" t="str"/>
+    </row>
+    <row r="2887" ht="52" customHeight="1">
+      <c r="A2887" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2887" t="str" s="23">
+        <v>workbench.baseStats</v>
+      </c>
+      <c r="C2887" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2887" t="str" s="24"/>
+      <c r="E2887" s="188" t="str">
+        <v>Base stats</v>
+      </c>
+      <c r="F2887" s="24" t="str"/>
+      <c r="G2887" s="24" t="str"/>
+      <c r="H2887" s="189" t="str">
+        <v>Базовые характеристики</v>
+      </c>
+      <c r="I2887" s="143" t="str"/>
+    </row>
+    <row r="2888" ht="52" customHeight="1">
+      <c r="A2888" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2888" t="str" s="23">
+        <v>workbench.results</v>
+      </c>
+      <c r="C2888" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2888" t="str" s="24"/>
+      <c r="E2888" s="188" t="str">
+        <v>Calculated stats</v>
+      </c>
+      <c r="F2888" s="24" t="str"/>
+      <c r="G2888" s="24" t="str"/>
+      <c r="H2888" s="189" t="str">
+        <v>Результаты расчёта</v>
+      </c>
+      <c r="I2888" s="143" t="str"/>
+    </row>
+    <row r="2889" ht="52" customHeight="1">
+      <c r="A2889" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2889" t="str" s="23">
+        <v>calculator.inputMaximum</v>
+      </c>
+      <c r="C2889" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2889" t="str" s="24"/>
+      <c r="E2889" s="190" t="str">
+        <v>{field}: maximum {max}. Esc cancels your edit.</v>
+      </c>
+      <c r="F2889" s="24" t="str"/>
+      <c r="G2889" s="24" t="str"/>
+      <c r="H2889" s="191" t="str">
+        <v>Максимальное значение поля «{field}» — {max}. Esc отменяет ввод.</v>
+      </c>
+      <c r="I2889" s="143" t="str"/>
+    </row>
+    <row r="2890" ht="52" customHeight="1">
+      <c r="A2890" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2890" t="str" s="23">
+        <v>calculator.inputMinimum</v>
+      </c>
+      <c r="C2890" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2890" t="str" s="24"/>
+      <c r="E2890" s="190" t="str">
+        <v>{field}: minimum {min}. Esc cancels your edit.</v>
+      </c>
+      <c r="F2890" s="24" t="str"/>
+      <c r="G2890" s="24" t="str"/>
+      <c r="H2890" s="191" t="str">
+        <v>Минимальное значение поля «{field}» — {min}. Esc отменяет ввод.</v>
+      </c>
+      <c r="I2890" s="143" t="str"/>
+    </row>
+    <row r="2891" ht="52" customHeight="1">
+      <c r="A2891" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2891" t="str" s="23">
+        <v>calculator.inputWholeNumber</v>
+      </c>
+      <c r="C2891" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2891" t="str" s="24"/>
+      <c r="E2891" s="190" t="str">
+        <v>{field}: enter a whole number from {min} to {max}. Esc cancels your edit.</v>
+      </c>
+      <c r="F2891" s="24" t="str"/>
+      <c r="G2891" s="24" t="str"/>
+      <c r="H2891" s="191" t="str">
+        <v>Для поля «{field}» введите целое число от {min} до {max}. Esc отменяет ввод.</v>
+      </c>
+      <c r="I2891" s="143" t="str"/>
+    </row>
+    <row r="2892" ht="52" customHeight="1">
+      <c r="A2892" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2892" t="str" s="23">
+        <v>calculator.inputRequired</v>
+      </c>
+      <c r="C2892" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2892" t="str" s="24"/>
+      <c r="E2892" s="190" t="str">
+        <v>{field}: enter a value from {min} to {max}. Esc cancels your edit.</v>
+      </c>
+      <c r="F2892" s="24" t="str"/>
+      <c r="G2892" s="24" t="str"/>
+      <c r="H2892" s="191" t="str">
+        <v>Заполните поле «{field}»: целое число от {min} до {max}. Esc отменяет ввод.</v>
+      </c>
+      <c r="I2892" s="143" t="str"/>
+    </row>
+    <row r="2893" ht="52" customHeight="1">
+      <c r="A2893" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2893" t="str" s="23">
+        <v>calculator.inputBudgetForField</v>
+      </c>
+      <c r="C2893" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2893" t="str" s="24"/>
+      <c r="E2893" s="190" t="str">
+        <v>{field}: not enough attribute points. Applied value: {value}.</v>
+      </c>
+      <c r="F2893" s="24" t="str"/>
+      <c r="G2893" s="24" t="str"/>
+      <c r="H2893" s="191" t="str">
+        <v>Для поля «{field}» не хватает очков характеристик. Применено значение: {value}.</v>
+      </c>
+      <c r="I2893" s="143" t="str"/>
+    </row>
+    <row r="2894" ht="52" customHeight="1">
+      <c r="A2894" t="str" s="23">
+        <v>Интерфейс</v>
+      </c>
+      <c r="B2894" t="str" s="23">
+        <v>skills.listDisabled</v>
+      </c>
+      <c r="C2894" t="str" s="23">
+        <v>Интерфейс сайта</v>
+      </c>
+      <c r="D2894" t="str" s="24"/>
+      <c r="E2894" s="192" t="str">
+        <v>The skill list is switched off. Enable it to show available and learned skills.</v>
+      </c>
+      <c r="F2894" s="24" t="str"/>
+      <c r="G2894" s="24" t="str"/>
+      <c r="H2894" s="193" t="str">
+        <v>Список умений выключен. Включите его, чтобы увидеть доступные и изученные умения.</v>
+      </c>
+      <c r="I2894" s="143" t="str"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/localization/translations.xlsx
+++ b/localization/translations.xlsx
@@ -913,8 +913,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2900" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I2900"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2904" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I2904"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Раздел"/>
     <tableColumn id="2" name="ID (не менять)"/>
@@ -34239,7 +34239,11 @@
       <c r="G1346" s="24" t="str">
         <v>激怒</v>
       </c>
-      <c r="H1346" s="25" t="str"/>
+      <c r="H1346" t="inlineStr" s="25">
+        <is>
+          <t>Провокация</t>
+        </is>
+      </c>
       <c r="I1346" s="143" t="str"/>
     </row>
     <row r="1347" ht="21" customHeight="1">
@@ -34264,7 +34268,11 @@
       <c r="G1347" s="24" t="str">
         <v>藥劑專門</v>
       </c>
-      <c r="H1347" s="25" t="str"/>
+      <c r="H1347" t="inlineStr" s="25">
+        <is>
+          <t>Улучшение лечения</t>
+        </is>
+      </c>
       <c r="I1347" s="143" t="str"/>
     </row>
     <row r="1348" ht="21" customHeight="1">
@@ -34289,7 +34297,11 @@
       <c r="G1348" s="24" t="str">
         <v>風之迅捷</v>
       </c>
-      <c r="H1348" s="25" t="str"/>
+      <c r="H1348" t="inlineStr" s="25">
+        <is>
+          <t>Рывок</t>
+        </is>
+      </c>
       <c r="I1348" s="143" t="str"/>
     </row>
     <row r="1349" ht="21" customHeight="1">
@@ -34314,7 +34326,11 @@
       <c r="G1349" s="24" t="str">
         <v>提高傷害</v>
       </c>
-      <c r="H1349" s="25" t="str"/>
+      <c r="H1349" t="inlineStr" s="25">
+        <is>
+          <t>Невероятная сила</t>
+        </is>
+      </c>
       <c r="I1349" s="143" t="str"/>
     </row>
     <row r="1350" ht="21" customHeight="1">
@@ -34339,7 +34355,11 @@
       <c r="G1350" s="24" t="str">
         <v>削足</v>
       </c>
-      <c r="H1350" s="25" t="str"/>
+      <c r="H1350" t="inlineStr" s="25">
+        <is>
+          <t>Удар по ногам</t>
+        </is>
+      </c>
       <c r="I1350" s="143" t="str"/>
     </row>
     <row r="1351" ht="21" customHeight="1">
@@ -34364,7 +34384,11 @@
       <c r="G1351" s="24" t="str">
         <v>信念</v>
       </c>
-      <c r="H1351" s="25" t="str"/>
+      <c r="H1351" t="inlineStr" s="25">
+        <is>
+          <t>Самооборона</t>
+        </is>
+      </c>
       <c r="I1351" s="143" t="str"/>
     </row>
     <row r="1352" ht="21" customHeight="1">
@@ -34389,7 +34413,11 @@
       <c r="G1352" s="24" t="str">
         <v>瘋狂挑釁</v>
       </c>
-      <c r="H1352" s="25" t="str"/>
+      <c r="H1352" t="inlineStr" s="25">
+        <is>
+          <t>Безумная провокация</t>
+        </is>
+      </c>
       <c r="I1352" s="143" t="str"/>
     </row>
     <row r="1353" ht="21" customHeight="1">
@@ -34414,7 +34442,11 @@
       <c r="G1353" s="24" t="str">
         <v>戰爭祈禱</v>
       </c>
-      <c r="H1353" s="25" t="str"/>
+      <c r="H1353" t="inlineStr" s="25">
+        <is>
+          <t>Боевой клич</t>
+        </is>
+      </c>
       <c r="I1353" s="143" t="str"/>
     </row>
     <row r="1354" ht="21" customHeight="1">
@@ -34439,7 +34471,11 @@
       <c r="G1354" s="24" t="str">
         <v>天佑</v>
       </c>
-      <c r="H1354" s="25" t="str"/>
+      <c r="H1354" t="inlineStr" s="25">
+        <is>
+          <t>Божественное благословление</t>
+        </is>
+      </c>
       <c r="I1354" s="143" t="str"/>
     </row>
     <row r="1355" ht="21" customHeight="1">
@@ -34464,7 +34500,11 @@
       <c r="G1355" s="24" t="str">
         <v>狂怒攻擊</v>
       </c>
-      <c r="H1355" s="25" t="str"/>
+      <c r="H1355" t="inlineStr" s="25">
+        <is>
+          <t>Яростная атака</t>
+        </is>
+      </c>
       <c r="I1355" s="143" t="str"/>
     </row>
     <row r="1356" ht="21" customHeight="1">
@@ -34489,7 +34529,11 @@
       <c r="G1356" s="24" t="str">
         <v>防禦集中</v>
       </c>
-      <c r="H1356" s="25" t="str"/>
+      <c r="H1356" t="inlineStr" s="25">
+        <is>
+          <t>Бастион</t>
+        </is>
+      </c>
       <c r="I1356" s="143" t="str"/>
     </row>
     <row r="1357" ht="21" customHeight="1">
@@ -34514,7 +34558,11 @@
       <c r="G1357" s="24" t="str">
         <v>捨命攻擊</v>
       </c>
-      <c r="H1357" s="25" t="str"/>
+      <c r="H1357" t="inlineStr" s="25">
+        <is>
+          <t>Отчаянье</t>
+        </is>
+      </c>
       <c r="I1357" s="143" t="str"/>
     </row>
     <row r="1358" ht="21" customHeight="1">
@@ -34539,7 +34587,11 @@
       <c r="G1358" s="24" t="str">
         <v>血之契約</v>
       </c>
-      <c r="H1358" s="25" t="str"/>
+      <c r="H1358" t="inlineStr" s="25">
+        <is>
+          <t>Воля к жизни</t>
+        </is>
+      </c>
       <c r="I1358" s="143" t="str"/>
     </row>
     <row r="1359" ht="21" customHeight="1">
@@ -34564,7 +34616,11 @@
       <c r="G1359" s="24" t="str">
         <v>致殘陷阱</v>
       </c>
-      <c r="H1359" s="25" t="str"/>
+      <c r="H1359" t="inlineStr" s="25">
+        <is>
+          <t>Захват</t>
+        </is>
+      </c>
       <c r="I1359" s="143" t="str"/>
     </row>
     <row r="1360" ht="21" customHeight="1">
@@ -34689,7 +34745,11 @@
       <c r="G1364" s="24" t="str">
         <v>二連斬</v>
       </c>
-      <c r="H1364" s="25" t="str"/>
+      <c r="H1364" t="inlineStr" s="25">
+        <is>
+          <t>Двойной удар</t>
+        </is>
+      </c>
       <c r="I1364" s="143" t="str"/>
     </row>
     <row r="1365" ht="21" customHeight="1">
@@ -34714,7 +34774,11 @@
       <c r="G1365" s="24" t="str">
         <v>三連斬</v>
       </c>
-      <c r="H1365" s="25" t="str"/>
+      <c r="H1365" t="inlineStr" s="25">
+        <is>
+          <t>Порез</t>
+        </is>
+      </c>
       <c r="I1365" s="143" t="str"/>
     </row>
     <row r="1366" ht="21" customHeight="1">
@@ -34739,7 +34803,11 @@
       <c r="G1366" s="24" t="str">
         <v>迴旋斬</v>
       </c>
-      <c r="H1366" s="25" t="str"/>
+      <c r="H1366" t="inlineStr" s="25">
+        <is>
+          <t>Круговой удар</t>
+        </is>
+      </c>
       <c r="I1366" s="143" t="str"/>
     </row>
     <row r="1367" ht="21" customHeight="1">
@@ -34764,7 +34832,11 @@
       <c r="G1367" s="24" t="str">
         <v>怒之反擊</v>
       </c>
-      <c r="H1367" s="25" t="str"/>
+      <c r="H1367" t="inlineStr" s="25">
+        <is>
+          <t>Парирование</t>
+        </is>
+      </c>
       <c r="I1367" s="143" t="str"/>
     </row>
     <row r="1368" ht="21" customHeight="1">
@@ -34789,7 +34861,11 @@
       <c r="G1368" s="24" t="str">
         <v>瞄準</v>
       </c>
-      <c r="H1368" s="25" t="str"/>
+      <c r="H1368" t="inlineStr" s="25">
+        <is>
+          <t>Сосредоточенность</t>
+        </is>
+      </c>
       <c r="I1368" s="143" t="str"/>
     </row>
     <row r="1369" ht="21" customHeight="1">
@@ -34814,7 +34890,11 @@
       <c r="G1369" s="24" t="str">
         <v>急流</v>
       </c>
-      <c r="H1369" s="25" t="str"/>
+      <c r="H1369" t="inlineStr" s="25">
+        <is>
+          <t>Громовой удар</t>
+        </is>
+      </c>
       <c r="I1369" s="143" t="str"/>
     </row>
     <row r="1370" ht="21" customHeight="1">
@@ -34839,7 +34919,11 @@
       <c r="G1370" s="24" t="str">
         <v>劍術大師</v>
       </c>
-      <c r="H1370" s="25" t="str"/>
+      <c r="H1370" t="inlineStr" s="25">
+        <is>
+          <t>Мастер меча</t>
+        </is>
+      </c>
       <c r="I1370" s="143" t="str"/>
     </row>
     <row r="1371" ht="21" customHeight="1">
@@ -34864,7 +34948,11 @@
       <c r="G1371" s="24" t="str">
         <v>強襲</v>
       </c>
-      <c r="H1371" s="25" t="str"/>
+      <c r="H1371" t="inlineStr" s="25">
+        <is>
+          <t>Стремительный удар</t>
+        </is>
+      </c>
       <c r="I1371" s="143" t="str"/>
     </row>
     <row r="1372" ht="21" customHeight="1">
@@ -34889,7 +34977,11 @@
       <c r="G1372" s="24" t="str">
         <v>強突</v>
       </c>
-      <c r="H1372" s="25" t="str"/>
+      <c r="H1372" t="inlineStr" s="25">
+        <is>
+          <t>Внезапный рывок</t>
+        </is>
+      </c>
       <c r="I1372" s="143" t="str"/>
     </row>
     <row r="1373" ht="21" customHeight="1">
@@ -34914,7 +35006,11 @@
       <c r="G1373" s="24" t="str">
         <v>穿刺</v>
       </c>
-      <c r="H1373" s="25" t="str"/>
+      <c r="H1373" t="inlineStr" s="25">
+        <is>
+          <t>Удар копьем</t>
+        </is>
+      </c>
       <c r="I1373" s="143" t="str"/>
     </row>
     <row r="1374" ht="21" customHeight="1">
@@ -34939,7 +35035,11 @@
       <c r="G1374" s="24" t="str">
         <v>三連刺</v>
       </c>
-      <c r="H1374" s="25" t="str"/>
+      <c r="H1374" t="inlineStr" s="25">
+        <is>
+          <t>Тройной укол</t>
+        </is>
+      </c>
       <c r="I1374" s="143" t="str"/>
     </row>
     <row r="1375" ht="21" customHeight="1">
@@ -34964,7 +35064,11 @@
       <c r="G1375" s="24" t="str">
         <v>回馬槍</v>
       </c>
-      <c r="H1375" s="25" t="str"/>
+      <c r="H1375" t="inlineStr" s="25">
+        <is>
+          <t>Могучий удар</t>
+        </is>
+      </c>
       <c r="I1375" s="143" t="str"/>
     </row>
     <row r="1376" ht="21" customHeight="1">
@@ -34989,7 +35093,11 @@
       <c r="G1376" s="24" t="str">
         <v>投槍</v>
       </c>
-      <c r="H1376" s="25" t="str"/>
+      <c r="H1376" t="inlineStr" s="25">
+        <is>
+          <t>Бросок</t>
+        </is>
+      </c>
       <c r="I1376" s="143" t="str"/>
     </row>
     <row r="1377" ht="21" customHeight="1">
@@ -35014,7 +35122,11 @@
       <c r="G1377" s="24" t="str">
         <v>四連刺</v>
       </c>
-      <c r="H1377" s="25" t="str"/>
+      <c r="H1377" t="inlineStr" s="25">
+        <is>
+          <t>Четверной укол</t>
+        </is>
+      </c>
       <c r="I1377" s="143" t="str"/>
     </row>
     <row r="1378" ht="21" customHeight="1">
@@ -35039,7 +35151,11 @@
       <c r="G1378" s="24" t="str">
         <v>反制</v>
       </c>
-      <c r="H1378" s="25" t="str"/>
+      <c r="H1378" t="inlineStr" s="25">
+        <is>
+          <t>Отпор</t>
+        </is>
+      </c>
       <c r="I1378" s="143" t="str"/>
     </row>
     <row r="1379" ht="21" customHeight="1">
@@ -35064,7 +35180,11 @@
       <c r="G1379" s="24" t="str">
         <v>蓄勢</v>
       </c>
-      <c r="H1379" s="25" t="str"/>
+      <c r="H1379" t="inlineStr" s="25">
+        <is>
+          <t>Критический удар</t>
+        </is>
+      </c>
       <c r="I1379" s="143" t="str"/>
     </row>
     <row r="1380" ht="21" customHeight="1">
@@ -35089,7 +35209,11 @@
       <c r="G1380" s="24" t="str">
         <v>反制一擊</v>
       </c>
-      <c r="H1380" s="25" t="str"/>
+      <c r="H1380" t="inlineStr" s="25">
+        <is>
+          <t>Контратака</t>
+        </is>
+      </c>
       <c r="I1380" s="143" t="str"/>
     </row>
     <row r="1381" ht="21" customHeight="1">
@@ -35114,7 +35238,11 @@
       <c r="G1381" s="24" t="str">
         <v>神聖指引</v>
       </c>
-      <c r="H1381" s="25" t="str"/>
+      <c r="H1381" t="inlineStr" s="25">
+        <is>
+          <t>Хладнокровие</t>
+        </is>
+      </c>
       <c r="I1381" s="143" t="str"/>
     </row>
     <row r="1382" ht="21" customHeight="1">
@@ -35139,7 +35267,11 @@
       <c r="G1382" s="24" t="str">
         <v>地裂斬</v>
       </c>
-      <c r="H1382" s="25" t="str"/>
+      <c r="H1382" t="inlineStr" s="25">
+        <is>
+          <t>Раскол</t>
+        </is>
+      </c>
       <c r="I1382" s="143" t="str"/>
     </row>
     <row r="1383" ht="21" customHeight="1">
@@ -35164,7 +35296,11 @@
       <c r="G1383" s="24" t="str">
         <v>亡命一擊</v>
       </c>
-      <c r="H1383" s="25" t="str"/>
+      <c r="H1383" t="inlineStr" s="25">
+        <is>
+          <t>Решающий удар</t>
+        </is>
+      </c>
       <c r="I1383" s="143" t="str"/>
     </row>
     <row r="1384" ht="21" customHeight="1">
@@ -35189,7 +35325,11 @@
       <c r="G1384" s="24" t="str">
         <v>碎顱擊</v>
       </c>
-      <c r="H1384" s="25" t="str"/>
+      <c r="H1384" t="inlineStr" s="25">
+        <is>
+          <t>Оглушающий удар</t>
+        </is>
+      </c>
       <c r="I1384" s="143" t="str"/>
     </row>
     <row r="1385" ht="21" customHeight="1">
@@ -35214,7 +35354,11 @@
       <c r="G1385" s="24" t="str">
         <v>大地衝擊</v>
       </c>
-      <c r="H1385" s="25" t="str"/>
+      <c r="H1385" t="inlineStr" s="25">
+        <is>
+          <t>Удар в землю</t>
+        </is>
+      </c>
       <c r="I1385" s="143" t="str"/>
     </row>
     <row r="1386" ht="21" customHeight="1">
@@ -35239,7 +35383,11 @@
       <c r="G1386" s="24" t="str">
         <v>眩暈錘</v>
       </c>
-      <c r="H1386" s="25" t="str"/>
+      <c r="H1386" t="inlineStr" s="25">
+        <is>
+          <t>Оглушающий грохот</t>
+        </is>
+      </c>
       <c r="I1386" s="143" t="str"/>
     </row>
     <row r="1387" ht="21" customHeight="1">
@@ -35264,7 +35412,11 @@
       <c r="G1387" s="24" t="str">
         <v>破防衝擊</v>
       </c>
-      <c r="H1387" s="25" t="str"/>
+      <c r="H1387" t="inlineStr" s="25">
+        <is>
+          <t>Удар по броне</t>
+        </is>
+      </c>
       <c r="I1387" s="143" t="str"/>
     </row>
     <row r="1388" ht="21" customHeight="1">
@@ -35289,7 +35441,11 @@
       <c r="G1388" s="24" t="str">
         <v>？？？</v>
       </c>
-      <c r="H1388" s="25" t="str"/>
+      <c r="H1388" t="inlineStr" s="25">
+        <is>
+          <t>Удар по щиту</t>
+        </is>
+      </c>
       <c r="I1388" s="143" t="str"/>
     </row>
     <row r="1389" ht="21" customHeight="1">
@@ -35314,7 +35470,11 @@
       <c r="G1389" s="24" t="str">
         <v>？？？</v>
       </c>
-      <c r="H1389" s="25" t="str"/>
+      <c r="H1389" t="inlineStr" s="25">
+        <is>
+          <t>Энергетический удар</t>
+        </is>
+      </c>
       <c r="I1389" s="143" t="str"/>
     </row>
     <row r="1390" ht="21" customHeight="1">
@@ -35339,7 +35499,11 @@
       <c r="G1390" s="24" t="str">
         <v>棘刺護盾</v>
       </c>
-      <c r="H1390" s="25" t="str"/>
+      <c r="H1390" t="inlineStr" s="25">
+        <is>
+          <t>Великая стена</t>
+        </is>
+      </c>
       <c r="I1390" s="143" t="str"/>
     </row>
     <row r="1391" ht="21" customHeight="1">
@@ -35364,7 +35528,11 @@
       <c r="G1391" s="24" t="str">
         <v>精神格擋</v>
       </c>
-      <c r="H1391" s="25" t="str"/>
+      <c r="H1391" t="inlineStr" s="25">
+        <is>
+          <t>Магический блок</t>
+        </is>
+      </c>
       <c r="I1391" s="143" t="str"/>
     </row>
     <row r="1392" ht="21" customHeight="1">
@@ -35389,7 +35557,11 @@
       <c r="G1392" s="24" t="str">
         <v>防禦解散</v>
       </c>
-      <c r="H1392" s="25" t="str"/>
+      <c r="H1392" t="inlineStr" s="25">
+        <is>
+          <t>Защитные маневры</t>
+        </is>
+      </c>
       <c r="I1392" s="143" t="str"/>
     </row>
     <row r="1393" ht="21" customHeight="1">
@@ -35414,7 +35586,11 @@
       <c r="G1393" s="24" t="str">
         <v>格檔</v>
       </c>
-      <c r="H1393" s="25" t="str"/>
+      <c r="H1393" t="inlineStr" s="25">
+        <is>
+          <t>Блокирование</t>
+        </is>
+      </c>
       <c r="I1393" s="143" t="str"/>
     </row>
     <row r="1394" ht="21" customHeight="1">
@@ -35439,7 +35615,11 @@
       <c r="G1394" s="24" t="str">
         <v>盾牌重擊</v>
       </c>
-      <c r="H1394" s="25" t="str"/>
+      <c r="H1394" t="inlineStr" s="25">
+        <is>
+          <t>Удар щитом</t>
+        </is>
+      </c>
       <c r="I1394" s="143" t="str"/>
     </row>
     <row r="1395" ht="21" customHeight="1">
@@ -35464,7 +35644,11 @@
       <c r="G1395" s="24" t="str">
         <v>剛毅護體</v>
       </c>
-      <c r="H1395" s="25" t="str"/>
+      <c r="H1395" t="inlineStr" s="25">
+        <is>
+          <t>Железная чешуя</t>
+        </is>
+      </c>
       <c r="I1395" s="143" t="str"/>
     </row>
     <row r="1396" ht="21" customHeight="1">
@@ -35489,7 +35673,11 @@
       <c r="G1396" s="24" t="str">
         <v>自動警衛</v>
       </c>
-      <c r="H1396" s="25" t="str"/>
+      <c r="H1396" t="inlineStr" s="25">
+        <is>
+          <t>Автозащита</t>
+        </is>
+      </c>
       <c r="I1396" s="143" t="str"/>
     </row>
     <row r="1397" ht="21" customHeight="1">
@@ -35514,7 +35702,11 @@
       <c r="G1397" s="24" t="str">
         <v>舉盾衝擊</v>
       </c>
-      <c r="H1397" s="25" t="str"/>
+      <c r="H1397" t="inlineStr" s="25">
+        <is>
+          <t>Бой щитом</t>
+        </is>
+      </c>
       <c r="I1397" s="143" t="str"/>
     </row>
     <row r="1398" ht="21" customHeight="1">
@@ -35539,7 +35731,11 @@
       <c r="G1398" s="24" t="str">
         <v>防禦</v>
       </c>
-      <c r="H1398" s="25" t="str"/>
+      <c r="H1398" t="inlineStr" s="25">
+        <is>
+          <t>Защита в движении</t>
+        </is>
+      </c>
       <c r="I1398" s="143" t="str"/>
     </row>
     <row r="1399" ht="21" customHeight="1">
@@ -35564,7 +35760,11 @@
       <c r="G1399" s="24" t="str">
         <v>替身護衛</v>
       </c>
-      <c r="H1399" s="25" t="str"/>
+      <c r="H1399" t="inlineStr" s="25">
+        <is>
+          <t>Жертвенность</t>
+        </is>
+      </c>
       <c r="I1399" s="143" t="str"/>
     </row>
     <row r="1400" ht="21" customHeight="1">
@@ -35589,7 +35789,11 @@
       <c r="G1400" s="24" t="str">
         <v>犧牲自我</v>
       </c>
-      <c r="H1400" s="25" t="str"/>
+      <c r="H1400" t="inlineStr" s="25">
+        <is>
+          <t>Великая жертва</t>
+        </is>
+      </c>
       <c r="I1400" s="143" t="str"/>
     </row>
     <row r="1401" ht="21" customHeight="1">
@@ -35614,7 +35818,11 @@
       <c r="G1401" s="24" t="str">
         <v>詛咒的聖歌</v>
       </c>
-      <c r="H1401" s="25" t="str"/>
+      <c r="H1401" t="inlineStr" s="25">
+        <is>
+          <t>Сковывающая песнь</t>
+        </is>
+      </c>
       <c r="I1401" s="143" t="str"/>
     </row>
     <row r="1402" ht="21" customHeight="1">
@@ -35639,7 +35847,11 @@
       <c r="G1402" s="24" t="str">
         <v>鷹眼</v>
       </c>
-      <c r="H1402" s="25" t="str"/>
+      <c r="H1402" t="inlineStr" s="25">
+        <is>
+          <t>Орлиный глаз</t>
+        </is>
+      </c>
       <c r="I1402" s="143" t="str"/>
     </row>
     <row r="1403" ht="21" customHeight="1">
@@ -35664,7 +35876,11 @@
       <c r="G1403" s="24" t="str">
         <v>迴避上升</v>
       </c>
-      <c r="H1403" s="25" t="str"/>
+      <c r="H1403" t="inlineStr" s="25">
+        <is>
+          <t>Быстрое уклонение</t>
+        </is>
+      </c>
       <c r="I1403" s="143" t="str"/>
     </row>
     <row r="1404" ht="21" customHeight="1">
@@ -35689,7 +35905,11 @@
       <c r="G1404" s="24" t="str">
         <v>風之祝福</v>
       </c>
-      <c r="H1404" s="25" t="str"/>
+      <c r="H1404" t="inlineStr" s="25">
+        <is>
+          <t>Благословение ветра</t>
+        </is>
+      </c>
       <c r="I1404" s="143" t="str"/>
     </row>
     <row r="1405" ht="21" customHeight="1">
@@ -35714,7 +35934,11 @@
       <c r="G1405" s="24" t="str">
         <v>提升專注</v>
       </c>
-      <c r="H1405" s="25" t="str"/>
+      <c r="H1405" t="inlineStr" s="25">
+        <is>
+          <t>Массовая сосредоточенность</t>
+        </is>
+      </c>
       <c r="I1405" s="143" t="str"/>
     </row>
     <row r="1406" ht="21" customHeight="1">
@@ -35739,7 +35963,11 @@
       <c r="G1406" s="24" t="str">
         <v>隱密機關</v>
       </c>
-      <c r="H1406" s="25" t="str"/>
+      <c r="H1406" t="inlineStr" s="25">
+        <is>
+          <t>Тайная ловушка</t>
+        </is>
+      </c>
       <c r="I1406" s="143" t="str"/>
     </row>
     <row r="1407" ht="21" customHeight="1">
@@ -35764,7 +35992,11 @@
       <c r="G1407" s="24" t="str">
         <v>速射</v>
       </c>
-      <c r="H1407" s="25" t="str"/>
+      <c r="H1407" t="inlineStr" s="25">
+        <is>
+          <t>Стремительная стрела</t>
+        </is>
+      </c>
       <c r="I1407" s="143" t="str"/>
     </row>
     <row r="1408" ht="21" customHeight="1">
@@ -35789,7 +36021,11 @@
       <c r="G1408" s="24" t="str">
         <v>精准狙擊</v>
       </c>
-      <c r="H1408" s="25" t="str"/>
+      <c r="H1408" t="inlineStr" s="25">
+        <is>
+          <t>Точная стрельба</t>
+        </is>
+      </c>
       <c r="I1408" s="143" t="str"/>
     </row>
     <row r="1409" ht="21" customHeight="1">
@@ -35814,7 +36050,11 @@
       <c r="G1409" s="24" t="str">
         <v>燃油箭</v>
       </c>
-      <c r="H1409" s="25" t="str"/>
+      <c r="H1409" t="inlineStr" s="25">
+        <is>
+          <t>Пламенная стрела</t>
+        </is>
+      </c>
       <c r="I1409" s="143" t="str"/>
     </row>
     <row r="1410" ht="21" customHeight="1">
@@ -35839,7 +36079,11 @@
       <c r="G1410" s="24" t="str">
         <v>定時爆彈</v>
       </c>
-      <c r="H1410" s="25" t="str"/>
+      <c r="H1410" t="inlineStr" s="25">
+        <is>
+          <t>Слежка</t>
+        </is>
+      </c>
       <c r="I1410" s="143" t="str"/>
     </row>
     <row r="1411" ht="21" customHeight="1">
@@ -35864,7 +36108,11 @@
       <c r="G1411" s="24" t="str">
         <v>風之速射</v>
       </c>
-      <c r="H1411" s="25" t="str"/>
+      <c r="H1411" t="inlineStr" s="25">
+        <is>
+          <t>Двойной выстрел</t>
+        </is>
+      </c>
       <c r="I1411" s="143" t="str"/>
     </row>
     <row r="1412" ht="21" customHeight="1">
@@ -35889,7 +36137,11 @@
       <c r="G1412" s="24" t="str">
         <v>火箭</v>
       </c>
-      <c r="H1412" s="25" t="str"/>
+      <c r="H1412" t="inlineStr" s="25">
+        <is>
+          <t>Пылающая стрела</t>
+        </is>
+      </c>
       <c r="I1412" s="143" t="str"/>
     </row>
     <row r="1413" ht="21" customHeight="1">
@@ -35914,7 +36166,11 @@
       <c r="G1413" s="24" t="str">
         <v>毒箭</v>
       </c>
-      <c r="H1413" s="25" t="str"/>
+      <c r="H1413" t="inlineStr" s="25">
+        <is>
+          <t>Ядовитая стрела</t>
+        </is>
+      </c>
       <c r="I1413" s="143" t="str"/>
     </row>
     <row r="1414" ht="21" customHeight="1">
@@ -35939,7 +36195,11 @@
       <c r="G1414" s="24" t="str">
         <v>箭雨</v>
       </c>
-      <c r="H1414" s="25" t="str"/>
+      <c r="H1414" t="inlineStr" s="25">
+        <is>
+          <t>Дождь стрел</t>
+        </is>
+      </c>
       <c r="I1414" s="143" t="str"/>
     </row>
     <row r="1415" ht="21" customHeight="1">
@@ -35964,7 +36224,11 @@
       <c r="G1415" s="24" t="str">
         <v>箭之風暴</v>
       </c>
-      <c r="H1415" s="25" t="str"/>
+      <c r="H1415" t="inlineStr" s="25">
+        <is>
+          <t>Ураган</t>
+        </is>
+      </c>
       <c r="I1415" s="143" t="str"/>
     </row>
     <row r="1416" ht="21" customHeight="1">
@@ -35989,7 +36253,11 @@
       <c r="G1416" s="24" t="str">
         <v>多重箭</v>
       </c>
-      <c r="H1416" s="25" t="str"/>
+      <c r="H1416" t="inlineStr" s="25">
+        <is>
+          <t>Пятикратный выстрел</t>
+        </is>
+      </c>
       <c r="I1416" s="143" t="str"/>
     </row>
     <row r="1417" ht="21" customHeight="1">
@@ -36014,7 +36282,11 @@
       <c r="G1417" s="24" t="str">
         <v>擊退箭</v>
       </c>
-      <c r="H1417" s="25" t="str"/>
+      <c r="H1417" t="inlineStr" s="25">
+        <is>
+          <t>Внезапный выстрел</t>
+        </is>
+      </c>
       <c r="I1417" s="143" t="str"/>
     </row>
     <row r="1418" ht="21" customHeight="1">
@@ -36039,7 +36311,11 @@
       <c r="G1418" s="24" t="str">
         <v>沉默之箭</v>
       </c>
-      <c r="H1418" s="25" t="str"/>
+      <c r="H1418" t="inlineStr" s="25">
+        <is>
+          <t>Печать тишины</t>
+        </is>
+      </c>
       <c r="I1418" s="143" t="str"/>
     </row>
     <row r="1419" ht="21" customHeight="1">
@@ -36064,7 +36340,11 @@
       <c r="G1419" s="24" t="str">
         <v>影襲</v>
       </c>
-      <c r="H1419" s="25" t="str"/>
+      <c r="H1419" t="inlineStr" s="25">
+        <is>
+          <t>Неясная тень</t>
+        </is>
+      </c>
       <c r="I1419" s="143" t="str"/>
     </row>
     <row r="1420" ht="21" customHeight="1">
@@ -36089,7 +36369,11 @@
       <c r="G1420" s="24" t="str">
         <v>毒藥製造</v>
       </c>
-      <c r="H1420" s="25" t="str"/>
+      <c r="H1420" t="inlineStr" s="25">
+        <is>
+          <t>Создание яда</t>
+        </is>
+      </c>
       <c r="I1420" s="143" t="str"/>
     </row>
     <row r="1421" ht="21" customHeight="1">
@@ -36114,7 +36398,11 @@
       <c r="G1421" s="24" t="str">
         <v>塗毒</v>
       </c>
-      <c r="H1421" s="25" t="str"/>
+      <c r="H1421" t="inlineStr" s="25">
+        <is>
+          <t>Яд</t>
+        </is>
+      </c>
       <c r="I1421" s="143" t="str"/>
     </row>
     <row r="1422" ht="21" customHeight="1">
@@ -36139,7 +36427,11 @@
       <c r="G1422" s="24" t="str">
         <v>調製解毒劑</v>
       </c>
-      <c r="H1422" s="25" t="str"/>
+      <c r="H1422" t="inlineStr" s="25">
+        <is>
+          <t>Создание противоядия</t>
+        </is>
+      </c>
       <c r="I1422" s="143" t="str"/>
     </row>
     <row r="1423" ht="21" customHeight="1">
@@ -36164,7 +36456,11 @@
       <c r="G1423" s="24" t="str">
         <v>神秘藥</v>
       </c>
-      <c r="H1423" s="25" t="str"/>
+      <c r="H1423" t="inlineStr" s="25">
+        <is>
+          <t>Составление зелий</t>
+        </is>
+      </c>
       <c r="I1423" s="143" t="str"/>
     </row>
     <row r="1424" ht="21" customHeight="1">
@@ -36189,7 +36485,11 @@
       <c r="G1424" s="24" t="str">
         <v>惡魔語言</v>
       </c>
-      <c r="H1424" s="25" t="str"/>
+      <c r="H1424" t="inlineStr" s="25">
+        <is>
+          <t>Скороговорка</t>
+        </is>
+      </c>
       <c r="I1424" s="143" t="str"/>
     </row>
     <row r="1425" ht="21" customHeight="1">
@@ -36214,7 +36514,11 @@
       <c r="G1425" s="24" t="str">
         <v>惡意毒素</v>
       </c>
-      <c r="H1425" s="25" t="str"/>
+      <c r="H1425" t="inlineStr" s="25">
+        <is>
+          <t>Усиление яда</t>
+        </is>
+      </c>
       <c r="I1425" s="143" t="str"/>
     </row>
     <row r="1426" ht="21" customHeight="1">
@@ -36239,7 +36543,11 @@
       <c r="G1426" s="24" t="str">
         <v>洞察</v>
       </c>
-      <c r="H1426" s="25" t="str"/>
+      <c r="H1426" t="inlineStr" s="25">
+        <is>
+          <t>Соколиный глаз</t>
+        </is>
+      </c>
       <c r="I1426" s="143" t="str"/>
     </row>
     <row r="1427" ht="21" customHeight="1">
@@ -36264,7 +36572,11 @@
       <c r="G1427" s="24" t="str">
         <v>隱身</v>
       </c>
-      <c r="H1427" s="25" t="str"/>
+      <c r="H1427" t="inlineStr" s="25">
+        <is>
+          <t>Невидимость</t>
+        </is>
+      </c>
       <c r="I1427" s="143" t="str"/>
     </row>
     <row r="1428" ht="21" customHeight="1">
@@ -36289,7 +36601,11 @@
       <c r="G1428" s="24" t="str">
         <v>隱蔽</v>
       </c>
-      <c r="H1428" s="25" t="str"/>
+      <c r="H1428" t="inlineStr" s="25">
+        <is>
+          <t>Маскировка</t>
+        </is>
+      </c>
       <c r="I1428" s="143" t="str"/>
     </row>
     <row r="1429" ht="21" customHeight="1">
@@ -36314,7 +36630,11 @@
       <c r="G1429" s="24" t="str">
         <v>隱身專精</v>
       </c>
-      <c r="H1429" s="25" t="str"/>
+      <c r="H1429" t="inlineStr" s="25">
+        <is>
+          <t>Легкий шаг</t>
+        </is>
+      </c>
       <c r="I1429" s="143" t="str"/>
     </row>
     <row r="1430" ht="21" customHeight="1">
@@ -36339,7 +36659,11 @@
       <c r="G1430" s="24" t="str">
         <v>武器大師</v>
       </c>
-      <c r="H1430" s="25" t="str"/>
+      <c r="H1430" t="inlineStr" s="25">
+        <is>
+          <t>Волна</t>
+        </is>
+      </c>
       <c r="I1430" s="143" t="str"/>
     </row>
     <row r="1431" ht="21" customHeight="1">
@@ -36364,7 +36688,11 @@
       <c r="G1431" s="24" t="str">
         <v>背刺</v>
       </c>
-      <c r="H1431" s="25" t="str"/>
+      <c r="H1431" t="inlineStr" s="25">
+        <is>
+          <t>Удар в спину</t>
+        </is>
+      </c>
       <c r="I1431" s="143" t="str"/>
     </row>
     <row r="1432" ht="21" customHeight="1">
@@ -36389,7 +36717,11 @@
       <c r="G1432" s="24" t="str">
         <v>致命投擲</v>
       </c>
-      <c r="H1432" s="25" t="str"/>
+      <c r="H1432" t="inlineStr" s="25">
+        <is>
+          <t>Метание кинжала</t>
+        </is>
+      </c>
       <c r="I1432" s="143" t="str"/>
     </row>
     <row r="1433" ht="21" customHeight="1">
@@ -36414,7 +36746,11 @@
       <c r="G1433" s="24" t="str">
         <v>鮮血之怒</v>
       </c>
-      <c r="H1433" s="25" t="str"/>
+      <c r="H1433" t="inlineStr" s="25">
+        <is>
+          <t>Беспощадная атака</t>
+        </is>
+      </c>
       <c r="I1433" s="143" t="str"/>
     </row>
     <row r="1434" ht="21" customHeight="1">
@@ -36439,7 +36775,11 @@
       <c r="G1434" s="24" t="str">
         <v>隱密刺殺</v>
       </c>
-      <c r="H1434" s="25" t="str"/>
+      <c r="H1434" t="inlineStr" s="25">
+        <is>
+          <t>Внезапная атака</t>
+        </is>
+      </c>
       <c r="I1434" s="143" t="str"/>
     </row>
     <row r="1435" ht="21" customHeight="1">
@@ -36464,7 +36804,11 @@
       <c r="G1435" s="24" t="str">
         <v>弱點攻擊</v>
       </c>
-      <c r="H1435" s="25" t="str"/>
+      <c r="H1435" t="inlineStr" s="25">
+        <is>
+          <t>Точный укол</t>
+        </is>
+      </c>
       <c r="I1435" s="143" t="str"/>
     </row>
     <row r="1436" ht="21" customHeight="1">
@@ -36489,7 +36833,11 @@
       <c r="G1436" s="24" t="str">
         <v>極惡歸返</v>
       </c>
-      <c r="H1436" s="25" t="str"/>
+      <c r="H1436" t="inlineStr" s="25">
+        <is>
+          <t>Стремительная смерть</t>
+        </is>
+      </c>
       <c r="I1436" s="143" t="str"/>
     </row>
     <row r="1437" ht="21" customHeight="1">
@@ -36514,7 +36862,11 @@
       <c r="G1437" s="24" t="str">
         <v>陷阱潰散</v>
       </c>
-      <c r="H1437" s="25" t="str"/>
+      <c r="H1437" t="inlineStr" s="25">
+        <is>
+          <t>Обезвреживание ловушек</t>
+        </is>
+      </c>
       <c r="I1437" s="143" t="str"/>
     </row>
     <row r="1438" ht="21" customHeight="1">
@@ -36539,7 +36891,11 @@
       <c r="G1438" s="24" t="str">
         <v>致殘陷阱</v>
       </c>
-      <c r="H1438" s="25" t="str"/>
+      <c r="H1438" t="inlineStr" s="25">
+        <is>
+          <t>Капкан</t>
+        </is>
+      </c>
       <c r="I1438" s="143" t="str"/>
     </row>
     <row r="1439" ht="21" customHeight="1">
@@ -36564,7 +36920,11 @@
       <c r="G1439" s="24" t="str">
         <v>爆破陷阱</v>
       </c>
-      <c r="H1439" s="25" t="str"/>
+      <c r="H1439" t="inlineStr" s="25">
+        <is>
+          <t>Взрывающаяся ловушка</t>
+        </is>
+      </c>
       <c r="I1439" s="143" t="str"/>
     </row>
     <row r="1440" ht="21" customHeight="1">
@@ -36589,7 +36949,11 @@
       <c r="G1440" s="24" t="str">
         <v>連續爆破</v>
       </c>
-      <c r="H1440" s="25" t="str"/>
+      <c r="H1440" t="inlineStr" s="25">
+        <is>
+          <t>Ползучая ловушка</t>
+        </is>
+      </c>
       <c r="I1440" s="143" t="str"/>
     </row>
     <row r="1441" ht="21" customHeight="1">
@@ -36614,7 +36978,11 @@
       <c r="G1441" s="24" t="str">
         <v>平靜氣氛</v>
       </c>
-      <c r="H1441" s="25" t="str"/>
+      <c r="H1441" t="inlineStr" s="25">
+        <is>
+          <t>Глаз урагана</t>
+        </is>
+      </c>
       <c r="I1441" s="143" t="str"/>
     </row>
     <row r="1442" ht="21" customHeight="1">
@@ -36639,7 +37007,11 @@
       <c r="G1442" s="24" t="str">
         <v>陷馬坑</v>
       </c>
-      <c r="H1442" s="25" t="str"/>
+      <c r="H1442" t="inlineStr" s="25">
+        <is>
+          <t>Вольер</t>
+        </is>
+      </c>
       <c r="I1442" s="143" t="str"/>
     </row>
     <row r="1443" ht="21" customHeight="1">
@@ -36664,7 +37036,11 @@
       <c r="G1443" s="24" t="str">
         <v>精神干擾</v>
       </c>
-      <c r="H1443" s="25" t="str"/>
+      <c r="H1443" t="inlineStr" s="25">
+        <is>
+          <t>Растворение сознания</t>
+        </is>
+      </c>
       <c r="I1443" s="143" t="str"/>
     </row>
     <row r="1444" ht="21" customHeight="1">
@@ -36689,7 +37065,11 @@
       <c r="G1444" s="24" t="str">
         <v>疾走</v>
       </c>
-      <c r="H1444" s="25" t="str"/>
+      <c r="H1444" t="inlineStr" s="25">
+        <is>
+          <t>Легкость</t>
+        </is>
+      </c>
       <c r="I1444" s="143" t="str"/>
     </row>
     <row r="1445" ht="21" customHeight="1">
@@ -36714,7 +37094,11 @@
       <c r="G1445" s="24" t="str">
         <v>遁逃</v>
       </c>
-      <c r="H1445" s="25" t="str"/>
+      <c r="H1445" t="inlineStr" s="25">
+        <is>
+          <t>Быстрый отход</t>
+        </is>
+      </c>
       <c r="I1445" s="143" t="str"/>
     </row>
     <row r="1446" ht="21" customHeight="1">
@@ -36739,7 +37123,11 @@
       <c r="G1446" s="24" t="str">
         <v>突進</v>
       </c>
-      <c r="H1446" s="25" t="str"/>
+      <c r="H1446" t="inlineStr" s="25">
+        <is>
+          <t>Порыв</t>
+        </is>
+      </c>
       <c r="I1446" s="143" t="str"/>
     </row>
     <row r="1447" ht="21" customHeight="1">
@@ -36764,7 +37152,11 @@
       <c r="G1447" s="24" t="str">
         <v>快速閃避</v>
       </c>
-      <c r="H1447" s="25" t="str"/>
+      <c r="H1447" t="inlineStr" s="25">
+        <is>
+          <t>Быстрое уклонение</t>
+        </is>
+      </c>
       <c r="I1447" s="143" t="str"/>
     </row>
     <row r="1448" ht="21" customHeight="1">
@@ -36789,7 +37181,11 @@
       <c r="G1448" s="24" t="str">
         <v>擾亂之觸</v>
       </c>
-      <c r="H1448" s="25" t="str"/>
+      <c r="H1448" t="inlineStr" s="25">
+        <is>
+          <t>Путающая рука</t>
+        </is>
+      </c>
       <c r="I1448" s="143" t="str"/>
     </row>
     <row r="1449" ht="21" customHeight="1">
@@ -36814,7 +37210,11 @@
       <c r="G1449" s="24" t="str">
         <v>炙熱守護</v>
       </c>
-      <c r="H1449" s="25" t="str"/>
+      <c r="H1449" t="inlineStr" s="25">
+        <is>
+          <t>Устойчивость</t>
+        </is>
+      </c>
       <c r="I1449" s="143" t="str"/>
     </row>
     <row r="1450" ht="21" customHeight="1">
@@ -36839,7 +37239,11 @@
       <c r="G1450" s="24" t="str">
         <v>閃避</v>
       </c>
-      <c r="H1450" s="25" t="str"/>
+      <c r="H1450" t="inlineStr" s="25">
+        <is>
+          <t>Ускользание</t>
+        </is>
+      </c>
       <c r="I1450" s="143" t="str"/>
     </row>
     <row r="1451" ht="21" customHeight="1">
@@ -36864,7 +37268,11 @@
       <c r="G1451" s="24" t="str">
         <v>堅守信仰</v>
       </c>
-      <c r="H1451" s="25" t="str"/>
+      <c r="H1451" t="inlineStr" s="25">
+        <is>
+          <t>Ограждение</t>
+        </is>
+      </c>
       <c r="I1451" s="143" t="str"/>
     </row>
     <row r="1452" ht="21" customHeight="1">
@@ -36889,7 +37297,11 @@
       <c r="G1452" s="24" t="str">
         <v>疾速賦予</v>
       </c>
-      <c r="H1452" s="25" t="str"/>
+      <c r="H1452" t="inlineStr" s="25">
+        <is>
+          <t>Вольный ветер</t>
+        </is>
+      </c>
       <c r="I1452" s="143" t="str"/>
     </row>
     <row r="1453" ht="21" customHeight="1">
@@ -36914,7 +37326,11 @@
       <c r="G1453" s="24" t="str">
         <v>靜心咒</v>
       </c>
-      <c r="H1453" s="25" t="str"/>
+      <c r="H1453" t="inlineStr" s="25">
+        <is>
+          <t>Медитация</t>
+        </is>
+      </c>
       <c r="I1453" s="143" t="str"/>
     </row>
     <row r="1454" ht="21" customHeight="1">
@@ -36939,7 +37355,11 @@
       <c r="G1454" s="24" t="str">
         <v>冥想</v>
       </c>
-      <c r="H1454" s="25" t="str"/>
+      <c r="H1454" t="inlineStr" s="25">
+        <is>
+          <t>Вдохновение</t>
+        </is>
+      </c>
       <c r="I1454" s="143" t="str"/>
     </row>
     <row r="1455" ht="21" customHeight="1">
@@ -36964,7 +37384,11 @@
       <c r="G1455" s="24" t="str">
         <v>虔誠非凡</v>
       </c>
-      <c r="H1455" s="25" t="str"/>
+      <c r="H1455" t="inlineStr" s="25">
+        <is>
+          <t>Святость</t>
+        </is>
+      </c>
       <c r="I1455" s="143" t="str"/>
     </row>
     <row r="1456" ht="21" customHeight="1">
@@ -37039,7 +37463,11 @@
       <c r="G1458" s="24" t="str">
         <v>治療術</v>
       </c>
-      <c r="H1458" s="25" t="str"/>
+      <c r="H1458" t="inlineStr" s="25">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
       <c r="I1458" s="143" t="str"/>
     </row>
     <row r="1459" ht="21" customHeight="1">
@@ -37064,7 +37492,11 @@
       <c r="G1459" s="24" t="str">
         <v>復活術</v>
       </c>
-      <c r="H1459" s="25" t="str"/>
+      <c r="H1459" t="inlineStr" s="25">
+        <is>
+          <t>Воскрешение</t>
+        </is>
+      </c>
       <c r="I1459" s="143" t="str"/>
     </row>
     <row r="1460" ht="21" customHeight="1">
@@ -37089,7 +37521,11 @@
       <c r="G1460" s="24" t="str">
         <v>聖堂之歌</v>
       </c>
-      <c r="H1460" s="25" t="str"/>
+      <c r="H1460" t="inlineStr" s="25">
+        <is>
+          <t>Храм</t>
+        </is>
+      </c>
       <c r="I1460" s="143" t="str"/>
     </row>
     <row r="1461" ht="21" customHeight="1">
@@ -37114,7 +37550,11 @@
       <c r="G1461" s="24" t="str">
         <v>聖母的祝福</v>
       </c>
-      <c r="H1461" s="25" t="str"/>
+      <c r="H1461" t="inlineStr" s="25">
+        <is>
+          <t>Великодушие</t>
+        </is>
+      </c>
       <c r="I1461" s="143" t="str"/>
     </row>
     <row r="1462" ht="21" customHeight="1">
@@ -37139,7 +37579,11 @@
       <c r="G1462" s="24" t="str">
         <v>聖母之心</v>
       </c>
-      <c r="H1462" s="25" t="str"/>
+      <c r="H1462" t="inlineStr" s="25">
+        <is>
+          <t>Распространение</t>
+        </is>
+      </c>
       <c r="I1462" s="143" t="str"/>
     </row>
     <row r="1463" ht="21" customHeight="1">
@@ -37164,7 +37608,11 @@
       <c r="G1463" s="24" t="str">
         <v>快速治癒</v>
       </c>
-      <c r="H1463" s="25" t="str"/>
+      <c r="H1463" t="inlineStr" s="25">
+        <is>
+          <t>Первая помощь</t>
+        </is>
+      </c>
       <c r="I1463" s="143" t="str"/>
     </row>
     <row r="1464" ht="21" customHeight="1">
@@ -37189,7 +37637,11 @@
       <c r="G1464" s="24" t="str">
         <v>解毒術</v>
       </c>
-      <c r="H1464" s="25" t="str"/>
+      <c r="H1464" t="inlineStr" s="25">
+        <is>
+          <t>Лечение отравления</t>
+        </is>
+      </c>
       <c r="I1464" s="143" t="str"/>
     </row>
     <row r="1465" ht="21" customHeight="1">
@@ -37214,7 +37666,11 @@
       <c r="G1465" s="24" t="str">
         <v>恢復術</v>
       </c>
-      <c r="H1465" s="25" t="str"/>
+      <c r="H1465" t="inlineStr" s="25">
+        <is>
+          <t>Регенерация</t>
+        </is>
+      </c>
       <c r="I1465" s="143" t="str"/>
     </row>
     <row r="1466" ht="21" customHeight="1">
@@ -37239,7 +37695,11 @@
       <c r="G1466" s="24" t="str">
         <v>神聖耳語</v>
       </c>
-      <c r="H1466" s="25" t="str"/>
+      <c r="H1466" t="inlineStr" s="25">
+        <is>
+          <t>Пробуждение</t>
+        </is>
+      </c>
       <c r="I1466" s="143" t="str"/>
     </row>
     <row r="1467" ht="21" customHeight="1">
@@ -37264,7 +37724,11 @@
       <c r="G1467" s="24" t="str">
         <v>自然恢復</v>
       </c>
-      <c r="H1467" s="25" t="str"/>
+      <c r="H1467" t="inlineStr" s="25">
+        <is>
+          <t>Восстановление</t>
+        </is>
+      </c>
       <c r="I1467" s="143" t="str"/>
     </row>
     <row r="1468" ht="21" customHeight="1">
@@ -37289,7 +37753,11 @@
       <c r="G1468" s="24" t="str">
         <v>治療之風</v>
       </c>
-      <c r="H1468" s="25" t="str"/>
+      <c r="H1468" t="inlineStr" s="25">
+        <is>
+          <t>Массовое исцеление</t>
+        </is>
+      </c>
       <c r="I1468" s="143" t="str"/>
     </row>
     <row r="1469" ht="21" customHeight="1">
@@ -37314,7 +37782,11 @@
       <c r="G1469" s="24" t="str">
         <v>天使障壁</v>
       </c>
-      <c r="H1469" s="25" t="str"/>
+      <c r="H1469" t="inlineStr" s="25">
+        <is>
+          <t>Полное исцеление</t>
+        </is>
+      </c>
       <c r="I1469" s="143" t="str"/>
     </row>
     <row r="1470" ht="21" customHeight="1">
@@ -37339,7 +37811,11 @@
       <c r="G1470" s="24" t="str">
         <v>精靈的擁抱</v>
       </c>
-      <c r="H1470" s="25" t="str"/>
+      <c r="H1470" t="inlineStr" s="25">
+        <is>
+          <t>Благословенный покой</t>
+        </is>
+      </c>
       <c r="I1470" s="143" t="str"/>
     </row>
     <row r="1471" ht="21" customHeight="1">
@@ -37364,7 +37840,11 @@
       <c r="G1471" s="24" t="str">
         <v>自然的祝福</v>
       </c>
-      <c r="H1471" s="25" t="str"/>
+      <c r="H1471" t="inlineStr" s="25">
+        <is>
+          <t>Знак жизни</t>
+        </is>
+      </c>
       <c r="I1471" s="143" t="str"/>
     </row>
     <row r="1472" ht="21" customHeight="1">
@@ -37389,7 +37869,11 @@
       <c r="G1472" s="24" t="str">
         <v>鋼力招來</v>
       </c>
-      <c r="H1472" s="25" t="str"/>
+      <c r="H1472" t="inlineStr" s="25">
+        <is>
+          <t>Чары усиления</t>
+        </is>
+      </c>
       <c r="I1472" s="143" t="str"/>
     </row>
     <row r="1473" ht="21" customHeight="1">
@@ -37414,7 +37898,11 @@
       <c r="G1473" s="24" t="str">
         <v>風之祝福</v>
       </c>
-      <c r="H1473" s="25" t="str"/>
+      <c r="H1473" t="inlineStr" s="25">
+        <is>
+          <t>Знак атаки</t>
+        </is>
+      </c>
       <c r="I1473" s="143" t="str"/>
     </row>
     <row r="1474" ht="21" customHeight="1">
@@ -37439,7 +37927,11 @@
       <c r="G1474" s="24" t="str">
         <v>地之祝福</v>
       </c>
-      <c r="H1474" s="25" t="str"/>
+      <c r="H1474" t="inlineStr" s="25">
+        <is>
+          <t>Знак защиты</t>
+        </is>
+      </c>
       <c r="I1474" s="143" t="str"/>
     </row>
     <row r="1475" ht="21" customHeight="1">
@@ -37464,7 +37956,11 @@
       <c r="G1475" s="24" t="str">
         <v>殘廢咒</v>
       </c>
-      <c r="H1475" s="25" t="str"/>
+      <c r="H1475" t="inlineStr" s="25">
+        <is>
+          <t>Задержка</t>
+        </is>
+      </c>
       <c r="I1475" s="143" t="str"/>
     </row>
     <row r="1476" ht="21" customHeight="1">
@@ -37489,7 +37985,11 @@
       <c r="G1476" s="24" t="str">
         <v>聖母之守護</v>
       </c>
-      <c r="H1476" s="25" t="str"/>
+      <c r="H1476" t="inlineStr" s="25">
+        <is>
+          <t>Божественная защита</t>
+        </is>
+      </c>
       <c r="I1476" s="143" t="str"/>
     </row>
     <row r="1477" ht="21" customHeight="1">
@@ -37514,7 +38014,11 @@
       <c r="G1477" s="24" t="str">
         <v>聖水的祈求</v>
       </c>
-      <c r="H1477" s="25" t="str"/>
+      <c r="H1477" t="inlineStr" s="25">
+        <is>
+          <t>Освящение воды</t>
+        </is>
+      </c>
       <c r="I1477" s="143" t="str"/>
     </row>
     <row r="1478" ht="21" customHeight="1">
@@ -37539,7 +38043,11 @@
       <c r="G1478" s="24" t="str">
         <v>祝福聖歌</v>
       </c>
-      <c r="H1478" s="25" t="str"/>
+      <c r="H1478" t="inlineStr" s="25">
+        <is>
+          <t>Воодушевление</t>
+        </is>
+      </c>
       <c r="I1478" s="143" t="str"/>
     </row>
     <row r="1479" ht="21" customHeight="1">
@@ -37564,7 +38072,11 @@
       <c r="G1479" s="24" t="str">
         <v>戰神祝福</v>
       </c>
-      <c r="H1479" s="25" t="str"/>
+      <c r="H1479" t="inlineStr" s="25">
+        <is>
+          <t>Ободрение</t>
+        </is>
+      </c>
       <c r="I1479" s="143" t="str"/>
     </row>
     <row r="1480" ht="21" customHeight="1">
@@ -37589,7 +38101,11 @@
       <c r="G1480" s="24" t="str">
         <v>心靈啟動</v>
       </c>
-      <c r="H1480" s="25" t="str"/>
+      <c r="H1480" t="inlineStr" s="25">
+        <is>
+          <t>Природное восстановление</t>
+        </is>
+      </c>
       <c r="I1480" s="143" t="str"/>
     </row>
     <row r="1481" ht="21" customHeight="1">
@@ -37614,7 +38130,11 @@
       <c r="G1481" s="24" t="str">
         <v>閃避結界</v>
       </c>
-      <c r="H1481" s="25" t="str"/>
+      <c r="H1481" t="inlineStr" s="25">
+        <is>
+          <t>Помощь ветра</t>
+        </is>
+      </c>
       <c r="I1481" s="143" t="str"/>
     </row>
     <row r="1482" ht="21" customHeight="1">
@@ -37639,7 +38159,11 @@
       <c r="G1482" s="24" t="str">
         <v>淨化屏障</v>
       </c>
-      <c r="H1482" s="25" t="str"/>
+      <c r="H1482" t="inlineStr" s="25">
+        <is>
+          <t>Врачевание</t>
+        </is>
+      </c>
       <c r="I1482" s="143" t="str"/>
     </row>
     <row r="1483" ht="21" customHeight="1">
@@ -37664,7 +38188,11 @@
       <c r="G1483" s="24" t="str">
         <v>心靈轉換</v>
       </c>
-      <c r="H1483" s="25" t="str"/>
+      <c r="H1483" t="inlineStr" s="25">
+        <is>
+          <t>Обмен маной</t>
+        </is>
+      </c>
       <c r="I1483" s="143" t="str"/>
     </row>
     <row r="1484" ht="21" customHeight="1">
@@ -37689,7 +38217,11 @@
       <c r="G1484" s="24" t="str">
         <v>身心轉換</v>
       </c>
-      <c r="H1484" s="25" t="str"/>
+      <c r="H1484" t="inlineStr" s="25">
+        <is>
+          <t>Обмен душами</t>
+        </is>
+      </c>
       <c r="I1484" s="143" t="str"/>
     </row>
     <row r="1485" ht="21" customHeight="1">
@@ -37714,7 +38246,11 @@
       <c r="G1485" s="24" t="str">
         <v>淨化</v>
       </c>
-      <c r="H1485" s="25" t="str"/>
+      <c r="H1485" t="inlineStr" s="25">
+        <is>
+          <t>Очищение</t>
+        </is>
+      </c>
       <c r="I1485" s="143" t="str"/>
     </row>
     <row r="1486" ht="21" customHeight="1">
@@ -37739,7 +38275,11 @@
       <c r="G1486" s="24" t="str">
         <v>光之箭</v>
       </c>
-      <c r="H1486" s="25" t="str"/>
+      <c r="H1486" t="inlineStr" s="25">
+        <is>
+          <t>Святая стрела</t>
+        </is>
+      </c>
       <c r="I1486" s="143" t="str"/>
     </row>
     <row r="1487" ht="21" customHeight="1">
@@ -37764,7 +38304,11 @@
       <c r="G1487" s="24" t="str">
         <v>元素屏障</v>
       </c>
-      <c r="H1487" s="25" t="str"/>
+      <c r="H1487" t="inlineStr" s="25">
+        <is>
+          <t>Поглощение стихий</t>
+        </is>
+      </c>
       <c r="I1487" s="143" t="str"/>
     </row>
     <row r="1488" ht="21" customHeight="1">
@@ -37789,7 +38333,11 @@
       <c r="G1488" s="24" t="str">
         <v>虔誠賜予</v>
       </c>
-      <c r="H1488" s="25" t="str"/>
+      <c r="H1488" t="inlineStr" s="25">
+        <is>
+          <t>Священное оружие</t>
+        </is>
+      </c>
       <c r="I1488" s="143" t="str"/>
     </row>
     <row r="1489" ht="21" customHeight="1">
@@ -37814,7 +38362,11 @@
       <c r="G1489" s="24" t="str">
         <v>淨身術</v>
       </c>
-      <c r="H1489" s="25" t="str"/>
+      <c r="H1489" t="inlineStr" s="25">
+        <is>
+          <t>Освобождение</t>
+        </is>
+      </c>
       <c r="I1489" s="143" t="str"/>
     </row>
     <row r="1490" ht="21" customHeight="1">
@@ -37839,7 +38391,11 @@
       <c r="G1490" s="24" t="str">
         <v>天威降臨</v>
       </c>
-      <c r="H1490" s="25" t="str"/>
+      <c r="H1490" t="inlineStr" s="25">
+        <is>
+          <t>Круг света</t>
+        </is>
+      </c>
       <c r="I1490" s="143" t="str"/>
     </row>
     <row r="1491" ht="21" customHeight="1">
@@ -37864,7 +38420,11 @@
       <c r="G1491" s="24" t="str">
         <v>黑暗回歸</v>
       </c>
-      <c r="H1491" s="25" t="str"/>
+      <c r="H1491" t="inlineStr" s="25">
+        <is>
+          <t>Изгнание</t>
+        </is>
+      </c>
       <c r="I1491" s="143" t="str"/>
     </row>
     <row r="1492" ht="21" customHeight="1">
@@ -37889,7 +38449,11 @@
       <c r="G1492" s="24" t="str">
         <v>心靈連結</v>
       </c>
-      <c r="H1492" s="25" t="str"/>
+      <c r="H1492" t="inlineStr" s="25">
+        <is>
+          <t>Преданность</t>
+        </is>
+      </c>
       <c r="I1492" s="143" t="str"/>
     </row>
     <row r="1493" ht="21" customHeight="1">
@@ -37914,7 +38478,11 @@
       <c r="G1493" s="24" t="str">
         <v>光之赦令</v>
       </c>
-      <c r="H1493" s="25" t="str"/>
+      <c r="H1493" t="inlineStr" s="25">
+        <is>
+          <t>Затишье</t>
+        </is>
+      </c>
       <c r="I1493" s="143" t="str"/>
     </row>
     <row r="1494" ht="21" customHeight="1">
@@ -37939,7 +38507,11 @@
       <c r="G1494" s="24" t="str">
         <v>詩人之歌</v>
       </c>
-      <c r="H1494" s="25" t="str"/>
+      <c r="H1494" t="inlineStr" s="25">
+        <is>
+          <t>Песнь поэта</t>
+        </is>
+      </c>
       <c r="I1494" s="143" t="str"/>
     </row>
     <row r="1495" ht="21" customHeight="1">
@@ -37964,7 +38536,11 @@
       <c r="G1495" s="24" t="str">
         <v>聖歌傳承</v>
       </c>
-      <c r="H1495" s="25" t="str"/>
+      <c r="H1495" t="inlineStr" s="25">
+        <is>
+          <t>Песнь света</t>
+        </is>
+      </c>
       <c r="I1495" s="143" t="str"/>
     </row>
     <row r="1496" ht="21" customHeight="1">
@@ -37989,7 +38565,11 @@
       <c r="G1496" s="24" t="str">
         <v>和平之歌</v>
       </c>
-      <c r="H1496" s="25" t="str"/>
+      <c r="H1496" t="inlineStr" s="25">
+        <is>
+          <t>Песнь мира</t>
+        </is>
+      </c>
       <c r="I1496" s="143" t="str"/>
     </row>
     <row r="1497" ht="21" customHeight="1">
@@ -38014,7 +38594,11 @@
       <c r="G1497" s="24" t="str">
         <v>魔力之歌</v>
       </c>
-      <c r="H1497" s="25" t="str"/>
+      <c r="H1497" t="inlineStr" s="25">
+        <is>
+          <t>Песнь чар</t>
+        </is>
+      </c>
       <c r="I1497" s="143" t="str"/>
     </row>
     <row r="1498" ht="21" customHeight="1">
@@ -38039,7 +38623,11 @@
       <c r="G1498" s="24" t="str">
         <v>魔力上升</v>
       </c>
-      <c r="H1498" s="25" t="str"/>
+      <c r="H1498" t="inlineStr" s="25">
+        <is>
+          <t>Магические знания</t>
+        </is>
+      </c>
       <c r="I1498" s="143" t="str"/>
     </row>
     <row r="1499" ht="21" customHeight="1">
@@ -38064,7 +38652,11 @@
       <c r="G1499" s="24" t="str">
         <v>黑暗結合</v>
       </c>
-      <c r="H1499" s="25" t="str"/>
+      <c r="H1499" t="inlineStr" s="25">
+        <is>
+          <t>Темная защита</t>
+        </is>
+      </c>
       <c r="I1499" s="143" t="str"/>
     </row>
     <row r="1500" ht="21" customHeight="1">
@@ -38089,7 +38681,11 @@
       <c r="G1500" s="24" t="str">
         <v>火之矢</v>
       </c>
-      <c r="H1500" s="25" t="str"/>
+      <c r="H1500" t="inlineStr" s="25">
+        <is>
+          <t>Огненная стрела</t>
+        </is>
+      </c>
       <c r="I1500" s="143" t="str"/>
     </row>
     <row r="1501" ht="21" customHeight="1">
@@ -38114,7 +38710,11 @@
       <c r="G1501" s="24" t="str">
         <v>閃電</v>
       </c>
-      <c r="H1501" s="25" t="str"/>
+      <c r="H1501" t="inlineStr" s="25">
+        <is>
+          <t>Удар молнии</t>
+        </is>
+      </c>
       <c r="I1501" s="143" t="str"/>
     </row>
     <row r="1502" ht="21" customHeight="1">
@@ -38139,7 +38739,11 @@
       <c r="G1502" s="24" t="str">
         <v>巨雷破</v>
       </c>
-      <c r="H1502" s="25" t="str"/>
+      <c r="H1502" t="inlineStr" s="25">
+        <is>
+          <t>Громовой разряд</t>
+        </is>
+      </c>
       <c r="I1502" s="143" t="str"/>
     </row>
     <row r="1503" ht="21" customHeight="1">
@@ -38164,7 +38768,11 @@
       <c r="G1503" s="24" t="str">
         <v>精神修養</v>
       </c>
-      <c r="H1503" s="25" t="str"/>
+      <c r="H1503" t="inlineStr" s="25">
+        <is>
+          <t>Сосредоточенность</t>
+        </is>
+      </c>
       <c r="I1503" s="143" t="str"/>
     </row>
     <row r="1504" ht="21" customHeight="1">
@@ -38189,7 +38797,11 @@
       <c r="G1504" s="24" t="str">
         <v>冰之石</v>
       </c>
-      <c r="H1504" s="25" t="str"/>
+      <c r="H1504" t="inlineStr" s="25">
+        <is>
+          <t>Ледяные осколки</t>
+        </is>
+      </c>
       <c r="I1504" s="143" t="str"/>
     </row>
     <row r="1505" ht="21" customHeight="1">
@@ -38214,7 +38826,11 @@
       <c r="G1505" s="24" t="str">
         <v>雷鳥球</v>
       </c>
-      <c r="H1505" s="25" t="str"/>
+      <c r="H1505" t="inlineStr" s="25">
+        <is>
+          <t>Шаровая молния</t>
+        </is>
+      </c>
       <c r="I1505" s="143" t="str"/>
     </row>
     <row r="1506" ht="21" customHeight="1">
@@ -38239,7 +38855,11 @@
       <c r="G1506" s="24" t="str">
         <v>冰之矛</v>
       </c>
-      <c r="H1506" s="25" t="str"/>
+      <c r="H1506" t="inlineStr" s="25">
+        <is>
+          <t>Ледяное копье</t>
+        </is>
+      </c>
       <c r="I1506" s="143" t="str"/>
     </row>
     <row r="1507" ht="21" customHeight="1">
@@ -38264,7 +38884,11 @@
       <c r="G1507" s="24" t="str">
         <v>火之風暴</v>
       </c>
-      <c r="H1507" s="25" t="str"/>
+      <c r="H1507" t="inlineStr" s="25">
+        <is>
+          <t>Огненная буря</t>
+        </is>
+      </c>
       <c r="I1507" s="143" t="str"/>
     </row>
     <row r="1508" ht="21" customHeight="1">
@@ -38289,7 +38913,11 @@
       <c r="G1508" s="24" t="str">
         <v>火系抗性</v>
       </c>
-      <c r="H1508" s="25" t="str"/>
+      <c r="H1508" t="inlineStr" s="25">
+        <is>
+          <t>Сопротивляемость огню</t>
+        </is>
+      </c>
       <c r="I1508" s="143" t="str"/>
     </row>
     <row r="1509" ht="21" customHeight="1">
@@ -38314,7 +38942,11 @@
       <c r="G1509" s="24" t="str">
         <v>冰系抗性</v>
       </c>
-      <c r="H1509" s="25" t="str"/>
+      <c r="H1509" t="inlineStr" s="25">
+        <is>
+          <t>Сопротивляемость льду</t>
+        </is>
+      </c>
       <c r="I1509" s="143" t="str"/>
     </row>
     <row r="1510" ht="21" customHeight="1">
@@ -38339,7 +38971,11 @@
       <c r="G1510" s="24" t="str">
         <v>雷系抗性</v>
       </c>
-      <c r="H1510" s="25" t="str"/>
+      <c r="H1510" t="inlineStr" s="25">
+        <is>
+          <t>Сопротивляемость молниям</t>
+        </is>
+      </c>
       <c r="I1510" s="143" t="str"/>
     </row>
     <row r="1511" ht="21" customHeight="1">
@@ -38364,7 +39000,11 @@
       <c r="G1511" s="24" t="str">
         <v>冰之漩渦</v>
       </c>
-      <c r="H1511" s="25" t="str"/>
+      <c r="H1511" t="inlineStr" s="25">
+        <is>
+          <t>Ледяной вихрь</t>
+        </is>
+      </c>
       <c r="I1511" s="143" t="str"/>
     </row>
     <row r="1512" ht="21" customHeight="1">
@@ -38389,7 +39029,11 @@
       <c r="G1512" s="24" t="str">
         <v>冰風暴</v>
       </c>
-      <c r="H1512" s="25" t="str"/>
+      <c r="H1512" t="inlineStr" s="25">
+        <is>
+          <t>Ледяная буря</t>
+        </is>
+      </c>
       <c r="I1512" s="143" t="str"/>
     </row>
     <row r="1513" ht="21" customHeight="1">
@@ -38414,7 +39058,11 @@
       <c r="G1513" s="24" t="str">
         <v>心靈爆震</v>
       </c>
-      <c r="H1513" s="25" t="str"/>
+      <c r="H1513" t="inlineStr" s="25">
+        <is>
+          <t>Неотвратимый взрыв</t>
+        </is>
+      </c>
       <c r="I1513" s="143" t="str"/>
     </row>
     <row r="1514" ht="21" customHeight="1">
@@ -38439,7 +39087,11 @@
       <c r="G1514" s="24" t="str">
         <v>雷電風暴</v>
       </c>
-      <c r="H1514" s="25" t="str"/>
+      <c r="H1514" t="inlineStr" s="25">
+        <is>
+          <t>Гроза</t>
+        </is>
+      </c>
       <c r="I1514" s="143" t="str"/>
     </row>
     <row r="1515" ht="21" customHeight="1">
@@ -38464,7 +39116,11 @@
       <c r="G1515" s="24" t="str">
         <v>流星風暴</v>
       </c>
-      <c r="H1515" s="25" t="str"/>
+      <c r="H1515" t="inlineStr" s="25">
+        <is>
+          <t>Метеорит</t>
+        </is>
+      </c>
       <c r="I1515" s="143" t="str"/>
     </row>
     <row r="1516" ht="21" customHeight="1">
@@ -38489,7 +39145,11 @@
       <c r="G1516" s="24" t="str">
         <v>記憶咒法</v>
       </c>
-      <c r="H1516" s="25" t="str"/>
+      <c r="H1516" t="inlineStr" s="25">
+        <is>
+          <t>Двойной портал</t>
+        </is>
+      </c>
       <c r="I1516" s="143" t="str"/>
     </row>
     <row r="1517" ht="21" customHeight="1">
@@ -38514,7 +39174,11 @@
       <c r="G1517" s="24" t="str">
         <v>移動咒法</v>
       </c>
-      <c r="H1517" s="25" t="str"/>
+      <c r="H1517" t="inlineStr" s="25">
+        <is>
+          <t>Телепорт</t>
+        </is>
+      </c>
       <c r="I1517" s="143" t="str"/>
     </row>
     <row r="1518" ht="21" customHeight="1">
@@ -38539,7 +39203,11 @@
       <c r="G1518" s="24" t="str">
         <v>長存咒法</v>
       </c>
-      <c r="H1518" s="25" t="str"/>
+      <c r="H1518" t="inlineStr" s="25">
+        <is>
+          <t>Множественные порталы</t>
+        </is>
+      </c>
       <c r="I1518" s="143" t="str"/>
     </row>
     <row r="1519" ht="21" customHeight="1">
@@ -38564,7 +39232,11 @@
       <c r="G1519" s="24" t="str">
         <v>精神具現</v>
       </c>
-      <c r="H1519" s="25" t="str"/>
+      <c r="H1519" t="inlineStr" s="25">
+        <is>
+          <t>Сияние разума</t>
+        </is>
+      </c>
       <c r="I1519" s="143" t="str"/>
     </row>
     <row r="1520" ht="21" customHeight="1">
@@ -38589,7 +39261,11 @@
       <c r="G1520" s="24" t="str">
         <v>靈魂之光</v>
       </c>
-      <c r="H1520" s="25" t="str"/>
+      <c r="H1520" t="inlineStr" s="25">
+        <is>
+          <t>Озарение</t>
+        </is>
+      </c>
       <c r="I1520" s="143" t="str"/>
     </row>
     <row r="1521" ht="21" customHeight="1">
@@ -38614,7 +39290,11 @@
       <c r="G1521" s="24" t="str">
         <v>魔力屏障</v>
       </c>
-      <c r="H1521" s="25" t="str"/>
+      <c r="H1521" t="inlineStr" s="25">
+        <is>
+          <t>Магический щит</t>
+        </is>
+      </c>
       <c r="I1521" s="143" t="str"/>
     </row>
     <row r="1522" ht="21" customHeight="1">
@@ -38639,7 +39319,11 @@
       <c r="G1522" s="24" t="str">
         <v>風行</v>
       </c>
-      <c r="H1522" s="25" t="str"/>
+      <c r="H1522" t="inlineStr" s="25">
+        <is>
+          <t>По следам ветра</t>
+        </is>
+      </c>
       <c r="I1522" s="143" t="str"/>
     </row>
     <row r="1523" ht="21" customHeight="1">
@@ -38664,7 +39348,11 @@
       <c r="G1523" s="24" t="str">
         <v>虛空之刃</v>
       </c>
-      <c r="H1523" s="25" t="str"/>
+      <c r="H1523" t="inlineStr" s="25">
+        <is>
+          <t>Летящее лезвие</t>
+        </is>
+      </c>
       <c r="I1523" s="143" t="str"/>
     </row>
     <row r="1524" ht="21" customHeight="1">
@@ -38689,7 +39377,11 @@
       <c r="G1524" s="24" t="str">
         <v>土牆術</v>
       </c>
-      <c r="H1524" s="25" t="str"/>
+      <c r="H1524" t="inlineStr" s="25">
+        <is>
+          <t>Непреодолимая стена</t>
+        </is>
+      </c>
       <c r="I1524" s="143" t="str"/>
     </row>
     <row r="1525" ht="21" customHeight="1">
@@ -38714,7 +39406,11 @@
       <c r="G1525" s="24" t="str">
         <v>沙之龍</v>
       </c>
-      <c r="H1525" s="25" t="str"/>
+      <c r="H1525" t="inlineStr" s="25">
+        <is>
+          <t>Песчаная буря</t>
+        </is>
+      </c>
       <c r="I1525" s="143" t="str"/>
     </row>
     <row r="1526" ht="21" customHeight="1">
@@ -38739,7 +39435,11 @@
       <c r="G1526" s="24" t="str">
         <v>樹人召喚</v>
       </c>
-      <c r="H1526" s="25" t="str"/>
+      <c r="H1526" t="inlineStr" s="25">
+        <is>
+          <t>Темное растение</t>
+        </is>
+      </c>
       <c r="I1526" s="143" t="str"/>
     </row>
     <row r="1527" ht="21" customHeight="1">
@@ -38764,7 +39464,11 @@
       <c r="G1527" s="24" t="str">
         <v>黑暗吸收</v>
       </c>
-      <c r="H1527" s="25" t="str"/>
+      <c r="H1527" t="inlineStr" s="25">
+        <is>
+          <t>Темный рикошет</t>
+        </is>
+      </c>
       <c r="I1527" s="143" t="str"/>
     </row>
     <row r="1528" ht="21" customHeight="1">
@@ -38789,7 +39493,11 @@
       <c r="G1528" s="24" t="str">
         <v>偽裝結界</v>
       </c>
-      <c r="H1528" s="25" t="str"/>
+      <c r="H1528" t="inlineStr" s="25">
+        <is>
+          <t>Массовая невидимость</t>
+        </is>
+      </c>
       <c r="I1528" s="143" t="str"/>
     </row>
     <row r="1529" ht="21" customHeight="1">
@@ -38814,7 +39522,11 @@
       <c r="G1529" s="24" t="str">
         <v>劇毒孢子</v>
       </c>
-      <c r="H1529" s="25" t="str"/>
+      <c r="H1529" t="inlineStr" s="25">
+        <is>
+          <t>Ядовитый удар</t>
+        </is>
+      </c>
       <c r="I1529" s="143" t="str"/>
     </row>
     <row r="1530" ht="21" customHeight="1">
@@ -38839,7 +39551,11 @@
       <c r="G1530" s="24" t="str">
         <v>黑暗契約</v>
       </c>
-      <c r="H1530" s="25" t="str"/>
+      <c r="H1530" t="inlineStr" s="25">
+        <is>
+          <t>Темная аура</t>
+        </is>
+      </c>
       <c r="I1530" s="143" t="str"/>
     </row>
     <row r="1531" ht="21" customHeight="1">
@@ -38864,7 +39580,11 @@
       <c r="G1531" s="24" t="str">
         <v>吸血術</v>
       </c>
-      <c r="H1531" s="25" t="str"/>
+      <c r="H1531" t="inlineStr" s="25">
+        <is>
+          <t>Кража жизни</t>
+        </is>
+      </c>
       <c r="I1531" s="143" t="str"/>
     </row>
     <row r="1532" ht="21" customHeight="1">
@@ -38889,7 +39609,11 @@
       <c r="G1532" s="24" t="str">
         <v>毒液腐蝕</v>
       </c>
-      <c r="H1532" s="25" t="str"/>
+      <c r="H1532" t="inlineStr" s="25">
+        <is>
+          <t>Гниение</t>
+        </is>
+      </c>
       <c r="I1532" s="143" t="str"/>
     </row>
     <row r="1533" ht="21" customHeight="1">
@@ -38914,7 +39638,11 @@
       <c r="G1533" s="24" t="str">
         <v>魔法抹滅</v>
       </c>
-      <c r="H1533" s="25" t="str"/>
+      <c r="H1533" t="inlineStr" s="25">
+        <is>
+          <t>Рассеивание</t>
+        </is>
+      </c>
       <c r="I1533" s="143" t="str"/>
     </row>
     <row r="1534" ht="21" customHeight="1">
@@ -38939,7 +39667,11 @@
       <c r="G1534" s="24" t="str">
         <v>毒系抗性</v>
       </c>
-      <c r="H1534" s="25" t="str"/>
+      <c r="H1534" t="inlineStr" s="25">
+        <is>
+          <t>Сопротивляемость магии тьмы</t>
+        </is>
+      </c>
       <c r="I1534" s="143" t="str"/>
     </row>
     <row r="1535" ht="21" customHeight="1">
@@ -38964,7 +39696,11 @@
       <c r="G1535" s="24" t="str">
         <v>心靈侵害</v>
       </c>
-      <c r="H1535" s="25" t="str"/>
+      <c r="H1535" t="inlineStr" s="25">
+        <is>
+          <t>Эфирная вспышка</t>
+        </is>
+      </c>
       <c r="I1535" s="143" t="str"/>
     </row>
     <row r="1536" ht="21" customHeight="1">
@@ -38989,7 +39725,11 @@
       <c r="G1536" s="24" t="str">
         <v>劇毒之源</v>
       </c>
-      <c r="H1536" s="25" t="str"/>
+      <c r="H1536" t="inlineStr" s="25">
+        <is>
+          <t>Ненависть</t>
+        </is>
+      </c>
       <c r="I1536" s="143" t="str"/>
     </row>
     <row r="1537" ht="21" customHeight="1">
@@ -39014,7 +39754,11 @@
       <c r="G1537" s="24" t="str">
         <v>削弱心智</v>
       </c>
-      <c r="H1537" s="25" t="str"/>
+      <c r="H1537" t="inlineStr" s="25">
+        <is>
+          <t>Срыв</t>
+        </is>
+      </c>
       <c r="I1537" s="143" t="str"/>
     </row>
     <row r="1538" ht="21" customHeight="1">
@@ -39039,7 +39783,11 @@
       <c r="G1538" s="24" t="str">
         <v>黑暗狂熱</v>
       </c>
-      <c r="H1538" s="25" t="str"/>
+      <c r="H1538" t="inlineStr" s="25">
+        <is>
+          <t>Темная грань</t>
+        </is>
+      </c>
       <c r="I1538" s="143" t="str"/>
     </row>
     <row r="1539" ht="21" customHeight="1">
@@ -39064,7 +39812,11 @@
       <c r="G1539" s="24" t="str">
         <v>思考凝結</v>
       </c>
-      <c r="H1539" s="25" t="str"/>
+      <c r="H1539" t="inlineStr" s="25">
+        <is>
+          <t>Остановка времени</t>
+        </is>
+      </c>
       <c r="I1539" s="143" t="str"/>
     </row>
     <row r="1540" ht="21" customHeight="1">
@@ -39089,7 +39841,11 @@
       <c r="G1540" s="24" t="str">
         <v>魔法</v>
       </c>
-      <c r="H1540" s="25" t="str"/>
+      <c r="H1540" t="inlineStr" s="25">
+        <is>
+          <t>Мираж</t>
+        </is>
+      </c>
       <c r="I1540" s="143" t="str"/>
     </row>
     <row r="1541" ht="21" customHeight="1">
@@ -39114,7 +39870,11 @@
       <c r="G1541" s="24" t="str">
         <v>迷惑詛咒</v>
       </c>
-      <c r="H1541" s="25" t="str"/>
+      <c r="H1541" t="inlineStr" s="25">
+        <is>
+          <t>Немощь</t>
+        </is>
+      </c>
       <c r="I1541" s="143" t="str"/>
     </row>
     <row r="1542" ht="21" customHeight="1">
@@ -39139,7 +39899,11 @@
       <c r="G1542" s="24" t="str">
         <v>風沙襲</v>
       </c>
-      <c r="H1542" s="25" t="str"/>
+      <c r="H1542" t="inlineStr" s="25">
+        <is>
+          <t>Песчаный вихрь</t>
+        </is>
+      </c>
       <c r="I1542" s="143" t="str"/>
     </row>
     <row r="1543" ht="21" customHeight="1">
@@ -39164,7 +39928,11 @@
       <c r="G1543" s="24" t="str">
         <v>精神制裁</v>
       </c>
-      <c r="H1543" s="25" t="str"/>
+      <c r="H1543" t="inlineStr" s="25">
+        <is>
+          <t>Мысленный удар</t>
+        </is>
+      </c>
       <c r="I1543" s="143" t="str"/>
     </row>
     <row r="1544" ht="21" customHeight="1">
@@ -39189,7 +39957,11 @@
       <c r="G1544" s="24" t="str">
         <v>毀滅鎧甲</v>
       </c>
-      <c r="H1544" s="25" t="str"/>
+      <c r="H1544" t="inlineStr" s="25">
+        <is>
+          <t>Слабость</t>
+        </is>
+      </c>
       <c r="I1544" s="143" t="str"/>
     </row>
     <row r="1545" ht="21" customHeight="1">
@@ -39214,7 +39986,11 @@
       <c r="G1545" s="24" t="str">
         <v>步伐緩慢</v>
       </c>
-      <c r="H1545" s="25" t="str"/>
+      <c r="H1545" t="inlineStr" s="25">
+        <is>
+          <t>Обуздание</t>
+        </is>
+      </c>
       <c r="I1545" s="143" t="str"/>
     </row>
     <row r="1546" ht="21" customHeight="1">
@@ -39239,7 +40015,11 @@
       <c r="G1546" s="24" t="str">
         <v>秘法抗性</v>
       </c>
-      <c r="H1546" s="25" t="str"/>
+      <c r="H1546" t="inlineStr" s="25">
+        <is>
+          <t>Сопротивляемость чарам</t>
+        </is>
+      </c>
       <c r="I1546" s="143" t="str"/>
     </row>
     <row r="1547" ht="21" customHeight="1">
@@ -39264,7 +40044,11 @@
       <c r="G1547" s="24" t="str">
         <v>寒冷意念</v>
       </c>
-      <c r="H1547" s="25" t="str"/>
+      <c r="H1547" t="inlineStr" s="25">
+        <is>
+          <t>Морозный удар</t>
+        </is>
+      </c>
       <c r="I1547" s="143" t="str"/>
     </row>
     <row r="1548" ht="21" customHeight="1">
@@ -39289,7 +40073,11 @@
       <c r="G1548" s="24" t="str">
         <v>劇毒沼</v>
       </c>
-      <c r="H1548" s="25" t="str"/>
+      <c r="H1548" t="inlineStr" s="25">
+        <is>
+          <t>Ядовитая топь</t>
+        </is>
+      </c>
       <c r="I1548" s="143" t="str"/>
     </row>
     <row r="1549" ht="21" customHeight="1">
@@ -39314,7 +40102,11 @@
       <c r="G1549" s="24" t="str">
         <v>靜默風暴</v>
       </c>
-      <c r="H1549" s="25" t="str"/>
+      <c r="H1549" t="inlineStr" s="25">
+        <is>
+          <t>Немая буря</t>
+        </is>
+      </c>
       <c r="I1549" s="143" t="str"/>
     </row>
     <row r="1550" ht="21" customHeight="1">
@@ -39339,7 +40131,11 @@
       <c r="G1550" s="24" t="str">
         <v>惡念之箭</v>
       </c>
-      <c r="H1550" s="25" t="str"/>
+      <c r="H1550" t="inlineStr" s="25">
+        <is>
+          <t>Чума</t>
+        </is>
+      </c>
       <c r="I1550" s="143" t="str"/>
     </row>
     <row r="1551" ht="21" customHeight="1">
@@ -39364,7 +40160,11 @@
       <c r="G1551" s="24" t="str">
         <v>騎乘攻擊</v>
       </c>
-      <c r="H1551" s="25" t="str"/>
+      <c r="H1551" t="inlineStr" s="25">
+        <is>
+          <t>Конный бой</t>
+        </is>
+      </c>
       <c r="I1551" s="143" t="str"/>
     </row>
     <row r="1552" ht="21" customHeight="1">
@@ -39389,7 +40189,11 @@
       <c r="G1552" s="24" t="str">
         <v>騎乘攻擊</v>
       </c>
-      <c r="H1552" s="25" t="str"/>
+      <c r="H1552" t="inlineStr" s="25">
+        <is>
+          <t>Конный бой</t>
+        </is>
+      </c>
       <c r="I1552" s="143" t="str"/>
     </row>
     <row r="1553" ht="21" customHeight="1">
@@ -39414,7 +40218,11 @@
       <c r="G1553" s="24" t="str">
         <v>騎乘中射擊</v>
       </c>
-      <c r="H1553" s="25" t="str"/>
+      <c r="H1553" t="inlineStr" s="25">
+        <is>
+          <t>Конная стрельба</t>
+        </is>
+      </c>
       <c r="I1553" s="143" t="str"/>
     </row>
     <row r="1554" ht="21" customHeight="1">
@@ -39439,7 +40247,11 @@
       <c r="G1554" s="24" t="str">
         <v>騎手之魂</v>
       </c>
-      <c r="H1554" s="25" t="str"/>
+      <c r="H1554" t="inlineStr" s="25">
+        <is>
+          <t>Конная магия</t>
+        </is>
+      </c>
       <c r="I1554" s="143" t="str"/>
     </row>
     <row r="1555" ht="21" customHeight="1">
@@ -39464,7 +40276,11 @@
       <c r="G1555" s="24" t="str">
         <v>召喚</v>
       </c>
-      <c r="H1555" s="25" t="str"/>
+      <c r="H1555" t="inlineStr" s="25">
+        <is>
+          <t>Вызов коня</t>
+        </is>
+      </c>
       <c r="I1555" s="143" t="str"/>
     </row>
     <row r="1556" ht="21" customHeight="1">
@@ -39489,7 +40305,11 @@
       <c r="G1556" s="24" t="str">
         <v>騎士守護</v>
       </c>
-      <c r="H1556" s="25" t="str"/>
+      <c r="H1556" t="inlineStr" s="25">
+        <is>
+          <t>Защита коня</t>
+        </is>
+      </c>
       <c r="I1556" s="143" t="str"/>
     </row>
     <row r="1557" ht="21" customHeight="1">
@@ -54788,8 +55608,16 @@
       <c r="G2173" s="39" t="str">
         <v>挑撥，故意激怒對方攻擊自己</v>
       </c>
-      <c r="H2173" s="40" t="str"/>
-      <c r="I2173" s="143" t="str"/>
+      <c r="H2173" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет разозлить цель. Применяется только против монстров.</t>
+        </is>
+      </c>
+      <c r="I2173" t="inlineStr" s="143">
+        <is>
+          <t>Taunts the enemy in order to enrage them.</t>
+        </is>
+      </c>
     </row>
     <row r="2174" ht="15" hidden="0" customHeight="1">
       <c r="A2174" s="38" t="str">
@@ -54863,7 +55691,11 @@
       <c r="G2176" s="39" t="str">
         <v>增加恢復類藥劑使用時的恢復量</v>
       </c>
-      <c r="H2176" s="40" t="str"/>
+      <c r="H2176" t="inlineStr" s="40">
+        <is>
+          <t>Увеличивает эффективность зелий.</t>
+        </is>
+      </c>
       <c r="I2176" s="143" t="str"/>
     </row>
     <row r="2177" ht="15" hidden="0" customHeight="1">
@@ -54938,8 +55770,16 @@
       <c r="G2179" s="39" t="str">
         <v>使自己的攻擊速度上升</v>
       </c>
-      <c r="H2179" s="40" t="str"/>
-      <c r="I2179" s="143" t="str"/>
+      <c r="H2179" t="inlineStr" s="40">
+        <is>
+          <t>Повышает скорость атаки.</t>
+        </is>
+      </c>
+      <c r="I2179" t="inlineStr" s="143">
+        <is>
+          <t>Increases your Attack Speed.</t>
+        </is>
+      </c>
     </row>
     <row r="2180" ht="15" hidden="0" customHeight="1">
       <c r="A2180" s="38" t="str">
@@ -55013,8 +55853,16 @@
       <c r="G2182" s="39" t="str">
         <v>使武器的近戰攻擊力上升</v>
       </c>
-      <c r="H2182" s="40" t="str"/>
-      <c r="I2182" s="143" t="str"/>
+      <c r="H2182" t="inlineStr" s="40">
+        <is>
+          <t>Увеличение урона, наносимого оружием ближнего боя.</t>
+        </is>
+      </c>
+      <c r="I2182" t="inlineStr" s="143">
+        <is>
+          <t>Increases the damage done by your weapons in melee combat.</t>
+        </is>
+      </c>
     </row>
     <row r="2183" ht="15" hidden="0" customHeight="1">
       <c r="A2183" s="38" t="str">
@@ -55088,8 +55936,16 @@
       <c r="G2185" s="39" t="str">
         <v>瞄準對手的腳部進行攻擊，使其移動速度降低。</v>
       </c>
-      <c r="H2185" s="40" t="str"/>
-      <c r="I2185" s="143" t="str"/>
+      <c r="H2185" t="inlineStr" s="40">
+        <is>
+          <t>Наносит удар по ногам врага и замедляет его движение.</t>
+        </is>
+      </c>
+      <c r="I2185" t="inlineStr" s="143">
+        <is>
+          <t>Attacks the enemy's legs, slowing their movements.</t>
+        </is>
+      </c>
     </row>
     <row r="2186" ht="15" hidden="0" customHeight="1">
       <c r="A2186" s="38" t="str">
@@ -55163,8 +56019,16 @@
       <c r="G2188" s="39" t="str">
         <v>防止外敵的攻擊，減少自身所受到的傷害</v>
       </c>
-      <c r="H2188" s="40" t="str"/>
-      <c r="I2188" s="143" t="str"/>
+      <c r="H2188" t="inlineStr" s="40">
+        <is>
+          <t>Снижение урона путем блокирования атак противника.</t>
+        </is>
+      </c>
+      <c r="I2188" t="inlineStr" s="143">
+        <is>
+          <t>Reduces the damage of incoming attacks through guarding in a defensive stance.</t>
+        </is>
+      </c>
     </row>
     <row r="2189" ht="15" hidden="0" customHeight="1">
       <c r="A2189" s="38" t="str">
@@ -55238,7 +56102,11 @@
       <c r="G2191" s="39" t="str">
         <v>挑釁，故意使目標對象生氣。暫時將目標注意力集中在自己身上。</v>
       </c>
-      <c r="H2191" s="40" t="str"/>
+      <c r="H2191" t="inlineStr" s="40">
+        <is>
+          <t>Противник обращает внимание только на применяющего умение.</t>
+        </is>
+      </c>
       <c r="I2191" s="143" t="str"/>
     </row>
     <row r="2192" ht="15" hidden="0" customHeight="1">
@@ -55313,8 +56181,16 @@
       <c r="G2194" s="39" t="str">
         <v>增加自身以及隊伍成員的攻擊力</v>
       </c>
-      <c r="H2194" s="40" t="str"/>
-      <c r="I2194" s="143" t="str"/>
+      <c r="H2194" t="inlineStr" s="40">
+        <is>
+          <t>Увеличивает силу атаки всех игроков в группе.</t>
+        </is>
+      </c>
+      <c r="I2194" t="inlineStr" s="143">
+        <is>
+          <t>Raises the physical abilities of all party members, increasing their Attack Power.</t>
+        </is>
+      </c>
     </row>
     <row r="2195" ht="15" hidden="0" customHeight="1">
       <c r="A2195" s="38" t="str">
@@ -55388,8 +56264,16 @@
       <c r="G2197" s="39" t="str">
         <v>提高信仰心，增加隊伍全員的魔法抵抗力</v>
       </c>
-      <c r="H2197" s="40" t="str"/>
-      <c r="I2197" s="143" t="str"/>
+      <c r="H2197" t="inlineStr" s="40">
+        <is>
+          <t>Сила веры повышает сопротивляемость всех игроков в группе магии.</t>
+        </is>
+      </c>
+      <c r="I2197" t="inlineStr" s="143">
+        <is>
+          <t>Increases the Magic Resistance of all party members by increasing their faith.</t>
+        </is>
+      </c>
     </row>
     <row r="2198" ht="15" hidden="0" customHeight="1">
       <c r="A2198" s="38" t="str">
@@ -55463,8 +56347,16 @@
       <c r="G2200" s="39" t="str">
         <v>犧牲自身防禦，增加自身命中率</v>
       </c>
-      <c r="H2200" s="40" t="str"/>
-      <c r="I2200" s="143" t="str"/>
+      <c r="H2200" t="inlineStr" s="40">
+        <is>
+          <t>Все силы фокусируются на атаке за счет ухудшения защиты.</t>
+        </is>
+      </c>
+      <c r="I2200" t="inlineStr" s="143">
+        <is>
+          <t>Sacrifices your Defense to focus on Attack Power.</t>
+        </is>
+      </c>
     </row>
     <row r="2201" ht="15" hidden="0" customHeight="1">
       <c r="A2201" s="38" t="str">
@@ -55538,8 +56430,16 @@
       <c r="G2203" s="39" t="str">
         <v>只有裝備盾牌時才能使用，犧牲攻擊力，將精神集中於防禦上。</v>
       </c>
-      <c r="H2203" s="40" t="str"/>
-      <c r="I2203" s="143" t="str"/>
+      <c r="H2203" t="inlineStr" s="40">
+        <is>
+          <t>Необходимо держать в руках щит. Защита увеличивается, но атака понижается.</t>
+        </is>
+      </c>
+      <c r="I2203" t="inlineStr" s="143">
+        <is>
+          <t>Can only be used when a shield is equipped. Sacrifices your Attack Power to focus on Defense.</t>
+        </is>
+      </c>
     </row>
     <row r="2204" ht="15" hidden="0" customHeight="1">
       <c r="A2204" s="38" t="str">
@@ -55613,8 +56513,16 @@
       <c r="G2206" s="39" t="str">
         <v>效果時間內，攻擊力增加，但受到的傷害也增加，攻擊一次後效果消失。</v>
       </c>
-      <c r="H2206" s="40" t="str"/>
-      <c r="I2206" s="143" t="str"/>
+      <c r="H2206" t="inlineStr" s="40">
+        <is>
+          <t>Во время действия увеличиваются сила атаки и получаемый урон. Действие прекращается после нанесения удара противнику.</t>
+        </is>
+      </c>
+      <c r="I2206" t="inlineStr" s="143">
+        <is>
+          <t>Increases Attack Power, but also increases the damage you take. The effect ends once you make an attack.</t>
+        </is>
+      </c>
     </row>
     <row r="2207" ht="15" hidden="0" customHeight="1">
       <c r="A2207" s="38" t="str">
@@ -55688,8 +56596,16 @@
       <c r="G2209" s="39" t="str">
         <v>HP減少30%，換取技能冷卻時間減半的效果</v>
       </c>
-      <c r="H2209" s="40" t="str"/>
-      <c r="I2209" s="143" t="str"/>
+      <c r="H2209" t="inlineStr" s="40">
+        <is>
+          <t>Уменьшает ОЗ на 30% и сокращает время перезарядки умений наполовину.</t>
+        </is>
+      </c>
+      <c r="I2209" t="inlineStr" s="143">
+        <is>
+          <t>Reduces HP by 30% and reduces skill cooldown by half.</t>
+        </is>
+      </c>
     </row>
     <row r="2210" ht="15" hidden="0" customHeight="1">
       <c r="A2210" s="38" t="str">
@@ -55763,8 +56679,16 @@
       <c r="G2212" s="39" t="str">
         <v>從背後命中目標時，敵我雙方停止動作</v>
       </c>
-      <c r="H2212" s="40" t="str"/>
-      <c r="I2212" s="143" t="str"/>
+      <c r="H2212" t="inlineStr" s="40">
+        <is>
+          <t>После нанесения удара в спину противника и игрок, и противник обездвиживаются.</t>
+        </is>
+      </c>
+      <c r="I2212" t="inlineStr" s="143">
+        <is>
+          <t>When you strike from behind, both you and your target cease moving.</t>
+        </is>
+      </c>
     </row>
     <row r="2213" ht="15" hidden="0" customHeight="1">
       <c r="A2213" s="38" t="str">
@@ -56138,8 +57062,16 @@
       <c r="G2227" s="39" t="str">
         <v>快速斬殺目標二次斬，組合技能之一</v>
       </c>
-      <c r="H2227" s="40" t="str"/>
-      <c r="I2227" s="143" t="str"/>
+      <c r="H2227" t="inlineStr" s="40">
+        <is>
+          <t>Быстрая сдвоенная режущая атака. Может использоваться в сочетании с другими умениями.</t>
+        </is>
+      </c>
+      <c r="I2227" t="inlineStr" s="143">
+        <is>
+          <t>A combo skill that strikes the enemy with two rapid cuts.</t>
+        </is>
+      </c>
     </row>
     <row r="2228" ht="15" hidden="0" customHeight="1">
       <c r="A2228" s="38" t="str">
@@ -56213,8 +57145,16 @@
       <c r="G2230" s="39" t="str">
         <v>迅速斬殺目標三次，有幾率對目標造成流血效果</v>
       </c>
-      <c r="H2230" s="40" t="str"/>
-      <c r="I2230" s="143" t="str"/>
+      <c r="H2230" t="inlineStr" s="40">
+        <is>
+          <t>Наносится тройной крученый удар. Есть шанс кровотечения противника.</t>
+        </is>
+      </c>
+      <c r="I2230" t="inlineStr" s="143">
+        <is>
+          <t>Strikes with three rapid cuts and may cause the enemy to Bleed.</t>
+        </is>
+      </c>
     </row>
     <row r="2231" ht="15" hidden="0" customHeight="1">
       <c r="A2231" s="38" t="str">
@@ -56288,8 +57228,16 @@
       <c r="G2233" s="39" t="str">
         <v>利用離心力，攻擊自己周圍的敵人</v>
       </c>
-      <c r="H2233" s="40" t="str"/>
-      <c r="I2233" s="143" t="str"/>
+      <c r="H2233" t="inlineStr" s="40">
+        <is>
+          <t>Атака по всем находящимся вблизи противникам с использованием центробежной силы.</t>
+        </is>
+      </c>
+      <c r="I2233" t="inlineStr" s="143">
+        <is>
+          <t>Attacks nearby enemies all at once with a spinning blow.</t>
+        </is>
+      </c>
     </row>
     <row r="2234" ht="15" hidden="0" customHeight="1">
       <c r="A2234" s="38" t="str">
@@ -56363,8 +57311,16 @@
       <c r="G2236" s="39" t="str">
         <v>接受對手的攻擊，並給以較大的反擊傷害</v>
       </c>
-      <c r="H2236" s="40" t="str"/>
-      <c r="I2236" s="143" t="str"/>
+      <c r="H2236" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет уклониться от удара противника.</t>
+        </is>
+      </c>
+      <c r="I2236" t="inlineStr" s="143">
+        <is>
+          <t>Knocks aside your opponent's attack, leaving them wide open.</t>
+        </is>
+      </c>
     </row>
     <row r="2237" ht="15" hidden="0" customHeight="1">
       <c r="A2237" s="38" t="str">
@@ -56438,8 +57394,16 @@
       <c r="G2239" s="39" t="str">
         <v>提高專注度，提升下次攻擊的命中率</v>
       </c>
-      <c r="H2239" s="40" t="str"/>
-      <c r="I2239" s="143" t="str"/>
+      <c r="H2239" t="inlineStr" s="40">
+        <is>
+          <t>Следующая атака будет более точной за счет роста сосредоточенности.</t>
+        </is>
+      </c>
+      <c r="I2239" t="inlineStr" s="143">
+        <is>
+          <t>Accuracy increases for your next attack as the result of boosted concentration.</t>
+        </is>
+      </c>
     </row>
     <row r="2240" ht="15" hidden="0" customHeight="1">
       <c r="A2240" s="38" t="str">
@@ -56513,8 +57477,16 @@
       <c r="G2242" s="39" t="str">
         <v>通過強烈的打擊，無視目標防具性能。連續技之一</v>
       </c>
-      <c r="H2242" s="40" t="str"/>
-      <c r="I2242" s="143" t="str"/>
+      <c r="H2242" t="inlineStr" s="40">
+        <is>
+          <t>Мощный удар, обходящий защиту противника.</t>
+        </is>
+      </c>
+      <c r="I2242" t="inlineStr" s="143">
+        <is>
+          <t>Launches a powerful attack that hits regardless of the enemy's armor. This is a combo skill.</t>
+        </is>
+      </c>
     </row>
     <row r="2243" ht="15" hidden="0" customHeight="1">
       <c r="A2243" s="38" t="str">
@@ -56588,8 +57560,16 @@
       <c r="G2245" s="39" t="str">
         <v>裝備劍類武器時技能威力提升</v>
       </c>
-      <c r="H2245" s="40" t="str"/>
-      <c r="I2245" s="143" t="str"/>
+      <c r="H2245" t="inlineStr" s="40">
+        <is>
+          <t>Во время использования меча эффективность умений повышается.</t>
+        </is>
+      </c>
+      <c r="I2245" t="inlineStr" s="143">
+        <is>
+          <t>Increases the damage done when you use a skill with a sword.</t>
+        </is>
+      </c>
     </row>
     <row r="2246" ht="15" hidden="0" customHeight="1">
       <c r="A2246" s="38" t="str">
@@ -56663,8 +57643,16 @@
       <c r="G2248" s="39" t="str">
         <v>消費精力，發動強大突襲，只能在騎乘中使用</v>
       </c>
-      <c r="H2248" s="40" t="str"/>
-      <c r="I2248" s="143" t="str"/>
+      <c r="H2248" t="inlineStr" s="40">
+        <is>
+          <t>Мощный удар с разбега. Умение может использоваться только всадником.</t>
+        </is>
+      </c>
+      <c r="I2248" t="inlineStr" s="143">
+        <is>
+          <t>Uses Momentum to perform a powerful charge. Can only be used while on horseback.</t>
+        </is>
+      </c>
     </row>
     <row r="2249" ht="15" hidden="0" customHeight="1">
       <c r="A2249" s="38" t="str">
@@ -56738,8 +57726,16 @@
       <c r="G2251" s="39" t="str">
         <v>依靠慣性，向前方攻擊，只能在騎乘中使用</v>
       </c>
-      <c r="H2251" s="40" t="str"/>
-      <c r="I2251" s="143" t="str"/>
+      <c r="H2251" t="inlineStr" s="40">
+        <is>
+          <t>Резкий бросок вперед на скорости. Может применяться только всадниками.</t>
+        </is>
+      </c>
+      <c r="I2251" t="inlineStr" s="143">
+        <is>
+          <t>Uses Momentum to charge forward. Can only be used while on horseback.</t>
+        </is>
+      </c>
     </row>
     <row r="2252" ht="15" hidden="0" customHeight="1">
       <c r="A2252" s="38" t="str">
@@ -56813,8 +57809,16 @@
       <c r="G2254" s="39" t="str">
         <v>用力將槍刺出，攻擊前方直線範圍</v>
       </c>
-      <c r="H2254" s="40" t="str"/>
-      <c r="I2254" s="143" t="str"/>
+      <c r="H2254" t="inlineStr" s="40">
+        <is>
+          <t>Атака противника мощным ударом копья.</t>
+        </is>
+      </c>
+      <c r="I2254" t="inlineStr" s="143">
+        <is>
+          <t>Thrusts your spear mightily, attacking the enemy in front of you.</t>
+        </is>
+      </c>
     </row>
     <row r="2255" ht="15" hidden="0" customHeight="1">
       <c r="A2255" s="38" t="str">
@@ -56888,8 +57892,16 @@
       <c r="G2257" s="39" t="str">
         <v>連續高速三次刺殺</v>
       </c>
-      <c r="H2257" s="40" t="str"/>
-      <c r="I2257" s="143" t="str"/>
+      <c r="H2257" t="inlineStr" s="40">
+        <is>
+          <t>Быстрая тройная колющая атака.</t>
+        </is>
+      </c>
+      <c r="I2257" t="inlineStr" s="143">
+        <is>
+          <t>Stabs your opponent rapidly three times.</t>
+        </is>
+      </c>
     </row>
     <row r="2258" ht="15" hidden="0" customHeight="1">
       <c r="A2258" s="38" t="str">
@@ -56963,8 +57975,16 @@
       <c r="G2260" s="39" t="str">
         <v>效果中，自身物理攻擊命中時有一定機率使目標落馬</v>
       </c>
-      <c r="H2260" s="40" t="str"/>
-      <c r="I2260" s="143" t="str"/>
+      <c r="H2260" t="inlineStr" s="40">
+        <is>
+          <t>Вероятность сбросить противника с коня, атакуя его.</t>
+        </is>
+      </c>
+      <c r="I2260" t="inlineStr" s="143">
+        <is>
+          <t>While under this effect, there is a chance to inflict the Unseat effect when you strike with a physical attack.</t>
+        </is>
+      </c>
     </row>
     <row r="2261" ht="15" hidden="0" customHeight="1">
       <c r="A2261" s="38" t="str">
@@ -57038,8 +58058,16 @@
       <c r="G2263" s="39" t="str">
         <v>用力將長槍投擲出去，攻擊遠處的敵人</v>
       </c>
-      <c r="H2263" s="40" t="str"/>
-      <c r="I2263" s="143" t="str"/>
+      <c r="H2263" t="inlineStr" s="40">
+        <is>
+          <t>Метание копья в противника.</t>
+        </is>
+      </c>
+      <c r="I2263" t="inlineStr" s="143">
+        <is>
+          <t>Hurls your spear to attack a distant enemy.</t>
+        </is>
+      </c>
     </row>
     <row r="2264" ht="15" hidden="0" customHeight="1">
       <c r="A2264" s="38" t="str">
@@ -57113,8 +58141,16 @@
       <c r="G2266" s="39" t="str">
         <v>連續高速四次刺殺，三連刺僵硬狀態下使用，增加威力</v>
       </c>
-      <c r="H2266" s="40" t="str"/>
-      <c r="I2266" s="143" t="str"/>
+      <c r="H2266" t="inlineStr" s="40">
+        <is>
+          <t>Четверная колющая атака. В сочетании с Тройным уколом урон увеличивается.</t>
+        </is>
+      </c>
+      <c r="I2266" t="inlineStr" s="143">
+        <is>
+          <t>You stab at your opponent rapidly four times. If you use it while you're activating Triple Stab, your damage will increase.</t>
+        </is>
+      </c>
     </row>
     <row r="2267" ht="15" hidden="0" customHeight="1">
       <c r="A2267" s="38" t="str">
@@ -57188,8 +58224,16 @@
       <c r="G2269" s="39" t="str">
         <v>對手騎乘狀態時，造成傷害增加，有一定機率使其落馬</v>
       </c>
-      <c r="H2269" s="40" t="str"/>
-      <c r="I2269" s="143" t="str"/>
+      <c r="H2269" t="inlineStr" s="40">
+        <is>
+          <t>Урон увеличивается, когда противник на коне. Появляется вероятность сбросить его.</t>
+        </is>
+      </c>
+      <c r="I2269" t="inlineStr" s="143">
+        <is>
+          <t>When your opponent is mounted, your damage will increase and you are granted a chance to Unseat them.</t>
+        </is>
+      </c>
     </row>
     <row r="2270" ht="15" hidden="0" customHeight="1">
       <c r="A2270" s="38" t="str">
@@ -57263,8 +58307,16 @@
       <c r="G2272" s="39" t="str">
         <v>待機蓄力，發生會心一擊</v>
       </c>
-      <c r="H2272" s="40" t="str"/>
-      <c r="I2272" s="143" t="str"/>
+      <c r="H2272" t="inlineStr" s="40">
+        <is>
+          <t>Критический удар по противнику.</t>
+        </is>
+      </c>
+      <c r="I2272" t="inlineStr" s="143">
+        <is>
+          <t>Performs a furious attack in an attempt to land a Critical Hit.</t>
+        </is>
+      </c>
     </row>
     <row r="2273" ht="15" hidden="0" customHeight="1">
       <c r="A2273" s="38" t="str">
@@ -57338,8 +58390,16 @@
       <c r="G2275" s="39" t="str">
         <v>化解對手的攻擊，並且反擊</v>
       </c>
-      <c r="H2275" s="40" t="str"/>
-      <c r="I2275" s="143" t="str"/>
+      <c r="H2275" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет избежать атаки противника и нанести ответный удар.</t>
+        </is>
+      </c>
+      <c r="I2275" t="inlineStr" s="143">
+        <is>
+          <t>Knocks aside your opponent's attack, allowing you to follow up with a counter-attack.</t>
+        </is>
+      </c>
     </row>
     <row r="2276" ht="15" hidden="0" customHeight="1">
       <c r="A2276" s="38" t="str">
@@ -57413,8 +58473,16 @@
       <c r="G2278" s="39" t="str">
         <v>通過對聖經的鑽研，使暴擊機率上升</v>
       </c>
-      <c r="H2278" s="40" t="str"/>
-      <c r="I2278" s="143" t="str"/>
+      <c r="H2278" t="inlineStr" s="40">
+        <is>
+          <t>Укрепляет нервы, повышая вероятность критического удара.</t>
+        </is>
+      </c>
+      <c r="I2278" t="inlineStr" s="143">
+        <is>
+          <t>Sharpens your nerves and increases your chance to land a Critical Hit.</t>
+        </is>
+      </c>
     </row>
     <row r="2279" ht="15" hidden="0" customHeight="1">
       <c r="A2279" s="38" t="str">
@@ -57488,7 +58556,11 @@
       <c r="G2281" s="39" t="str">
         <v>用斧切開地面，向自己前方攻擊</v>
       </c>
-      <c r="H2281" s="40" t="str"/>
+      <c r="H2281" t="inlineStr" s="40">
+        <is>
+          <t>Прямая атака, при которой топор врезается в землю.</t>
+        </is>
+      </c>
       <c r="I2281" s="143" t="str"/>
     </row>
     <row r="2282" ht="15" hidden="0" customHeight="1">
@@ -57563,8 +58635,16 @@
       <c r="G2284" s="39" t="str">
         <v>給予目標暴力一擊，使其進入暈眩狀態。攻擊失敗或被格擋時自身受到傷害</v>
       </c>
-      <c r="H2284" s="40" t="str"/>
-      <c r="I2284" s="143" t="str"/>
+      <c r="H2284" t="inlineStr" s="40">
+        <is>
+          <t>Оглушающая атака. Если противник отбивает или блокирует атаку, атакующий получает урон.</t>
+        </is>
+      </c>
+      <c r="I2284" t="inlineStr" s="143">
+        <is>
+          <t>Strikes your opponent with a mighty attack that Stuns them. If your attack fails or is blocked, the effect is reversed.</t>
+        </is>
+      </c>
     </row>
     <row r="2285" ht="15" hidden="0" customHeight="1">
       <c r="A2285" s="38" t="str">
@@ -57638,8 +58718,16 @@
       <c r="G2287" s="39" t="str">
         <v>通過強力打擊使對手暈眩</v>
       </c>
-      <c r="H2287" s="40" t="str"/>
-      <c r="I2287" s="143" t="str"/>
+      <c r="H2287" t="inlineStr" s="40">
+        <is>
+          <t>Сильный удар, который оглушает противника.</t>
+        </is>
+      </c>
+      <c r="I2287" t="inlineStr" s="143">
+        <is>
+          <t>Stuns your opponent with a powerful strike.</t>
+        </is>
+      </c>
     </row>
     <row r="2288" ht="15" hidden="0" customHeight="1">
       <c r="A2288" s="38" t="str">
@@ -57713,8 +58801,16 @@
       <c r="G2290" s="39" t="str">
         <v>強力擊打地面，給予前方目標傷害，並造成吟唱中斷</v>
       </c>
-      <c r="H2290" s="40" t="str"/>
-      <c r="I2290" s="143" t="str"/>
+      <c r="H2290" t="inlineStr" s="40">
+        <is>
+          <t>Мощный удар в землю, передающийся стоящему впереди противнику и прерывающий его умения.</t>
+        </is>
+      </c>
+      <c r="I2290" t="inlineStr" s="143">
+        <is>
+          <t>Strikes the ground hard, damaging your opponent with a shockwave that interrupts their spellcasting.</t>
+        </is>
+      </c>
     </row>
     <row r="2291" ht="15" hidden="0" customHeight="1">
       <c r="A2291" s="38" t="str">
@@ -57788,8 +58884,16 @@
       <c r="G2293" s="39" t="str">
         <v>強烈擊打地面，通過強大的地面振動使周圍的敵人暈眩</v>
       </c>
-      <c r="H2293" s="40" t="str"/>
-      <c r="I2293" s="143" t="str"/>
+      <c r="H2293" t="inlineStr" s="40">
+        <is>
+          <t>Наносимый с огромной силой удар в землю оглушает окружающих противников.</t>
+        </is>
+      </c>
+      <c r="I2293" t="inlineStr" s="143">
+        <is>
+          <t>Strikes the ground hard and Stuns your surrounding enemies with the resulting shockwaves.</t>
+        </is>
+      </c>
     </row>
     <row r="2294" ht="15" hidden="0" customHeight="1">
       <c r="A2294" s="38" t="str">
@@ -57863,8 +58967,16 @@
       <c r="G2296" s="39" t="str">
         <v>用力一擊，解除對象的鎧甲，中斷吟唱</v>
       </c>
-      <c r="H2296" s="40" t="str"/>
-      <c r="I2296" s="143" t="str"/>
+      <c r="H2296" t="inlineStr" s="40">
+        <is>
+          <t>Атака, при которой имеется шанс лишить противника брони, а также прервать применение его умения.</t>
+        </is>
+      </c>
+      <c r="I2296" t="inlineStr" s="143">
+        <is>
+          <t>Knocks your opponent's armor off with a powerful attack, and interrupts their spellcasting.</t>
+        </is>
+      </c>
     </row>
     <row r="2297" ht="15" hidden="0" customHeight="1">
       <c r="A2297" s="38" t="str">
@@ -57938,8 +59050,16 @@
       <c r="G2299" s="39" t="str">
         <v>？？？</v>
       </c>
-      <c r="H2299" s="40" t="str"/>
-      <c r="I2299" s="143" t="str"/>
+      <c r="H2299" t="inlineStr" s="40">
+        <is>
+          <t>Мощный удар, позволяющий сломать щит и нанести критический удар блокирующему противнику.</t>
+        </is>
+      </c>
+      <c r="I2299" t="inlineStr" s="143">
+        <is>
+          <t>When your opponent is Blocking, you will inflict a Critical Hit and prevent them from using a shield.</t>
+        </is>
+      </c>
     </row>
     <row r="2300" ht="15" hidden="0" customHeight="1">
       <c r="A2300" s="38" t="str">
@@ -58013,8 +59133,16 @@
       <c r="G2302" s="39" t="str">
         <v>？？？</v>
       </c>
-      <c r="H2302" s="40" t="str"/>
-      <c r="I2302" s="143" t="str"/>
+      <c r="H2302" t="inlineStr" s="40">
+        <is>
+          <t>Мощный энергетический удар. Чем выше защита противника, тем больше урон.</t>
+        </is>
+      </c>
+      <c r="I2302" t="inlineStr" s="143">
+        <is>
+          <t>Destroys your opponent from within. The higher their Defense, the more damage they take.</t>
+        </is>
+      </c>
     </row>
     <row r="2303" ht="15" hidden="0" customHeight="1">
       <c r="A2303" s="38" t="str">
@@ -58088,7 +59216,11 @@
       <c r="G2305" s="39" t="str">
         <v>格擋狀態下，受到蓄力攻擊時，反彈傷害</v>
       </c>
-      <c r="H2305" s="40" t="str"/>
+      <c r="H2305" t="inlineStr" s="40">
+        <is>
+          <t>При использовании умения 'Блокирование' урон, нанесенный атакой типа 'Напор', возвращается противнику.</t>
+        </is>
+      </c>
       <c r="I2305" s="143" t="str"/>
     </row>
     <row r="2306" ht="15" hidden="0" customHeight="1">
@@ -58163,8 +59295,16 @@
       <c r="G2308" s="39" t="str">
         <v>格擋姿態時，可以防禦魔法傷害，不會被擊退</v>
       </c>
-      <c r="H2308" s="40" t="str"/>
-      <c r="I2308" s="143" t="str"/>
+      <c r="H2308" t="inlineStr" s="40">
+        <is>
+          <t>При использовании умения 'Блокирование' отражается и урон, наносимый магическими атаками.</t>
+        </is>
+      </c>
+      <c r="I2308" t="inlineStr" s="143">
+        <is>
+          <t>When using the Blocking, the damage caused by magic attacks is also reflected.</t>
+        </is>
+      </c>
     </row>
     <row r="2309" ht="15" hidden="0" customHeight="1">
       <c r="A2309" s="38" t="str">
@@ -58238,8 +59378,16 @@
       <c r="G2311" s="39" t="str">
         <v>解除防禦中的行動限制</v>
       </c>
-      <c r="H2311" s="40" t="str"/>
-      <c r="I2311" s="143" t="str"/>
+      <c r="H2311" t="inlineStr" s="40">
+        <is>
+          <t>Снимается ограничение движения во время действия умения 'Защита в движении'.</t>
+        </is>
+      </c>
+      <c r="I2311" t="inlineStr" s="143">
+        <is>
+          <t>Your limits when in Defensive March are released.</t>
+        </is>
+      </c>
     </row>
     <row r="2312" ht="15" hidden="0" customHeight="1">
       <c r="A2312" s="38" t="str">
@@ -58313,8 +59461,16 @@
       <c r="G2314" s="39" t="str">
         <v>迅速舉盾，大幅減少物理傷害</v>
       </c>
-      <c r="H2314" s="40" t="str"/>
-      <c r="I2314" s="143" t="str"/>
+      <c r="H2314" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет быстро подставить щит, чтобы существенно уменьшить физический урон от атаки.</t>
+        </is>
+      </c>
+      <c r="I2314" t="inlineStr" s="143">
+        <is>
+          <t>Quickly raises your shield, greatly reducing the amount of physical damage you take.</t>
+        </is>
+      </c>
     </row>
     <row r="2315" ht="15" hidden="0" customHeight="1">
       <c r="A2315" s="38" t="str">
@@ -58388,8 +59544,16 @@
       <c r="G2317" s="39" t="str">
         <v>只可在格檔姿態中使用，盾防禦同時，給予目標強力反擊</v>
       </c>
-      <c r="H2317" s="40" t="str"/>
-      <c r="I2317" s="143" t="str"/>
+      <c r="H2317" t="inlineStr" s="40">
+        <is>
+          <t>При блокировании атаки позволяет сбить противника с ног.</t>
+        </is>
+      </c>
+      <c r="I2317" t="inlineStr" s="143">
+        <is>
+          <t>When you are Blocking with your shield, strike back with a powerful blow.</t>
+        </is>
+      </c>
     </row>
     <row r="2318" ht="15" hidden="0" customHeight="1">
       <c r="A2318" s="38" t="str">
@@ -58463,8 +59627,16 @@
       <c r="G2320" s="39" t="str">
         <v>閃避率下降，但能夠避開緊急情況，不易受到暴擊</v>
       </c>
-      <c r="H2320" s="40" t="str"/>
-      <c r="I2320" s="143" t="str"/>
+      <c r="H2320" t="inlineStr" s="40">
+        <is>
+          <t>Ухудшает уклонение, но увеличивает защиту от критических ударов.</t>
+        </is>
+      </c>
+      <c r="I2320" t="inlineStr" s="143">
+        <is>
+          <t>Your Dodge goes down, but you also become harder to hit with a Critical Hit.</t>
+        </is>
+      </c>
     </row>
     <row r="2321" ht="15" hidden="0" customHeight="1">
       <c r="A2321" s="38" t="str">
@@ -58538,8 +59710,16 @@
       <c r="G2323" s="39" t="str">
         <v>熟練用盾進行攻擊，行動中也能夠自動防禦攻擊</v>
       </c>
-      <c r="H2323" s="40" t="str"/>
-      <c r="I2323" s="143" t="str"/>
+      <c r="H2323" t="inlineStr" s="40">
+        <is>
+          <t>Щит позволяет с определенной вероятностью блокировать удар противника.</t>
+        </is>
+      </c>
+      <c r="I2323" t="inlineStr" s="143">
+        <is>
+          <t>Automatically defends against attacks as you move.</t>
+        </is>
+      </c>
     </row>
     <row r="2324" ht="15" hidden="0" customHeight="1">
       <c r="A2324" s="38" t="str">
@@ -58613,8 +59793,16 @@
       <c r="G2326" s="39" t="str">
         <v>只能在格檔中使用。拿著盾往前衝刺，驅散前方的敵人</v>
       </c>
-      <c r="H2326" s="40" t="str"/>
-      <c r="I2326" s="143" t="str"/>
+      <c r="H2326" t="inlineStr" s="40">
+        <is>
+          <t>Взмах щитом, дающий шанс сбить противника с ног (только при блокировании).</t>
+        </is>
+      </c>
+      <c r="I2326" t="inlineStr" s="143">
+        <is>
+          <t>Only usable while you are Blocking. You raise your shield and charge forward, knocking aside enemies in your way.</t>
+        </is>
+      </c>
     </row>
     <row r="2327" ht="15" hidden="0" customHeight="1">
       <c r="A2327" s="38" t="str">
@@ -58688,8 +59876,16 @@
       <c r="G2329" s="39" t="str">
         <v>可舉盾推進</v>
       </c>
-      <c r="H2329" s="40" t="str"/>
-      <c r="I2329" s="143" t="str"/>
+      <c r="H2329" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет продвигаться вперед, блокируя удары щитом.</t>
+        </is>
+      </c>
+      <c r="I2329" t="inlineStr" s="143">
+        <is>
+          <t>Allows you to move while your shield is raised.</t>
+        </is>
+      </c>
     </row>
     <row r="2330" ht="15" hidden="0" customHeight="1">
       <c r="A2330" s="38" t="str">
@@ -58763,8 +59959,16 @@
       <c r="G2332" s="39" t="str">
         <v>承受某位隊伍成員所受到的傷害</v>
       </c>
-      <c r="H2332" s="40" t="str"/>
-      <c r="I2332" s="143" t="str"/>
+      <c r="H2332" t="inlineStr" s="40">
+        <is>
+          <t>Игрок принимает на себя урон, наносимый одному из игроков в группе.</t>
+        </is>
+      </c>
+      <c r="I2332" t="inlineStr" s="143">
+        <is>
+          <t>Allows you to take damage in place of another party member.</t>
+        </is>
+      </c>
     </row>
     <row r="2333" ht="15" hidden="0" customHeight="1">
       <c r="A2333" s="38" t="str">
@@ -58838,7 +60042,11 @@
       <c r="G2335" s="39" t="str">
         <v>承受隊伍成員所受到的傷害，最多3人</v>
       </c>
-      <c r="H2335" s="40" t="str"/>
+      <c r="H2335" t="inlineStr" s="40">
+        <is>
+          <t>Игрок принимает на себя урон, получаемый другими игроками (до трех игроков одновременно).</t>
+        </is>
+      </c>
       <c r="I2335" s="143" t="str"/>
     </row>
     <row r="2336" ht="15" hidden="0" customHeight="1">
@@ -58913,8 +60121,16 @@
       <c r="G2338" s="39" t="str">
         <v>在範圍內的玩家不能使用技能</v>
       </c>
-      <c r="H2338" s="40" t="str"/>
-      <c r="I2338" s="143" t="str"/>
+      <c r="H2338" t="inlineStr" s="40">
+        <is>
+          <t>Игроки в радиусе действия не смогут применять умения.</t>
+        </is>
+      </c>
+      <c r="I2338" t="inlineStr" s="143">
+        <is>
+          <t>Prevents players in the area of effect from using skills.</t>
+        </is>
+      </c>
     </row>
     <row r="2339" ht="15" hidden="0" customHeight="1">
       <c r="A2339" s="38" t="str">
@@ -58988,8 +60204,16 @@
       <c r="G2341" s="39" t="str">
         <v>用如同鷹一般銳利的眼四處張望，使命中率上升</v>
       </c>
-      <c r="H2341" s="40" t="str"/>
-      <c r="I2341" s="143" t="str"/>
+      <c r="H2341" t="inlineStr" s="40">
+        <is>
+          <t>Увеличение точности за счет улучшения зрения.</t>
+        </is>
+      </c>
+      <c r="I2341" t="inlineStr" s="143">
+        <is>
+          <t>Grants you the power to survey the area with the watchful eye of a hawk, increasing your Accuracy and Attack Speed.</t>
+        </is>
+      </c>
     </row>
     <row r="2342" ht="15" hidden="0" customHeight="1">
       <c r="A2342" s="38" t="str">
@@ -59063,8 +60287,16 @@
       <c r="G2344" s="39" t="str">
         <v>可以看到敵人快速的動作並且預防，使迴避上升</v>
       </c>
-      <c r="H2344" s="40" t="str"/>
-      <c r="I2344" s="143" t="str"/>
+      <c r="H2344" t="inlineStr" s="40">
+        <is>
+          <t>Улучшает уклонение игрока.</t>
+        </is>
+      </c>
+      <c r="I2344" t="inlineStr" s="143">
+        <is>
+          <t>Increases your Dodge.</t>
+        </is>
+      </c>
     </row>
     <row r="2345" ht="15" hidden="0" customHeight="1">
       <c r="A2345" s="38" t="str">
@@ -59138,8 +60370,16 @@
       <c r="G2347" s="39" t="str">
         <v>藉由封的祝福，迎著順風，使自身移動速度增加</v>
       </c>
-      <c r="H2347" s="40" t="str"/>
-      <c r="I2347" s="143" t="str"/>
+      <c r="H2347" t="inlineStr" s="40">
+        <is>
+          <t>Благословение ветра повышает скорость передвижения.</t>
+        </is>
+      </c>
+      <c r="I2347" t="inlineStr" s="143">
+        <is>
+          <t>Grants you the blessing of the wind, increasing your Movement Speed.</t>
+        </is>
+      </c>
     </row>
     <row r="2348" ht="15" hidden="0" customHeight="1">
       <c r="A2348" s="38" t="str">
@@ -59213,8 +60453,16 @@
       <c r="G2350" s="39" t="str">
         <v>使隊伍成員全員命中率增加</v>
       </c>
-      <c r="H2350" s="40" t="str"/>
-      <c r="I2350" s="143" t="str"/>
+      <c r="H2350" t="inlineStr" s="40">
+        <is>
+          <t>Повышает точность всех игроков в группе.</t>
+        </is>
+      </c>
+      <c r="I2350" t="inlineStr" s="143">
+        <is>
+          <t>Increases the Accuracy of all party members.</t>
+        </is>
+      </c>
     </row>
     <row r="2351" ht="15" hidden="0" customHeight="1">
       <c r="A2351" s="38" t="str">
@@ -59288,8 +60536,16 @@
       <c r="G2353" s="39" t="str">
         <v>障眼法時即使設置了陷阱，也不接觸隱身狀態</v>
       </c>
-      <c r="H2353" s="40" t="str"/>
-      <c r="I2353" s="143" t="str"/>
+      <c r="H2353" t="inlineStr" s="40">
+        <is>
+          <t>Действие невидимости не прекращается, когда игрок устанавливает ловушку, одновременно используя умение 'Маскировка'.</t>
+        </is>
+      </c>
+      <c r="I2353" t="inlineStr" s="143">
+        <is>
+          <t>Prevents you from dropping out of the Hiding state after striking an enemy.</t>
+        </is>
+      </c>
     </row>
     <row r="2354" ht="15" hidden="0" customHeight="1">
       <c r="A2354" s="38" t="str">
@@ -59363,8 +60619,16 @@
       <c r="G2356" s="39" t="str">
         <v>能夠以快速的動作使弩連射</v>
       </c>
-      <c r="H2356" s="40" t="str"/>
-      <c r="I2356" s="143" t="str"/>
+      <c r="H2356" t="inlineStr" s="40">
+        <is>
+          <t>Быстрая стрельба из арбалета.</t>
+        </is>
+      </c>
+      <c r="I2356" t="inlineStr" s="143">
+        <is>
+          <t>Allows you to fire bolts in rapid succession by darting about.</t>
+        </is>
+      </c>
     </row>
     <row r="2357" ht="15" hidden="0" customHeight="1">
       <c r="A2357" s="38" t="str">
@@ -59438,8 +60702,16 @@
       <c r="G2359" s="39" t="str">
         <v>攻擊力、命中、射程增加，但不可移動。再一次使用後效果消失</v>
       </c>
-      <c r="H2359" s="40" t="str"/>
-      <c r="I2359" s="143" t="str"/>
+      <c r="H2359" t="inlineStr" s="40">
+        <is>
+          <t>Сила атаки/концентрации/колющего удара увеличивается, но движение прекращается. Может использоваться один раз.</t>
+        </is>
+      </c>
+      <c r="I2359" t="inlineStr" s="143">
+        <is>
+          <t>Attack Power, Accuracy, and ranged attack distance increase, but unable to move. Toggle on/off for effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2360" ht="15" hidden="0" customHeight="1">
       <c r="A2360" s="38" t="str">
@@ -59513,8 +60785,16 @@
       <c r="G2362" s="39" t="str">
         <v>用火箭使目標的地點燃燒，形成火系區域</v>
       </c>
-      <c r="H2362" s="40" t="str"/>
-      <c r="I2362" s="143" t="str"/>
+      <c r="H2362" t="inlineStr" s="40">
+        <is>
+          <t>Стрела сжигает цель, создавая вокруг нее поле огня.</t>
+        </is>
+      </c>
+      <c r="I2362" t="inlineStr" s="143">
+        <is>
+          <t>Sets the area of effect ablaze with a fiery arrow, creating a field of flame.</t>
+        </is>
+      </c>
     </row>
     <row r="2363" ht="15" hidden="0" customHeight="1">
       <c r="A2363" s="38" t="str">
@@ -59588,8 +60868,16 @@
       <c r="G2365" s="39" t="str">
         <v>能夠看到視野內隱身狀態的敵人，增加傷害，但不能移動</v>
       </c>
-      <c r="H2365" s="40" t="str"/>
-      <c r="I2365" s="143" t="str"/>
+      <c r="H2365" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет видеть скрывающихся врагов. Урон увеличивается, но двигаться при этом нельзя.</t>
+        </is>
+      </c>
+      <c r="I2365" t="inlineStr" s="143">
+        <is>
+          <t>Allows you to spot Hiding enemies within your area of effect. Your damage against them increases, but you are unable to move.</t>
+        </is>
+      </c>
     </row>
     <row r="2366" ht="15" hidden="0" customHeight="1">
       <c r="A2366" s="38" t="str">
@@ -59663,8 +60951,16 @@
       <c r="G2368" s="39" t="str">
         <v>使用弩時射程增加，並觸發2連射</v>
       </c>
-      <c r="H2368" s="40" t="str"/>
-      <c r="I2368" s="143" t="str"/>
+      <c r="H2368" t="inlineStr" s="40">
+        <is>
+          <t>Двойной выстрел из арбалета с увеличенным радиусом действия.</t>
+        </is>
+      </c>
+      <c r="I2368" t="inlineStr" s="143">
+        <is>
+          <t>Using a crossbow increases range and grants the ability to fire twice in a row</t>
+        </is>
+      </c>
     </row>
     <row r="2369" ht="15" hidden="0" customHeight="1">
       <c r="A2369" s="38" t="str">
@@ -59738,8 +61034,16 @@
       <c r="G2371" s="39" t="str">
         <v>放出火箭</v>
       </c>
-      <c r="H2371" s="40" t="str"/>
-      <c r="I2371" s="143" t="str"/>
+      <c r="H2371" t="inlineStr" s="40">
+        <is>
+          <t>Выстрел горящей стрелой, наносящий двойной урон.</t>
+        </is>
+      </c>
+      <c r="I2371" t="inlineStr" s="143">
+        <is>
+          <t>Fires a flaming arrow that deals double damage.</t>
+        </is>
+      </c>
     </row>
     <row r="2372" ht="15" hidden="0" customHeight="1">
       <c r="A2372" s="38" t="str">
@@ -59813,8 +61117,16 @@
       <c r="G2374" s="39" t="str">
         <v>放出毒箭，付與目標中毒效果</v>
       </c>
-      <c r="H2374" s="40" t="str"/>
-      <c r="I2374" s="143" t="str"/>
+      <c r="H2374" t="inlineStr" s="40">
+        <is>
+          <t>Выстрел отравленной стрелой, противник страдает от яда.</t>
+        </is>
+      </c>
+      <c r="I2374" t="inlineStr" s="143">
+        <is>
+          <t>Fires a venomous arrow, Poisoning your opponent.</t>
+        </is>
+      </c>
     </row>
     <row r="2375" ht="15" hidden="0" customHeight="1">
       <c r="A2375" s="38" t="str">
@@ -59888,8 +61200,16 @@
       <c r="G2377" s="39" t="str">
         <v>朝天空放箭，像雨一樣落向目的地區域</v>
       </c>
-      <c r="H2377" s="40" t="str"/>
-      <c r="I2377" s="143" t="str"/>
+      <c r="H2377" t="inlineStr" s="40">
+        <is>
+          <t>На противников в пределах радиуса действия обрушивается множество стрел.</t>
+        </is>
+      </c>
+      <c r="I2377" t="inlineStr" s="143">
+        <is>
+          <t>Aims for a point in the air and unleashes a rain of arrows in the area of effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2378" ht="15" hidden="0" customHeight="1">
       <c r="A2378" s="38" t="str">
@@ -59963,8 +61283,16 @@
       <c r="G2380" s="39" t="str">
         <v>箭像風暴一樣落到物件地點，造成連續傷害</v>
       </c>
-      <c r="H2380" s="40" t="str"/>
-      <c r="I2380" s="143" t="str"/>
+      <c r="H2380" t="inlineStr" s="40">
+        <is>
+          <t>Ураган стрел, наносящий продолжительный урон.</t>
+        </is>
+      </c>
+      <c r="I2380" t="inlineStr" s="143">
+        <is>
+          <t>Unleashes a storm of arrows on the area of effect, inflicting continuous damage.</t>
+        </is>
+      </c>
     </row>
     <row r="2381" ht="15" hidden="0" customHeight="1">
       <c r="A2381" s="38" t="str">
@@ -60038,8 +61366,16 @@
       <c r="G2383" s="39" t="str">
         <v>能夠同時向5個方向射箭</v>
       </c>
-      <c r="H2383" s="40" t="str"/>
-      <c r="I2383" s="143" t="str"/>
+      <c r="H2383" t="inlineStr" s="40">
+        <is>
+          <t>Одновременный выстрел в пяти разных направлениях.</t>
+        </is>
+      </c>
+      <c r="I2383" t="inlineStr" s="143">
+        <is>
+          <t>Fires arrows in five directions at once.</t>
+        </is>
+      </c>
     </row>
     <row r="2384" ht="15" hidden="0" customHeight="1">
       <c r="A2384" s="38" t="str">
@@ -60113,8 +61449,16 @@
       <c r="G2386" s="39" t="str">
         <v>放出擊退目標的強力箭</v>
       </c>
-      <c r="H2386" s="40" t="str"/>
-      <c r="I2386" s="143" t="str"/>
+      <c r="H2386" t="inlineStr" s="40">
+        <is>
+          <t>Мощный выстрел, который отбрасывает противника назад.</t>
+        </is>
+      </c>
+      <c r="I2386" t="inlineStr" s="143">
+        <is>
+          <t>Fires a powerful arrow that will Knockback your target.</t>
+        </is>
+      </c>
     </row>
     <row r="2387" ht="15" hidden="0" customHeight="1">
       <c r="A2387" s="38" t="str">
@@ -60188,8 +61532,16 @@
       <c r="G2389" s="39" t="str">
         <v>使命中的目標變為沉默狀態，以一定機率使目標處於長期沉默</v>
       </c>
-      <c r="H2389" s="40" t="str"/>
-      <c r="I2389" s="143" t="str"/>
+      <c r="H2389" t="inlineStr" s="40">
+        <is>
+          <t>Насылает немоту. Есть вероятность того, что эффект будет более длительным.</t>
+        </is>
+      </c>
+      <c r="I2389" t="inlineStr" s="143">
+        <is>
+          <t>Fires an arrow that has a chance of inflicting the enemy with Silence.</t>
+        </is>
+      </c>
     </row>
     <row r="2390" ht="15" hidden="0" customHeight="1">
       <c r="A2390" s="38" t="str">
@@ -60263,8 +61615,16 @@
       <c r="G2392" s="39" t="str">
         <v>在目標背後發動攻擊時，施加定身效果，下次攻擊命中後，該效果解除</v>
       </c>
-      <c r="H2392" s="40" t="str"/>
-      <c r="I2392" s="143" t="str"/>
+      <c r="H2392" t="inlineStr" s="40">
+        <is>
+          <t>Удар в спину, обездвиживающий противника. Противник приходит в себя, если его атаковать.</t>
+        </is>
+      </c>
+      <c r="I2392" t="inlineStr" s="143">
+        <is>
+          <t>Immobilizes the enemy when struck from behind. A hit from another attack ends this effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2393" ht="15" hidden="0" customHeight="1">
       <c r="A2393" s="38" t="str">
@@ -60338,8 +61698,16 @@
       <c r="G2395" s="39" t="str">
         <v>消耗巨毒草、空瓶，製造毒藥</v>
       </c>
-      <c r="H2395" s="40" t="str"/>
-      <c r="I2395" s="143" t="str"/>
+      <c r="H2395" t="inlineStr" s="40">
+        <is>
+          <t>Создание яда (требуется ядовитый корень и пустая бутыль).</t>
+        </is>
+      </c>
+      <c r="I2395" t="inlineStr" s="143">
+        <is>
+          <t>Consumes a Deadly Nightshade and a Container to create Venom.</t>
+        </is>
+      </c>
     </row>
     <row r="2396" ht="15" hidden="0" customHeight="1">
       <c r="A2396" s="38" t="str">
@@ -60413,8 +61781,16 @@
       <c r="G2398" s="39" t="str">
         <v>消耗毒藥，在武器上塗抹毒藥</v>
       </c>
-      <c r="H2398" s="40" t="str"/>
-      <c r="I2398" s="143" t="str"/>
+      <c r="H2398" t="inlineStr" s="40">
+        <is>
+          <t>Отравляет оружие игрока с помощью ядовитого зелья.</t>
+        </is>
+      </c>
+      <c r="I2398" t="inlineStr" s="143">
+        <is>
+          <t>Consumes a Venom to coat your weapons.</t>
+        </is>
+      </c>
     </row>
     <row r="2399" ht="15" hidden="0" customHeight="1">
       <c r="A2399" s="38" t="str">
@@ -60488,8 +61864,16 @@
       <c r="G2401" s="39" t="str">
         <v>消耗解毒草、空瓶，製作解毒劑</v>
       </c>
-      <c r="H2401" s="40" t="str"/>
-      <c r="I2401" s="143" t="str"/>
+      <c r="H2401" t="inlineStr" s="40">
+        <is>
+          <t>Создание противоядия с использованием исцеляющего корня и пустой бутыли.</t>
+        </is>
+      </c>
+      <c r="I2401" t="inlineStr" s="143">
+        <is>
+          <t>Consumes an Antidote Herb and a Container to create an Antidote.</t>
+        </is>
+      </c>
     </row>
     <row r="2402" ht="15" hidden="0" customHeight="1">
       <c r="A2402" s="38" t="str">
@@ -60563,8 +61947,16 @@
       <c r="G2404" s="39" t="str">
         <v>消耗月光草、蓬萊花、空瓶，製作神祕的藥劑</v>
       </c>
-      <c r="H2404" s="40" t="str"/>
-      <c r="I2404" s="143" t="str"/>
+      <c r="H2404" t="inlineStr" s="40">
+        <is>
+          <t>Создание таинственного зелья (требуются лунный и огненный корень и пустая бутыль).</t>
+        </is>
+      </c>
+      <c r="I2404" t="inlineStr" s="143">
+        <is>
+          <t>Consumes a Moonlight Herb, an Aquilegia, and a Container to create a Mysterious Potion.</t>
+        </is>
+      </c>
     </row>
     <row r="2405" ht="15" hidden="0" customHeight="1">
       <c r="A2405" s="38" t="str">
@@ -60638,8 +62030,16 @@
       <c r="G2407" s="39" t="str">
         <v>攻擊命中時，對象為吟唱中時，減少吟唱速度，消費1個毒藥</v>
       </c>
-      <c r="H2407" s="40" t="str"/>
-      <c r="I2407" s="143" t="str"/>
+      <c r="H2407" t="inlineStr" s="40">
+        <is>
+          <t>Уменьшается скорость применения умений, если цель применяет умение в момент атаки. Используется одно ядовитое зелье.</t>
+        </is>
+      </c>
+      <c r="I2407" t="inlineStr" s="143">
+        <is>
+          <t>Slows down the Casting Speed of any opponent you strike with a physical attack. Consumes one Venom.</t>
+        </is>
+      </c>
     </row>
     <row r="2408" ht="15" hidden="0" customHeight="1">
       <c r="A2408" s="38" t="str">
@@ -60713,8 +62113,16 @@
       <c r="G2410" s="39" t="str">
         <v>增加涂毒時的屬性傷害</v>
       </c>
-      <c r="H2410" s="40" t="str"/>
-      <c r="I2410" s="143" t="str"/>
+      <c r="H2410" t="inlineStr" s="40">
+        <is>
+          <t>Урон, наносимый умением 'Яд', увеличивается.</t>
+        </is>
+      </c>
+      <c r="I2410" t="inlineStr" s="143">
+        <is>
+          <t>Increases Poison damage while Toxify is active.</t>
+        </is>
+      </c>
     </row>
     <row r="2411" ht="15" hidden="0" customHeight="1">
       <c r="A2411" s="38" t="str">
@@ -60788,8 +62196,16 @@
       <c r="G2413" s="39" t="str">
         <v>能夠看到敵人設置的陷阱</v>
       </c>
-      <c r="H2413" s="40" t="str"/>
-      <c r="I2413" s="143" t="str"/>
+      <c r="H2413" t="inlineStr" s="40">
+        <is>
+          <t>Видны ловушки врагов.</t>
+        </is>
+      </c>
+      <c r="I2413" t="inlineStr" s="143">
+        <is>
+          <t>Allows you to spot traps that your enemies have set.</t>
+        </is>
+      </c>
     </row>
     <row r="2414" ht="15" hidden="0" customHeight="1">
       <c r="A2414" s="38" t="str">
@@ -60863,8 +62279,16 @@
       <c r="G2416" s="39" t="str">
         <v>變為隱身狀態，可當場消失</v>
       </c>
-      <c r="H2416" s="40" t="str"/>
-      <c r="I2416" s="143" t="str"/>
+      <c r="H2416" t="inlineStr" s="40">
+        <is>
+          <t>Игрок замирает и становится невидимым.</t>
+        </is>
+      </c>
+      <c r="I2416" t="inlineStr" s="143">
+        <is>
+          <t>Enables you to camouflage your appearance where you stand.</t>
+        </is>
+      </c>
     </row>
     <row r="2417" ht="15" hidden="0" customHeight="1">
       <c r="A2417" s="38" t="str">
@@ -60938,8 +62362,16 @@
       <c r="G2419" s="39" t="str">
         <v>進入隱遁狀態，可以直接移動。隱遁狀態將持續消耗MP。</v>
       </c>
-      <c r="H2419" s="40" t="str"/>
-      <c r="I2419" s="143" t="str"/>
+      <c r="H2419" t="inlineStr" s="40">
+        <is>
+          <t>Игрок становится невидимым и может передвигаться, оставаясь незамеченным.</t>
+        </is>
+      </c>
+      <c r="I2419" t="inlineStr" s="143">
+        <is>
+          <t>Enables you to enter a Hiding state that allows movement.</t>
+        </is>
+      </c>
     </row>
     <row r="2420" ht="15" hidden="0" customHeight="1">
       <c r="A2420" s="38" t="str">
@@ -61013,8 +62445,16 @@
       <c r="G2422" s="39" t="str">
         <v>消除障眼法時的移動懲罰，魔力自動恢復</v>
       </c>
-      <c r="H2422" s="40" t="str"/>
-      <c r="I2422" s="143" t="str"/>
+      <c r="H2422" t="inlineStr" s="40">
+        <is>
+          <t>Нет замедление во время применения умения 'Маскировка'. Восстанавливает ОМ.</t>
+        </is>
+      </c>
+      <c r="I2422" t="inlineStr" s="143">
+        <is>
+          <t>Removes the Movement Speed reduction while Cloaking and slightly increases MP Recovery Rate.</t>
+        </is>
+      </c>
     </row>
     <row r="2423" ht="15" hidden="0" customHeight="1">
       <c r="A2423" s="38" t="str">
@@ -61088,8 +62528,16 @@
       <c r="G2425" s="39" t="str">
         <v>使用後格鬥武器時，會發動低威力的追加攻擊</v>
       </c>
-      <c r="H2425" s="40" t="str"/>
-      <c r="I2425" s="143" t="str"/>
+      <c r="H2425" t="inlineStr" s="40">
+        <is>
+          <t>Если игрок безоружен, за основной атакой следует еще одна, меньшая по силе.</t>
+        </is>
+      </c>
+      <c r="I2425" t="inlineStr" s="143">
+        <is>
+          <t>When using martial arts, you will strike with a weaker follow-up attack</t>
+        </is>
+      </c>
     </row>
     <row r="2426" ht="15" hidden="0" customHeight="1">
       <c r="A2426" s="38" t="str">
@@ -61163,8 +62611,16 @@
       <c r="G2428" s="39" t="str">
         <v>對於目標的背後給予強大的一擊</v>
       </c>
-      <c r="H2428" s="40" t="str"/>
-      <c r="I2428" s="143" t="str"/>
+      <c r="H2428" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет нанести противнику критический удар в спину.</t>
+        </is>
+      </c>
+      <c r="I2428" t="inlineStr" s="143">
+        <is>
+          <t>A powerful attack that targets your opponent's back.</t>
+        </is>
+      </c>
     </row>
     <row r="2429" ht="15" hidden="0" customHeight="1">
       <c r="A2429" s="38" t="str">
@@ -61238,8 +62694,16 @@
       <c r="G2431" s="39" t="str">
         <v>快速向敵人投擲匕首</v>
       </c>
-      <c r="H2431" s="40" t="str"/>
-      <c r="I2431" s="143" t="str"/>
+      <c r="H2431" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет быстро метнуть в противника кинжал.</t>
+        </is>
+      </c>
+      <c r="I2431" t="inlineStr" s="143">
+        <is>
+          <t>Quickly throws daggers at your opponent.</t>
+        </is>
+      </c>
     </row>
     <row r="2432" ht="15" hidden="0" customHeight="1">
       <c r="A2432" s="38" t="str">
@@ -61313,8 +62777,16 @@
       <c r="G2434" s="39" t="str">
         <v>不顧防禦，連續攻擊對手</v>
       </c>
-      <c r="H2434" s="40" t="str"/>
-      <c r="I2434" s="143" t="str"/>
+      <c r="H2434" t="inlineStr" s="40">
+        <is>
+          <t>Противнику наносится двойной удар.</t>
+        </is>
+      </c>
+      <c r="I2434" t="inlineStr" s="143">
+        <is>
+          <t>Each attack will hit twice, but damage taken will be increased.</t>
+        </is>
+      </c>
     </row>
     <row r="2435" ht="15" hidden="0" customHeight="1">
       <c r="A2435" s="38" t="str">
@@ -61388,8 +62860,16 @@
       <c r="G2437" s="39" t="str">
         <v>隱身狀態時可以使用，攻擊命中時不解除隱身狀態</v>
       </c>
-      <c r="H2437" s="40" t="str"/>
-      <c r="I2437" s="143" t="str"/>
+      <c r="H2437" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет сбить противника с ног. Используется только при невидимости. После атаки невидимость не снимается.</t>
+        </is>
+      </c>
+      <c r="I2437" t="inlineStr" s="143">
+        <is>
+          <t>Prevents you from dropping out of the Hiding state after striking the enemy.</t>
+        </is>
+      </c>
     </row>
     <row r="2438" ht="15" hidden="0" customHeight="1">
       <c r="A2438" s="38" t="str">
@@ -61463,8 +62943,16 @@
       <c r="G2440" s="39" t="str">
         <v>瞄準鎧甲的間隙突擊，對擊倒的目標有附加傷害效果</v>
       </c>
-      <c r="H2440" s="40" t="str"/>
-      <c r="I2440" s="143" t="str"/>
+      <c r="H2440" t="inlineStr" s="40">
+        <is>
+          <t>Атака, нацеленная на слабое место доспехов. Очень действенна, если противник сбит с ног.</t>
+        </is>
+      </c>
+      <c r="I2440" t="inlineStr" s="143">
+        <is>
+          <t>An attack that aims for openings in your opponent's armor. Especially effective against enemies affected by Trip.</t>
+        </is>
+      </c>
     </row>
     <row r="2441" ht="15" hidden="0" customHeight="1">
       <c r="A2441" s="38" t="str">
@@ -61538,8 +63026,16 @@
       <c r="G2443" s="39" t="str">
         <v>命中目標的背後時，該技能以外的技能冷卻時間全部解除</v>
       </c>
-      <c r="H2443" s="40" t="str"/>
-      <c r="I2443" s="143" t="str"/>
+      <c r="H2443" t="inlineStr" s="40">
+        <is>
+          <t>Если удар наносится в спину противнику, время перезарядки всех умений, кроме этого, снимается.</t>
+        </is>
+      </c>
+      <c r="I2443" t="inlineStr" s="143">
+        <is>
+          <t>After striking your opponent in the back, all Skill Cooldowns finish, excluding this one.</t>
+        </is>
+      </c>
     </row>
     <row r="2444" ht="15" hidden="0" customHeight="1">
       <c r="A2444" s="38" t="str">
@@ -61613,8 +63109,16 @@
       <c r="G2446" s="39" t="str">
         <v>無論敵我，將這一帶設置的陷阱全部解除</v>
       </c>
-      <c r="H2446" s="40" t="str"/>
-      <c r="I2446" s="143" t="str"/>
+      <c r="H2446" t="inlineStr" s="40">
+        <is>
+          <t>Обезвреживает все ловушки в радиусе действия (как вражеские, так и союзников).</t>
+        </is>
+      </c>
+      <c r="I2446" t="inlineStr" s="143">
+        <is>
+          <t>Disarms every trap in the area of effect, regardless of who set it.</t>
+        </is>
+      </c>
     </row>
     <row r="2447" ht="15" hidden="0" customHeight="1">
       <c r="A2447" s="38" t="str">
@@ -61688,8 +63192,16 @@
       <c r="G2449" s="39" t="str">
         <v>設置一個致殘陷阱，讓對方無法移動。消費1個陷阱</v>
       </c>
-      <c r="H2449" s="40" t="str"/>
-      <c r="I2449" s="143" t="str"/>
+      <c r="H2449" t="inlineStr" s="40">
+        <is>
+          <t>Обездвиживает противника. Используется одна ловушка.</t>
+        </is>
+      </c>
+      <c r="I2449" t="inlineStr" s="143">
+        <is>
+          <t>Sets a trap that grabs your opponent's legs and renders them immobile. This consumes one Trap.</t>
+        </is>
+      </c>
     </row>
     <row r="2450" ht="15" hidden="0" customHeight="1">
       <c r="A2450" s="38" t="str">
@@ -61763,8 +63275,16 @@
       <c r="G2452" s="39" t="str">
         <v>設置爆炸一整排的爆破陷阱，消費2個陷阱</v>
       </c>
-      <c r="H2452" s="40" t="str"/>
-      <c r="I2452" s="143" t="str"/>
+      <c r="H2452" t="inlineStr" s="40">
+        <is>
+          <t>Устанавливает ловушки, наносящие массовый урон. Используется одна ловушка.</t>
+        </is>
+      </c>
+      <c r="I2452" t="inlineStr" s="143">
+        <is>
+          <t>Sets a trap that explodes when stepped on, inflicting damage to the surrounding area. This consumes one Trap.</t>
+        </is>
+      </c>
     </row>
     <row r="2453" ht="15" hidden="0" customHeight="1">
       <c r="A2453" s="38" t="str">
@@ -61838,8 +63358,16 @@
       <c r="G2455" s="39" t="str">
         <v>設置爆炸一整排的爆破陷阱，消費2個陷阱</v>
       </c>
-      <c r="H2455" s="40" t="str"/>
-      <c r="I2455" s="143" t="str"/>
+      <c r="H2455" t="inlineStr" s="40">
+        <is>
+          <t>Живая бомба взрывается при столкновении с врагом. Используются две ловушки.</t>
+        </is>
+      </c>
+      <c r="I2455" t="inlineStr" s="143">
+        <is>
+          <t>Unleashes a worm that moves forward in a straight line, exploding whatever it touches. This consumes two Traps.</t>
+        </is>
+      </c>
     </row>
     <row r="2456" ht="15" hidden="0" customHeight="1">
       <c r="A2456" s="38" t="str">
@@ -61913,8 +63441,16 @@
       <c r="G2458" s="39" t="str">
         <v>在效果範圍內的玩家，使範圍技能效果失效</v>
       </c>
-      <c r="H2458" s="40" t="str"/>
-      <c r="I2458" s="143" t="str"/>
+      <c r="H2458" t="inlineStr" s="40">
+        <is>
+          <t>Действие всех умений игроков, попавших в радиус действия, прекращается.</t>
+        </is>
+      </c>
+      <c r="I2458" t="inlineStr" s="143">
+        <is>
+          <t>When a player enters the area of effect, any effects on them caused by Field Skills will be dispelled.</t>
+        </is>
+      </c>
     </row>
     <row r="2459" ht="15" hidden="0" customHeight="1">
       <c r="A2459" s="38" t="str">
@@ -61988,8 +63524,16 @@
       <c r="G2461" s="39" t="str">
         <v>只對馬產生效果，踏到的玩家周圍的4個方向出現牆壁</v>
       </c>
-      <c r="H2461" s="40" t="str"/>
-      <c r="I2461" s="143" t="str"/>
+      <c r="H2461" t="inlineStr" s="40">
+        <is>
+          <t>Создает стену, окружающую игрока. Действует только на всадников.</t>
+        </is>
+      </c>
+      <c r="I2461" t="inlineStr" s="143">
+        <is>
+          <t>Traps players behind a solid wall. Can only be triggered by mounted players. This consumes one Trap.</t>
+        </is>
+      </c>
     </row>
     <row r="2462" ht="15" hidden="0" customHeight="1">
       <c r="A2462" s="38" t="str">
@@ -62063,8 +63607,16 @@
       <c r="G2464" s="39" t="str">
         <v>設定一個減少對手MP的陷阱，消費1個陷阱</v>
       </c>
-      <c r="H2464" s="40" t="str"/>
-      <c r="I2464" s="143" t="str"/>
+      <c r="H2464" t="inlineStr" s="40">
+        <is>
+          <t>Ловушка, снижающая ОМ противника. Используется одна ловушка.</t>
+        </is>
+      </c>
+      <c r="I2464" t="inlineStr" s="143">
+        <is>
+          <t>Sets a trap that removes some of the target's MP. This consumes one Trap.</t>
+        </is>
+      </c>
     </row>
     <row r="2465" ht="15" hidden="0" customHeight="1">
       <c r="A2465" s="38" t="str">
@@ -62138,8 +63690,16 @@
       <c r="G2467" s="39" t="str">
         <v>增加自己的移動速度</v>
       </c>
-      <c r="H2467" s="40" t="str"/>
-      <c r="I2467" s="143" t="str"/>
+      <c r="H2467" t="inlineStr" s="40">
+        <is>
+          <t>Увеличивает скорость передвижения игрока.</t>
+        </is>
+      </c>
+      <c r="I2467" t="inlineStr" s="143">
+        <is>
+          <t>Increases your Movement Speed.</t>
+        </is>
+      </c>
     </row>
     <row r="2468" ht="15" hidden="0" customHeight="1">
       <c r="A2468" s="38" t="str">
@@ -62213,8 +63773,16 @@
       <c r="G2470" s="39" t="str">
         <v>快速地往後退</v>
       </c>
-      <c r="H2470" s="40" t="str"/>
-      <c r="I2470" s="143" t="str"/>
+      <c r="H2470" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет быстро сделать шаг назад.</t>
+        </is>
+      </c>
+      <c r="I2470" t="inlineStr" s="143">
+        <is>
+          <t>Quickly move backwards.</t>
+        </is>
+      </c>
     </row>
     <row r="2471" ht="15" hidden="0" customHeight="1">
       <c r="A2471" s="38" t="str">
@@ -62288,8 +63856,16 @@
       <c r="G2473" s="39" t="str">
         <v>瞬間提升腳力，能夠高速移動</v>
       </c>
-      <c r="H2473" s="40" t="str"/>
-      <c r="I2473" s="143" t="str"/>
+      <c r="H2473" t="inlineStr" s="40">
+        <is>
+          <t>Мгновенно увеличивает скорость.</t>
+        </is>
+      </c>
+      <c r="I2473" t="inlineStr" s="143">
+        <is>
+          <t>Momentarily increases your Movement Speed, allowing you to move very quickly.</t>
+        </is>
+      </c>
     </row>
     <row r="2474" ht="15" hidden="0" customHeight="1">
       <c r="A2474" s="38" t="str">
@@ -62363,8 +63939,16 @@
       <c r="G2476" s="39" t="str">
         <v>增加自己的閃避</v>
       </c>
-      <c r="H2476" s="40" t="str"/>
-      <c r="I2476" s="143" t="str"/>
+      <c r="H2476" t="inlineStr" s="40">
+        <is>
+          <t>Улучшает уклонение игрока.</t>
+        </is>
+      </c>
+      <c r="I2476" t="inlineStr" s="143">
+        <is>
+          <t>Increases your Dodge.</t>
+        </is>
+      </c>
     </row>
     <row r="2477" ht="15" hidden="0" customHeight="1">
       <c r="A2477" s="38" t="str">
@@ -62438,8 +64022,16 @@
       <c r="G2479" s="39" t="str">
         <v>減少目標命中率</v>
       </c>
-      <c r="H2479" s="40" t="str"/>
-      <c r="I2479" s="143" t="str"/>
+      <c r="H2479" t="inlineStr" s="40">
+        <is>
+          <t>Уменьшает точность противника.</t>
+        </is>
+      </c>
+      <c r="I2479" t="inlineStr" s="143">
+        <is>
+          <t>Reduces your opponent's Accuracy.</t>
+        </is>
+      </c>
     </row>
     <row r="2480" ht="15" hidden="0" customHeight="1">
       <c r="A2480" s="38" t="str">
@@ -62513,8 +64105,16 @@
       <c r="G2482" s="39" t="str">
         <v>擊倒抗性、暈眩抗性、凍傷抗性+15%</v>
       </c>
-      <c r="H2482" s="40" t="str"/>
-      <c r="I2482" s="143" t="str"/>
+      <c r="H2482" t="inlineStr" s="40">
+        <is>
+          <t>Устойчивость к падению, оглушению и заморозке +15.</t>
+        </is>
+      </c>
+      <c r="I2482" t="inlineStr" s="143">
+        <is>
+          <t>Trip Resistance, Stun Resistance, and Freeze Resistance +15%.</t>
+        </is>
+      </c>
     </row>
     <row r="2483" ht="15" hidden="0" customHeight="1">
       <c r="A2483" s="38" t="str">
@@ -62588,8 +64188,16 @@
       <c r="G2485" s="39" t="str">
         <v>效果時間中，增加閃避。受到2次物理攻擊後，效果結束</v>
       </c>
-      <c r="H2485" s="40" t="str"/>
-      <c r="I2485" s="143" t="str"/>
+      <c r="H2485" t="inlineStr" s="40">
+        <is>
+          <t>Улучшает уклонение. Действие прекращается, если игрок дважды получит урон.</t>
+        </is>
+      </c>
+      <c r="I2485" t="inlineStr" s="143">
+        <is>
+          <t>While this is in effect, your Dodge increases. The effect ends when you are hit by two physical attacks.</t>
+        </is>
+      </c>
     </row>
     <row r="2486" ht="15" hidden="0" customHeight="1">
       <c r="A2486" s="38" t="str">
@@ -62663,8 +64271,16 @@
       <c r="G2488" s="39" t="str">
         <v>一定機率閃避敵人的魔法</v>
       </c>
-      <c r="H2488" s="40" t="str"/>
-      <c r="I2488" s="143" t="str"/>
+      <c r="H2488" t="inlineStr" s="40">
+        <is>
+          <t>Способность с некоторой вероятностью уклоняться от магической атаки.</t>
+        </is>
+      </c>
+      <c r="I2488" t="inlineStr" s="143">
+        <is>
+          <t>Gives you a chance to evade your enemy's magic.</t>
+        </is>
+      </c>
     </row>
     <row r="2489" ht="15" hidden="0" customHeight="1">
       <c r="A2489" s="38" t="str">
@@ -62738,8 +64354,16 @@
       <c r="G2491" s="39" t="str">
         <v>對目標施加突進效果</v>
       </c>
-      <c r="H2491" s="40" t="str"/>
-      <c r="I2491" s="143" t="str"/>
+      <c r="H2491" t="inlineStr" s="40">
+        <is>
+          <t>Дает цели эффект порыва.</t>
+        </is>
+      </c>
+      <c r="I2491" t="inlineStr" s="143">
+        <is>
+          <t>The targeted player gains the Dash skill effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2492" ht="15" hidden="0" customHeight="1">
       <c r="A2492" s="38" t="str">
@@ -62813,8 +64437,16 @@
       <c r="G2494" s="39" t="str">
         <v>通過坐下狀態的深刻的精神統一來增加魔力的恢復量</v>
       </c>
-      <c r="H2494" s="40" t="str"/>
-      <c r="I2494" s="143" t="str"/>
+      <c r="H2494" t="inlineStr" s="40">
+        <is>
+          <t>Повышает скорость восстановления ОМ при сидении.</t>
+        </is>
+      </c>
+      <c r="I2494" t="inlineStr" s="143">
+        <is>
+          <t>Unifies your spirit and increases your MP Restore Rate.</t>
+        </is>
+      </c>
     </row>
     <row r="2495" ht="15" hidden="0" customHeight="1">
       <c r="A2495" s="38" t="str">
@@ -62888,8 +64520,16 @@
       <c r="G2497" s="39" t="str">
         <v>使感覺靈敏，提升靈感</v>
       </c>
-      <c r="H2497" s="40" t="str"/>
-      <c r="I2497" s="143" t="str"/>
+      <c r="H2497" t="inlineStr" s="40">
+        <is>
+          <t>Прилив вдохновения, повышающий силу духа.</t>
+        </is>
+      </c>
+      <c r="I2497" t="inlineStr" s="143">
+        <is>
+          <t>Increases your Spirit through honed senses.</t>
+        </is>
+      </c>
     </row>
     <row r="2498" ht="15" hidden="0" customHeight="1">
       <c r="A2498" s="38" t="str">
@@ -62963,8 +64603,16 @@
       <c r="G2500" s="39" t="str">
         <v>裝備光屬性裝備後，對於毒系、魅惑、秘法擁有抗性</v>
       </c>
-      <c r="H2500" s="40" t="str"/>
-      <c r="I2500" s="143" t="str"/>
+      <c r="H2500" t="inlineStr" s="40">
+        <is>
+          <t>Повышает сопротивляемость яду, чарам и магии при ношении снаряжения со святой аурой.</t>
+        </is>
+      </c>
+      <c r="I2500" t="inlineStr" s="143">
+        <is>
+          <t>When you wear equipment that has a Holy aura, you gain Resistance to Poison, Charm, and Magic.</t>
+        </is>
+      </c>
     </row>
     <row r="2501" ht="15" hidden="0" customHeight="1">
       <c r="A2501" s="38" t="str">
@@ -63188,8 +64836,16 @@
       <c r="G2509" s="39" t="str">
         <v>能夠恢復生命的治癒魔法</v>
       </c>
-      <c r="H2509" s="40" t="str"/>
-      <c r="I2509" s="143" t="str"/>
+      <c r="H2509" t="inlineStr" s="40">
+        <is>
+          <t>Целительная магия, восстанавливающая некоторое количество ОЗ.</t>
+        </is>
+      </c>
+      <c r="I2509" t="inlineStr" s="143">
+        <is>
+          <t>Restores your target's LP using healing magic.</t>
+        </is>
+      </c>
     </row>
     <row r="2510" ht="15" hidden="0" customHeight="1">
       <c r="A2510" s="38" t="str">
@@ -63263,8 +64919,16 @@
       <c r="G2512" s="39" t="str">
         <v>可以讓死亡的目標復活。消耗3個聖水</v>
       </c>
-      <c r="H2512" s="40" t="str"/>
-      <c r="I2512" s="143" t="str"/>
+      <c r="H2512" t="inlineStr" s="40">
+        <is>
+          <t>Воскрешает погибших союзников. Используется три бутыли святой воды.</t>
+        </is>
+      </c>
+      <c r="I2512" t="inlineStr" s="143">
+        <is>
+          <t>Revives someone who has been defeated in battle. This consumes three Holy Waters.</t>
+        </is>
+      </c>
     </row>
     <row r="2513" ht="15" hidden="0" customHeight="1">
       <c r="A2513" s="38" t="str">
@@ -63338,8 +65002,16 @@
       <c r="G2515" s="39" t="str">
         <v>能夠使範圍內的全部玩家的HP恢復</v>
       </c>
-      <c r="H2515" s="40" t="str"/>
-      <c r="I2515" s="143" t="str"/>
+      <c r="H2515" t="inlineStr" s="40">
+        <is>
+          <t>Создает святую область, в которой восстанавливаются ОМ всех игроков.</t>
+        </is>
+      </c>
+      <c r="I2515" t="inlineStr" s="143">
+        <is>
+          <t>Creates a consecrated area, restoring LP to all players within.</t>
+        </is>
+      </c>
     </row>
     <row r="2516" ht="15" hidden="0" customHeight="1">
       <c r="A2516" s="38" t="str">
@@ -63413,8 +65085,16 @@
       <c r="G2518" s="39" t="str">
         <v>通過強大的慈愛之力，能夠增強HP恢復技能的力量</v>
       </c>
-      <c r="H2518" s="40" t="str"/>
-      <c r="I2518" s="143" t="str"/>
+      <c r="H2518" t="inlineStr" s="40">
+        <is>
+          <t>Истинное великодушие позволяет восстанавливать ОЗ.</t>
+        </is>
+      </c>
+      <c r="I2518" t="inlineStr" s="143">
+        <is>
+          <t>True benevolence restores HP.</t>
+        </is>
+      </c>
     </row>
     <row r="2519" ht="15" hidden="0" customHeight="1">
       <c r="A2519" s="38" t="str">
@@ -63488,8 +65168,16 @@
       <c r="G2521" s="39" t="str">
         <v>使增益效果的祝福技能，效果範圍遍及自己周圍的己方全體人員</v>
       </c>
-      <c r="H2521" s="40" t="str"/>
-      <c r="I2521" s="143" t="str"/>
+      <c r="H2521" t="inlineStr" s="40">
+        <is>
+          <t>Все союзники в радиусе действия умения получают положительный эффект, который в данный момент действует на вас.</t>
+        </is>
+      </c>
+      <c r="I2521" t="inlineStr" s="143">
+        <is>
+          <t>Grants positive status effects to all allies within the area of effect. Toggle on/off for effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2522" ht="15" hidden="0" customHeight="1">
       <c r="A2522" s="38" t="str">
@@ -63563,8 +65251,16 @@
       <c r="G2524" s="39" t="str">
         <v>快速恢復目標少量生命值</v>
       </c>
-      <c r="H2524" s="40" t="str"/>
-      <c r="I2524" s="143" t="str"/>
+      <c r="H2524" t="inlineStr" s="40">
+        <is>
+          <t>Быстро восстанавливает небольшое количество ОЗ цели.</t>
+        </is>
+      </c>
+      <c r="I2524" t="inlineStr" s="143">
+        <is>
+          <t>Quickly heals a little bit of your target's LP.</t>
+        </is>
+      </c>
     </row>
     <row r="2525" ht="15" hidden="0" customHeight="1">
       <c r="A2525" s="38" t="str">
@@ -63638,8 +65334,16 @@
       <c r="G2527" s="39" t="str">
         <v>能夠清除目標毒素</v>
       </c>
-      <c r="H2527" s="40" t="str"/>
-      <c r="I2527" s="143" t="str"/>
+      <c r="H2527" t="inlineStr" s="40">
+        <is>
+          <t>Излечивает союзника от отравления.</t>
+        </is>
+      </c>
+      <c r="I2527" t="inlineStr" s="143">
+        <is>
+          <t>Cures your target of Poison effects.</t>
+        </is>
+      </c>
     </row>
     <row r="2528" ht="15" hidden="0" customHeight="1">
       <c r="A2528" s="38" t="str">
@@ -63713,8 +65417,16 @@
       <c r="G2530" s="39" t="str">
         <v>使用治癒的魔法,一定時間內恢復生命</v>
       </c>
-      <c r="H2530" s="40" t="str"/>
-      <c r="I2530" s="143" t="str"/>
+      <c r="H2530" t="inlineStr" s="40">
+        <is>
+          <t>Целительная магия, постепенно восстанавливающая ОЗ в течение некоторого времени.</t>
+        </is>
+      </c>
+      <c r="I2530" t="inlineStr" s="143">
+        <is>
+          <t>Imbues your target with restorative magic, healing them continually for a set period of time.</t>
+        </is>
+      </c>
     </row>
     <row r="2531" ht="15" hidden="0" customHeight="1">
       <c r="A2531" s="38" t="str">
@@ -63788,8 +65500,16 @@
       <c r="G2533" s="39" t="str">
         <v>能夠治療睡眠,暈眩,凍傷</v>
       </c>
-      <c r="H2533" s="40" t="str"/>
-      <c r="I2533" s="143" t="str"/>
+      <c r="H2533" t="inlineStr" s="40">
+        <is>
+          <t>Снимает с союзника сон, оглушение и заморозку.</t>
+        </is>
+      </c>
+      <c r="I2533" t="inlineStr" s="143">
+        <is>
+          <t>Cures Sleep, Stun, and Freeze effects.</t>
+        </is>
+      </c>
     </row>
     <row r="2534" ht="15" hidden="0" customHeight="1">
       <c r="A2534" s="38" t="str">
@@ -63863,8 +65583,16 @@
       <c r="G2536" s="39" t="str">
         <v>能夠使隊伍全體成員的生命恢復,繼續戰鬥</v>
       </c>
-      <c r="H2536" s="40" t="str"/>
-      <c r="I2536" s="143" t="str"/>
+      <c r="H2536" t="inlineStr" s="40">
+        <is>
+          <t>Восстанавливает ОЗ всех игроков в группе (24 ОЗ в течение 3 с.)</t>
+        </is>
+      </c>
+      <c r="I2536" t="inlineStr" s="143">
+        <is>
+          <t>Continuously restores LP for all party members.</t>
+        </is>
+      </c>
     </row>
     <row r="2537" ht="15" hidden="0" customHeight="1">
       <c r="A2537" s="38" t="str">
@@ -63938,8 +65666,16 @@
       <c r="G2539" s="39" t="str">
         <v>能夠為隊伍全體成員恢復生命的魔法</v>
       </c>
-      <c r="H2539" s="40" t="str"/>
-      <c r="I2539" s="143" t="str"/>
+      <c r="H2539" t="inlineStr" s="40">
+        <is>
+          <t>Восстанавливает ОЗ всех игроков в группе.</t>
+        </is>
+      </c>
+      <c r="I2539" t="inlineStr" s="143">
+        <is>
+          <t>Restores LP for all party members.</t>
+        </is>
+      </c>
     </row>
     <row r="2540" ht="15" hidden="0" customHeight="1">
       <c r="A2540" s="38" t="str">
@@ -64013,8 +65749,16 @@
       <c r="G2542" s="39" t="str">
         <v>完全消除目標異常狀態，並增加異常狀態抵抗力</v>
       </c>
-      <c r="H2542" s="40" t="str"/>
-      <c r="I2542" s="143" t="str"/>
+      <c r="H2542" t="inlineStr" s="40">
+        <is>
+          <t>Снимает с цели аномальные состояния и повышает сопротивляемость урону.</t>
+        </is>
+      </c>
+      <c r="I2542" t="inlineStr" s="143">
+        <is>
+          <t>Cures your target of all debuffs and increases Debuff Resistance.</t>
+        </is>
+      </c>
     </row>
     <row r="2543" ht="15" hidden="0" customHeight="1">
       <c r="A2543" s="38" t="str">
@@ -64088,8 +65832,16 @@
       <c r="G2545" s="39" t="str">
         <v>使隊伍成員全員的魔力恢復速度增加</v>
       </c>
-      <c r="H2545" s="40" t="str"/>
-      <c r="I2545" s="143" t="str"/>
+      <c r="H2545" t="inlineStr" s="40">
+        <is>
+          <t>Повышает скорость восстановления ОМ всех игроков в группе.</t>
+        </is>
+      </c>
+      <c r="I2545" t="inlineStr" s="143">
+        <is>
+          <t>Increases the MP Recovery Rate for all party members.</t>
+        </is>
+      </c>
     </row>
     <row r="2546" ht="15" hidden="0" customHeight="1">
       <c r="A2546" s="38" t="str">
@@ -64163,8 +65915,16 @@
       <c r="G2548" s="39" t="str">
         <v>藉由祝福生命，使最大生命量大幅增加</v>
       </c>
-      <c r="H2548" s="40" t="str"/>
-      <c r="I2548" s="143" t="str"/>
+      <c r="H2548" t="inlineStr" s="40">
+        <is>
+          <t>Увеличивает максимальное количество ОЗ всем игрокам в группе.</t>
+        </is>
+      </c>
+      <c r="I2548" t="inlineStr" s="143">
+        <is>
+          <t>Grants you the blessing of health, greatly increasing the LP of all party members.</t>
+        </is>
+      </c>
     </row>
     <row r="2549" ht="15" hidden="0" customHeight="1">
       <c r="A2549" s="38" t="str">
@@ -64238,8 +65998,16 @@
       <c r="G2551" s="39" t="str">
         <v>給效果時間內己方玩家增加屬性傷害和魔法攻擊力</v>
       </c>
-      <c r="H2551" s="40" t="str"/>
-      <c r="I2551" s="143" t="str"/>
+      <c r="H2551" t="inlineStr" s="40">
+        <is>
+          <t>Увеличивает силу физической и магической атаки союзника.</t>
+        </is>
+      </c>
+      <c r="I2551" t="inlineStr" s="143">
+        <is>
+          <t>Places an effect on a targeted ally player, granting them increased Elemental Damage and Magical Attack Power.</t>
+        </is>
+      </c>
     </row>
     <row r="2552" ht="15" hidden="0" customHeight="1">
       <c r="A2552" s="38" t="str">
@@ -64313,8 +66081,16 @@
       <c r="G2554" s="39" t="str">
         <v>增加目標的攻擊速度</v>
       </c>
-      <c r="H2554" s="40" t="str"/>
-      <c r="I2554" s="143" t="str"/>
+      <c r="H2554" t="inlineStr" s="40">
+        <is>
+          <t>Повышает скорость атаки цели.</t>
+        </is>
+      </c>
+      <c r="I2554" t="inlineStr" s="143">
+        <is>
+          <t>Increases the Attack Speed of your target.</t>
+        </is>
+      </c>
     </row>
     <row r="2555" ht="15" hidden="0" customHeight="1">
       <c r="A2555" s="38" t="str">
@@ -64388,8 +66164,16 @@
       <c r="G2557" s="39" t="str">
         <v>增加隊伍全體成員的防禦力</v>
       </c>
-      <c r="H2557" s="40" t="str"/>
-      <c r="I2557" s="143" t="str"/>
+      <c r="H2557" t="inlineStr" s="40">
+        <is>
+          <t>Улучшает защиту всех игроков в группе.</t>
+        </is>
+      </c>
+      <c r="I2557" t="inlineStr" s="143">
+        <is>
+          <t>Increases the Defense of all party members.</t>
+        </is>
+      </c>
     </row>
     <row r="2558" ht="15" hidden="0" customHeight="1">
       <c r="A2558" s="38" t="str">
@@ -64463,8 +66247,16 @@
       <c r="G2560" s="39" t="str">
         <v>減少目標的移動速度</v>
       </c>
-      <c r="H2560" s="40" t="str"/>
-      <c r="I2560" s="143" t="str"/>
+      <c r="H2560" t="inlineStr" s="40">
+        <is>
+          <t>Уменьшает скорость передвижения цели.</t>
+        </is>
+      </c>
+      <c r="I2560" t="inlineStr" s="143">
+        <is>
+          <t>Reduces your target's Movement Speed.</t>
+        </is>
+      </c>
     </row>
     <row r="2561" ht="15" hidden="0" customHeight="1">
       <c r="A2561" s="38" t="str">
@@ -64538,8 +66330,16 @@
       <c r="G2563" s="39" t="str">
         <v>能夠減少全體隊伍成員受到的傷害</v>
       </c>
-      <c r="H2563" s="40" t="str"/>
-      <c r="I2563" s="143" t="str"/>
+      <c r="H2563" t="inlineStr" s="40">
+        <is>
+          <t>Уменьшает урон, наносимый всем игрокам группы.</t>
+        </is>
+      </c>
+      <c r="I2563" t="inlineStr" s="143">
+        <is>
+          <t>Reduces all incoming damage for all party members.</t>
+        </is>
+      </c>
     </row>
     <row r="2564" ht="15" hidden="0" customHeight="1">
       <c r="A2564" s="38" t="str">
@@ -64613,8 +66413,16 @@
       <c r="G2566" s="39" t="str">
         <v>消費空瓶,製作聖水</v>
       </c>
-      <c r="H2566" s="40" t="str"/>
-      <c r="I2566" s="143" t="str"/>
+      <c r="H2566" t="inlineStr" s="40">
+        <is>
+          <t>Изготовление святой воды. Используется одна пустая бутыль.</t>
+        </is>
+      </c>
+      <c r="I2566" t="inlineStr" s="143">
+        <is>
+          <t>Consumes a Container to create Holy Water.</t>
+        </is>
+      </c>
     </row>
     <row r="2567" ht="15" hidden="0" customHeight="1">
       <c r="A2567" s="38" t="str">
@@ -64688,8 +66496,16 @@
       <c r="G2569" s="39" t="str">
         <v>施加在友軍身上時,增加技能的吟唱速度</v>
       </c>
-      <c r="H2569" s="40" t="str"/>
-      <c r="I2569" s="143" t="str"/>
+      <c r="H2569" t="inlineStr" s="40">
+        <is>
+          <t>Повышает скорость применения умений для всех союзников.</t>
+        </is>
+      </c>
+      <c r="I2569" t="inlineStr" s="143">
+        <is>
+          <t>Increases the Casting Speed of any skill being used by a target other than yourself.</t>
+        </is>
+      </c>
     </row>
     <row r="2570" ht="15" hidden="0" customHeight="1">
       <c r="A2570" s="38" t="str">
@@ -64763,8 +66579,16 @@
       <c r="G2572" s="39" t="str">
         <v>增加目標的力量，敏捷，智慧</v>
       </c>
-      <c r="H2572" s="40" t="str"/>
-      <c r="I2572" s="143" t="str"/>
+      <c r="H2572" t="inlineStr" s="40">
+        <is>
+          <t>Увеличивает силу, проворство и интеллект цели.</t>
+        </is>
+      </c>
+      <c r="I2572" t="inlineStr" s="143">
+        <is>
+          <t>Increases the target's Strength, Agility, and Intelligence.</t>
+        </is>
+      </c>
     </row>
     <row r="2573" ht="15" hidden="0" customHeight="1">
       <c r="A2573" s="38" t="str">
@@ -64838,8 +66662,16 @@
       <c r="G2575" s="39" t="str">
         <v>使目標或自身的魔力活化，讓MP慢慢的回覆</v>
       </c>
-      <c r="H2575" s="40" t="str"/>
-      <c r="I2575" s="143" t="str"/>
+      <c r="H2575" t="inlineStr" s="40">
+        <is>
+          <t>ОМ цели непрерывно восстанавливаются благодаря ее магическому потенциалу.</t>
+        </is>
+      </c>
+      <c r="I2575" t="inlineStr" s="143">
+        <is>
+          <t>Restores the target's MP by invigorating their magical power.</t>
+        </is>
+      </c>
     </row>
     <row r="2576" ht="15" hidden="0" customHeight="1">
       <c r="A2576" s="38" t="str">
@@ -64913,8 +66745,16 @@
       <c r="G2578" s="39" t="str">
         <v>增加隊伍全員的閃避率</v>
       </c>
-      <c r="H2578" s="40" t="str"/>
-      <c r="I2578" s="143" t="str"/>
+      <c r="H2578" t="inlineStr" s="40">
+        <is>
+          <t>Улучшает уклонение всех игроков в группе.</t>
+        </is>
+      </c>
+      <c r="I2578" t="inlineStr" s="143">
+        <is>
+          <t>Increases the Dodge of all party members.</t>
+        </is>
+      </c>
     </row>
     <row r="2579" ht="15" hidden="0" customHeight="1">
       <c r="A2579" s="38" t="str">
@@ -64988,8 +66828,16 @@
       <c r="G2581" s="39" t="str">
         <v>使負面傷害的魔法效果時間減少</v>
       </c>
-      <c r="H2581" s="40" t="str"/>
-      <c r="I2581" s="143" t="str"/>
+      <c r="H2581" t="inlineStr" s="40">
+        <is>
+          <t>Снижает время действия отрицательного эффекта.</t>
+        </is>
+      </c>
+      <c r="I2581" t="inlineStr" s="143">
+        <is>
+          <t>Reduces the duration of debuffs.</t>
+        </is>
+      </c>
     </row>
     <row r="2582" ht="15" hidden="0" customHeight="1">
       <c r="A2582" s="38" t="str">
@@ -65063,8 +66911,16 @@
       <c r="G2584" s="39" t="str">
         <v>交換目標玩家和自己的MP值</v>
       </c>
-      <c r="H2584" s="40" t="str"/>
-      <c r="I2584" s="143" t="str"/>
+      <c r="H2584" t="inlineStr" s="40">
+        <is>
+          <t>Обмен ОМ с целью.</t>
+        </is>
+      </c>
+      <c r="I2584" t="inlineStr" s="143">
+        <is>
+          <t>Exchanges your MP with your target's.</t>
+        </is>
+      </c>
     </row>
     <row r="2585" ht="15" hidden="0" customHeight="1">
       <c r="A2585" s="38" t="str">
@@ -65138,8 +66994,16 @@
       <c r="G2587" s="39" t="str">
         <v>替換自身與目標身上魔法效果的技能</v>
       </c>
-      <c r="H2587" s="40" t="str"/>
-      <c r="I2587" s="143" t="str"/>
+      <c r="H2587" t="inlineStr" s="40">
+        <is>
+          <t>Обмен магическими эффектами с целью.</t>
+        </is>
+      </c>
+      <c r="I2587" t="inlineStr" s="143">
+        <is>
+          <t>Exchanges your status effects with your target's.</t>
+        </is>
+      </c>
     </row>
     <row r="2588" ht="15" hidden="0" customHeight="1">
       <c r="A2588" s="38" t="str">
@@ -65213,8 +67077,16 @@
       <c r="G2590" s="39" t="str">
         <v>消除1個負面的魔法效果</v>
       </c>
-      <c r="H2590" s="40" t="str"/>
-      <c r="I2590" s="143" t="str"/>
+      <c r="H2590" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет снять с цели один отрицательный эффект.</t>
+        </is>
+      </c>
+      <c r="I2590" t="inlineStr" s="143">
+        <is>
+          <t>Dispels a single Disorder.</t>
+        </is>
+      </c>
     </row>
     <row r="2591" ht="15" hidden="0" customHeight="1">
       <c r="A2591" s="38" t="str">
@@ -65288,8 +67160,16 @@
       <c r="G2593" s="39" t="str">
         <v>發出光之箭體，對惡魔和不死族的怪物有加成效果</v>
       </c>
-      <c r="H2593" s="40" t="str"/>
-      <c r="I2593" s="143" t="str"/>
+      <c r="H2593" t="inlineStr" s="40">
+        <is>
+          <t>Выстрел освященной стрелой. Действенно против демонов и нежити.</t>
+        </is>
+      </c>
+      <c r="I2593" t="inlineStr" s="143">
+        <is>
+          <t>Fires an arrow made out of light. Highly effective against demons and the undead.</t>
+        </is>
+      </c>
     </row>
     <row r="2594" ht="15" hidden="0" customHeight="1">
       <c r="A2594" s="38" t="str">
@@ -65363,8 +67243,16 @@
       <c r="G2596" s="39" t="str">
         <v>減少火系、冰系、雷系魔法的傷害</v>
       </c>
-      <c r="H2596" s="40" t="str"/>
-      <c r="I2596" s="143" t="str"/>
+      <c r="H2596" t="inlineStr" s="40">
+        <is>
+          <t>Снижает урон от магии огня, льда и молний.</t>
+        </is>
+      </c>
+      <c r="I2596" t="inlineStr" s="143">
+        <is>
+          <t>Reduces the damage from Fire, Ice, and Lightning magic.</t>
+        </is>
+      </c>
     </row>
     <row r="2597" ht="15" hidden="0" customHeight="1">
       <c r="A2597" s="38" t="str">
@@ -65438,8 +67326,16 @@
       <c r="G2599" s="39" t="str">
         <v>使目標的武器帶有光屬性</v>
       </c>
-      <c r="H2599" s="40" t="str"/>
-      <c r="I2599" s="143" t="str"/>
+      <c r="H2599" t="inlineStr" s="40">
+        <is>
+          <t>Придает оружию святую ауру.</t>
+        </is>
+      </c>
+      <c r="I2599" t="inlineStr" s="143">
+        <is>
+          <t>Grants a Holy aura to the target's weapon.</t>
+        </is>
+      </c>
     </row>
     <row r="2600" ht="15" hidden="0" customHeight="1">
       <c r="A2600" s="38" t="str">
@@ -65513,8 +67409,16 @@
       <c r="G2602" s="39" t="str">
         <v>通過祝福,消除負面效果的魔法效果</v>
       </c>
-      <c r="H2602" s="40" t="str"/>
-      <c r="I2602" s="143" t="str"/>
+      <c r="H2602" t="inlineStr" s="40">
+        <is>
+          <t>Рассеивает отрицательные магические эффекты.</t>
+        </is>
+      </c>
+      <c r="I2602" t="inlineStr" s="143">
+        <is>
+          <t>Dispels Disorders through the power of a blessing.</t>
+        </is>
+      </c>
     </row>
     <row r="2603" ht="15" hidden="0" customHeight="1">
       <c r="A2603" s="38" t="str">
@@ -65588,8 +67492,16 @@
       <c r="G2605" s="39" t="str">
         <v>在自己的周圍出現光之柱,給予傷害</v>
       </c>
-      <c r="H2605" s="40" t="str"/>
-      <c r="I2605" s="143" t="str"/>
+      <c r="H2605" t="inlineStr" s="40">
+        <is>
+          <t>Игрока окружают столпы света, наносящие урон всем противникам вблизи него.</t>
+        </is>
+      </c>
+      <c r="I2605" t="inlineStr" s="143">
+        <is>
+          <t>Creates pillars of light surrounding the caster, damaging one's enemies.</t>
+        </is>
+      </c>
     </row>
     <row r="2606" ht="15" hidden="0" customHeight="1">
       <c r="A2606" s="38" t="str">
@@ -65663,8 +67575,16 @@
       <c r="G2608" s="39" t="str">
         <v>將範圍內被召喚的東西消滅</v>
       </c>
-      <c r="H2608" s="40" t="str"/>
-      <c r="I2608" s="143" t="str"/>
+      <c r="H2608" t="inlineStr" s="40">
+        <is>
+          <t>Уничтожение вызванного предмета.</t>
+        </is>
+      </c>
+      <c r="I2608" t="inlineStr" s="143">
+        <is>
+          <t>Eliminates any summoned creatures within a certain radius around the caster.</t>
+        </is>
+      </c>
     </row>
     <row r="2609" ht="15" hidden="0" customHeight="1">
       <c r="A2609" s="38" t="str">
@@ -65738,8 +67658,16 @@
       <c r="G2611" s="39" t="str">
         <v>將目標使用技能時的MP由自己代替，同時可使用4人</v>
       </c>
-      <c r="H2611" s="40" t="str"/>
-      <c r="I2611" s="143" t="str"/>
+      <c r="H2611" t="inlineStr" s="40">
+        <is>
+          <t>Цель использует ОМ игрока вместо своих. Может использоваться четырьмя игроками одновременно.</t>
+        </is>
+      </c>
+      <c r="I2611" t="inlineStr" s="143">
+        <is>
+          <t>Supplies the MP for any skills used by the target. This can be used on up to four people.</t>
+        </is>
+      </c>
     </row>
     <row r="2612" ht="15" hidden="0" customHeight="1">
       <c r="A2612" s="38" t="str">
@@ -65813,8 +67741,16 @@
       <c r="G2614" s="39" t="str">
         <v>使作用到一定區域內的範圍技能失效，不能指定地點</v>
       </c>
-      <c r="H2614" s="40" t="str"/>
-      <c r="I2614" s="143" t="str"/>
+      <c r="H2614" t="inlineStr" s="40">
+        <is>
+          <t>Отменяет все навыки. Невозможно зафиксировать позицию на карте.</t>
+        </is>
+      </c>
+      <c r="I2614" t="inlineStr" s="143">
+        <is>
+          <t>Disables Field Skills and prevents targeting areas within the area of effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2615" ht="15" hidden="0" customHeight="1">
       <c r="A2615" s="38" t="str">
@@ -65888,8 +67824,16 @@
       <c r="G2617" s="39" t="str">
         <v>唱增加命中力的歌，效果內的玩家的命中&amp;閃避增加</v>
       </c>
-      <c r="H2617" s="40" t="str"/>
-      <c r="I2617" s="143" t="str"/>
+      <c r="H2617" t="inlineStr" s="40">
+        <is>
+          <t>Песнь, увеличивающая сосредоточенность. Увеличивается шанс попаданий и уклонение игрока.</t>
+        </is>
+      </c>
+      <c r="I2617" t="inlineStr" s="143">
+        <is>
+          <t>A song that increases the Accuracy and Dodge of players within the area of effect. Toggle on/off for effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2618" ht="15" hidden="0" customHeight="1">
       <c r="A2618" s="38" t="str">
@@ -65963,8 +67907,16 @@
       <c r="G2620" s="39" t="str">
         <v>使用聖歌技能中，可根據熟練度增加移動速度的效果</v>
       </c>
-      <c r="H2620" s="40" t="str"/>
-      <c r="I2620" s="143" t="str"/>
+      <c r="H2620" t="inlineStr" s="40">
+        <is>
+          <t>Когда звучит эта песнь, игрок получает возможность двигаться в зависимости от уровня мастерства.</t>
+        </is>
+      </c>
+      <c r="I2620" t="inlineStr" s="143">
+        <is>
+          <t>Grants the ability to move while using Hymn skills. Based on level of Hymn Expertise.</t>
+        </is>
+      </c>
     </row>
     <row r="2621" ht="15" hidden="0" customHeight="1">
       <c r="A2621" s="38" t="str">
@@ -66038,8 +67990,16 @@
       <c r="G2623" s="39" t="str">
         <v>唱增加防禦力的歌，效果內玩家受到一定量的傷害減免</v>
       </c>
-      <c r="H2623" s="40" t="str"/>
-      <c r="I2623" s="143" t="str"/>
+      <c r="H2623" t="inlineStr" s="40">
+        <is>
+          <t>Песнь, увеличивающая защиту. Игроки не получают урон меньше определенной величины.</t>
+        </is>
+      </c>
+      <c r="I2623" t="inlineStr" s="143">
+        <is>
+          <t>A song that makes players within the area of effect immune to damage lower than a set amount. Toggle on/off for effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2624" ht="15" hidden="0" customHeight="1">
       <c r="A2624" s="38" t="str">
@@ -66113,8 +68073,16 @@
       <c r="G2626" s="39" t="str">
         <v>增加效果內的玩家的魔法攻擊力，減少技能冷卻時間</v>
       </c>
-      <c r="H2626" s="40" t="str"/>
-      <c r="I2626" s="143" t="str"/>
+      <c r="H2626" t="inlineStr" s="40">
+        <is>
+          <t>Увеличивает магическую атаку игрока в радиусе действия и уменьшает время перезарядки умений.</t>
+        </is>
+      </c>
+      <c r="I2626" t="inlineStr" s="143">
+        <is>
+          <t>Attack spells are stronger and Skill Cooldown is shortened for players in the area of effect. Toggle on/off for effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2627" ht="15" hidden="0" customHeight="1">
       <c r="A2627" s="38" t="str">
@@ -66188,7 +68156,11 @@
       <c r="G2629" s="39" t="str">
         <v>獲得豐富多彩的魔法知識，在一定時間內使魔法威力上升</v>
       </c>
-      <c r="H2629" s="40" t="str"/>
+      <c r="H2629" t="inlineStr" s="40">
+        <is>
+          <t>Благодаря обширным познаниям в магии урон, наносимый магией, увеличивается.</t>
+        </is>
+      </c>
       <c r="I2629" s="143" t="str"/>
     </row>
     <row r="2630" ht="15" hidden="0" customHeight="1">
@@ -66263,8 +68235,16 @@
       <c r="G2632" s="39" t="str">
         <v>全身覆蓋黑暗光環，提升對於火焰、冷氣、電擊的抵抗能力</v>
       </c>
-      <c r="H2632" s="40" t="str"/>
-      <c r="I2632" s="143" t="str"/>
+      <c r="H2632" t="inlineStr" s="40">
+        <is>
+          <t>Повышает сопротивляемость магии огня, льда и молний, если снаряжение улучшено самоцветом тьмы.</t>
+        </is>
+      </c>
+      <c r="I2632" t="inlineStr" s="143">
+        <is>
+          <t>When you wear equipment that has a Dark aura, you gain Resistance to Fire, Ice, and Lightning.</t>
+        </is>
+      </c>
     </row>
     <row r="2633" ht="15" hidden="0" customHeight="1">
       <c r="A2633" s="38" t="str">
@@ -66338,8 +68318,16 @@
       <c r="G2635" s="39" t="str">
         <v>射出火系箭，造成傷害</v>
       </c>
-      <c r="H2635" s="40" t="str"/>
-      <c r="I2635" s="143" t="str"/>
+      <c r="H2635" t="inlineStr" s="40">
+        <is>
+          <t>Огненная стрела, поражающая противника.</t>
+        </is>
+      </c>
+      <c r="I2635" t="inlineStr" s="143">
+        <is>
+          <t>Launches a fiery arrow at your target.</t>
+        </is>
+      </c>
     </row>
     <row r="2636" ht="15" hidden="0" customHeight="1">
       <c r="A2636" s="38" t="str">
@@ -66413,8 +68401,16 @@
       <c r="G2638" s="39" t="str">
         <v>從對手的頭上落雷，在一段時間停止移動</v>
       </c>
-      <c r="H2638" s="40" t="str"/>
-      <c r="I2638" s="143" t="str"/>
+      <c r="H2638" t="inlineStr" s="40">
+        <is>
+          <t>Удар молнии, вызывающий оцепенение противника.</t>
+        </is>
+      </c>
+      <c r="I2638" t="inlineStr" s="143">
+        <is>
+          <t>Strikes your target with lightning and temporarily restricts their movement.</t>
+        </is>
+      </c>
     </row>
     <row r="2639" ht="15" hidden="0" customHeight="1">
       <c r="A2639" s="38" t="str">
@@ -66488,8 +68484,16 @@
       <c r="G2641" s="39" t="str">
         <v>從對手的頭上落下強力的雷</v>
       </c>
-      <c r="H2641" s="40" t="str"/>
-      <c r="I2641" s="143" t="str"/>
+      <c r="H2641" t="inlineStr" s="40">
+        <is>
+          <t>На противника обрушивается мощный удар молнии.</t>
+        </is>
+      </c>
+      <c r="I2641" t="inlineStr" s="143">
+        <is>
+          <t>Causes powerful lightning to strike your opponent from above.</t>
+        </is>
+      </c>
     </row>
     <row r="2642" ht="15" hidden="0" customHeight="1">
       <c r="A2642" s="38" t="str">
@@ -66563,8 +68567,16 @@
       <c r="G2644" s="39" t="str">
         <v>增加自己下次使用的魔法威力</v>
       </c>
-      <c r="H2644" s="40" t="str"/>
-      <c r="I2644" s="143" t="str"/>
+      <c r="H2644" t="inlineStr" s="40">
+        <is>
+          <t>Увеличивает силу следующей магической атаки.</t>
+        </is>
+      </c>
+      <c r="I2644" t="inlineStr" s="143">
+        <is>
+          <t>Amplifies the effect of the next magic spell you use.</t>
+        </is>
+      </c>
     </row>
     <row r="2645" ht="15" hidden="0" customHeight="1">
       <c r="A2645" s="38" t="str">
@@ -66638,8 +68650,16 @@
       <c r="G2647" s="39" t="str">
         <v>快速製作冰塊,扔向對象</v>
       </c>
-      <c r="H2647" s="40" t="str"/>
-      <c r="I2647" s="143" t="str"/>
+      <c r="H2647" t="inlineStr" s="40">
+        <is>
+          <t>Атака осколками льда.</t>
+        </is>
+      </c>
+      <c r="I2647" t="inlineStr" s="143">
+        <is>
+          <t>Launches a mass of ice at your target.</t>
+        </is>
+      </c>
     </row>
     <row r="2648" ht="15" hidden="0" customHeight="1">
       <c r="A2648" s="38" t="str">
@@ -66713,8 +68733,16 @@
       <c r="G2650" s="39" t="str">
         <v>從遠處扔出一個雷球,對周圍進行傷害</v>
       </c>
-      <c r="H2650" s="40" t="str"/>
-      <c r="I2650" s="143" t="str"/>
+      <c r="H2650" t="inlineStr" s="40">
+        <is>
+          <t>Шаровая молния, которая взрывается вблизи цели, нанося массовый урон.</t>
+        </is>
+      </c>
+      <c r="I2650" t="inlineStr" s="143">
+        <is>
+          <t>Expels a mass of lightning into the distance, damaging the target and enemies in the surrounding area.</t>
+        </is>
+      </c>
     </row>
     <row r="2651" ht="15" hidden="0" customHeight="1">
       <c r="A2651" s="38" t="str">
@@ -66788,8 +68816,16 @@
       <c r="G2653" s="39" t="str">
         <v>快速向對象射出銳利的冰箭</v>
       </c>
-      <c r="H2653" s="40" t="str"/>
-      <c r="I2653" s="143" t="str"/>
+      <c r="H2653" t="inlineStr" s="40">
+        <is>
+          <t>В противника летит копье изо льда.</t>
+        </is>
+      </c>
+      <c r="I2653" t="inlineStr" s="143">
+        <is>
+          <t>Launches a sharp ice arrow at your target.</t>
+        </is>
+      </c>
     </row>
     <row r="2654" ht="15" hidden="0" customHeight="1">
       <c r="A2654" s="38" t="str">
@@ -66863,8 +68899,16 @@
       <c r="G2656" s="39" t="str">
         <v>在自己的周圍發生火系龍捲風</v>
       </c>
-      <c r="H2656" s="40" t="str"/>
-      <c r="I2656" s="143" t="str"/>
+      <c r="H2656" t="inlineStr" s="40">
+        <is>
+          <t>Игрока окружает огненная буря, наносящая массовый урон.</t>
+        </is>
+      </c>
+      <c r="I2656" t="inlineStr" s="143">
+        <is>
+          <t>Creates an enveloping hurricane of fire.</t>
+        </is>
+      </c>
     </row>
     <row r="2657" ht="15" hidden="0" customHeight="1">
       <c r="A2657" s="38" t="str">
@@ -66938,8 +68982,16 @@
       <c r="G2659" s="39" t="str">
         <v>增加對象的火系抵抗,減少冰系抵抗、雷系抵抗</v>
       </c>
-      <c r="H2659" s="40" t="str"/>
-      <c r="I2659" s="143" t="str"/>
+      <c r="H2659" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость цели к магии огня повышается, а к магии льда и молний - понижается.</t>
+        </is>
+      </c>
+      <c r="I2659" t="inlineStr" s="143">
+        <is>
+          <t>Increases the target's Fire Resistance, but decreases their Ice and Lightning Resistance.</t>
+        </is>
+      </c>
     </row>
     <row r="2660" ht="15" hidden="0" customHeight="1">
       <c r="A2660" s="38" t="str">
@@ -67013,8 +69065,16 @@
       <c r="G2662" s="39" t="str">
         <v>增加對象的冰系抵抗,但減少火系抵抗、雷系抵抗</v>
       </c>
-      <c r="H2662" s="40" t="str"/>
-      <c r="I2662" s="143" t="str"/>
+      <c r="H2662" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость цели к магии льда повышается, а к магии огня и молний - понижается.</t>
+        </is>
+      </c>
+      <c r="I2662" t="inlineStr" s="143">
+        <is>
+          <t>Increases your target's Ice Resistance, but reduces their Fire and Lightning Resistance.</t>
+        </is>
+      </c>
     </row>
     <row r="2663" ht="15" hidden="0" customHeight="1">
       <c r="A2663" s="38" t="str">
@@ -67088,8 +69148,16 @@
       <c r="G2665" s="39" t="str">
         <v>增加對象的雷系抵抗,但減少火系抵抗、冰系抵抗</v>
       </c>
-      <c r="H2665" s="40" t="str"/>
-      <c r="I2665" s="143" t="str"/>
+      <c r="H2665" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость цели к магии молний повышается, а к магии огня и льда - понижается.</t>
+        </is>
+      </c>
+      <c r="I2665" t="inlineStr" s="143">
+        <is>
+          <t>Increases your target's Lightning Resistance, but decreases their Fire and Ice Resistance.</t>
+        </is>
+      </c>
     </row>
     <row r="2666" ht="15" hidden="0" customHeight="1">
       <c r="A2666" s="38" t="str">
@@ -67163,8 +69231,16 @@
       <c r="G2668" s="39" t="str">
         <v>快速在指定區域內生成寒流旋渦,可以擊退被命中的目標</v>
       </c>
-      <c r="H2668" s="40" t="str"/>
-      <c r="I2668" s="143" t="str"/>
+      <c r="H2668" t="inlineStr" s="40">
+        <is>
+          <t>Создает ледяной вихрь, отбрасывающий противников назад.</t>
+        </is>
+      </c>
+      <c r="I2668" t="inlineStr" s="143">
+        <is>
+          <t>Creates a whirling icy vortex that will Knockback the enemy.</t>
+        </is>
+      </c>
     </row>
     <row r="2669" ht="15" hidden="0" customHeight="1">
       <c r="A2669" s="38" t="str">
@@ -67238,8 +69314,16 @@
       <c r="G2671" s="39" t="str">
         <v>生成範圍更大、威力更強的寒流漩渦，可以擊退被命中的目標</v>
       </c>
-      <c r="H2671" s="40" t="str"/>
-      <c r="I2671" s="143" t="str"/>
+      <c r="H2671" t="inlineStr" s="40">
+        <is>
+          <t>Ледяная буря, отбрасывающая противника назад.</t>
+        </is>
+      </c>
+      <c r="I2671" t="inlineStr" s="143">
+        <is>
+          <t>Creates an immense icy vortex that will Knockback the enemy.</t>
+        </is>
+      </c>
     </row>
     <row r="2672" ht="15" hidden="0" customHeight="1">
       <c r="A2672" s="38" t="str">
@@ -67313,8 +69397,16 @@
       <c r="G2674" s="39" t="str">
         <v>使目標在一定時間后爆破，威力與爆破存在的時間有關</v>
       </c>
-      <c r="H2674" s="40" t="str"/>
-      <c r="I2674" s="143" t="str"/>
+      <c r="H2674" t="inlineStr" s="40">
+        <is>
+          <t>Поражает противника через определенное время. Чем дольше задержка, тем мощнее взрыв.</t>
+        </is>
+      </c>
+      <c r="I2674" t="inlineStr" s="143">
+        <is>
+          <t>Explodes your target after a certain period of time. Damage based on how much time passes before explosion.</t>
+        </is>
+      </c>
     </row>
     <row r="2675" ht="15" hidden="0" customHeight="1">
       <c r="A2675" s="38" t="str">
@@ -67388,8 +69480,16 @@
       <c r="G2677" s="39" t="str">
         <v>在指定地點召喚天雷，目標騎乘狀態下將被定身</v>
       </c>
-      <c r="H2677" s="40" t="str"/>
-      <c r="I2677" s="143" t="str"/>
+      <c r="H2677" t="inlineStr" s="40">
+        <is>
+          <t>Гроза, поражающая противников в радиусе действия. Всадники будут обездвижены.</t>
+        </is>
+      </c>
+      <c r="I2677" t="inlineStr" s="143">
+        <is>
+          <t>Strikes the area of effect with lightning. If the target is on horseback, they will be unable to move.</t>
+        </is>
+      </c>
     </row>
     <row r="2678" ht="15" hidden="0" customHeight="1">
       <c r="A2678" s="38" t="str">
@@ -67463,8 +69563,16 @@
       <c r="G2680" s="39" t="str">
         <v>在指定的地點周圍落下隕石，有暈眩效果</v>
       </c>
-      <c r="H2680" s="40" t="str"/>
-      <c r="I2680" s="143" t="str"/>
+      <c r="H2680" t="inlineStr" s="40">
+        <is>
+          <t>Метеорит, оглушающий противников в радиусе действия.</t>
+        </is>
+      </c>
+      <c r="I2680" t="inlineStr" s="143">
+        <is>
+          <t>Showers meteors on the designated area, possibly Stunning those in the area of effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2681" ht="15" hidden="0" customHeight="1">
       <c r="A2681" s="38" t="str">
@@ -67538,8 +69646,16 @@
       <c r="G2683" s="39" t="str">
         <v>記憶1個地點，只能在部份地圖使用</v>
       </c>
-      <c r="H2683" s="40" t="str"/>
-      <c r="I2683" s="143" t="str"/>
+      <c r="H2683" t="inlineStr" s="40">
+        <is>
+          <t>Дополнительный портал на той же территории, что и первый.</t>
+        </is>
+      </c>
+      <c r="I2683" t="inlineStr" s="143">
+        <is>
+          <t>Saves a single location to warp to with the Teleport skill. Warping can only be used on certain PvP maps.</t>
+        </is>
+      </c>
     </row>
     <row r="2684" ht="15" hidden="0" customHeight="1">
       <c r="A2684" s="38" t="str">
@@ -67613,8 +69729,16 @@
       <c r="G2686" s="39" t="str">
         <v>出現一個連結記錄點的特殊傳送門</v>
       </c>
-      <c r="H2686" s="40" t="str"/>
-      <c r="I2686" s="143" t="str"/>
+      <c r="H2686" t="inlineStr" s="40">
+        <is>
+          <t>Портал, соединяющий запомненную точку с точкой, в которой находится игрок.</t>
+        </is>
+      </c>
+      <c r="I2686" t="inlineStr" s="143">
+        <is>
+          <t>Creates a warp linking your current location with the location saved by the Memorize skill.</t>
+        </is>
+      </c>
     </row>
     <row r="2687" ht="15" hidden="0" customHeight="1">
       <c r="A2687" s="38" t="str">
@@ -67688,8 +69812,16 @@
       <c r="G2689" s="39" t="str">
         <v>能夠根據熟練度的增加，增加可保存復活點的個數</v>
       </c>
-      <c r="H2689" s="40" t="str"/>
-      <c r="I2689" s="143" t="str"/>
+      <c r="H2689" t="inlineStr" s="40">
+        <is>
+          <t>Количество порталов, которые можно создать, зависит от уровня мастерства.</t>
+        </is>
+      </c>
+      <c r="I2689" t="inlineStr" s="143">
+        <is>
+          <t>Increases the number of locations that can be saved by Memorize. Based on level of Invocation Expertise.</t>
+        </is>
+      </c>
     </row>
     <row r="2690" ht="15" hidden="0" customHeight="1">
       <c r="A2690" s="38" t="str">
@@ -67763,7 +69895,11 @@
       <c r="G2692" s="39" t="str">
         <v>通過精神的鍛煉，能夠強化具現系技能</v>
       </c>
-      <c r="H2692" s="40" t="str"/>
+      <c r="H2692" t="inlineStr" s="40">
+        <is>
+          <t>Благодаря мощному интеллекту действие некоторых умений усиливается.</t>
+        </is>
+      </c>
       <c r="I2692" s="143" t="str"/>
     </row>
     <row r="2693" ht="15" hidden="0" customHeight="1">
@@ -67838,8 +69974,16 @@
       <c r="G2695" s="39" t="str">
         <v>照亮自己的周圍,解除隱身狀態</v>
       </c>
-      <c r="H2695" s="40" t="str"/>
-      <c r="I2695" s="143" t="str"/>
+      <c r="H2695" t="inlineStr" s="40">
+        <is>
+          <t>Местность вокруг игрока освещается, все невидимое становится видимым.</t>
+        </is>
+      </c>
+      <c r="I2695" t="inlineStr" s="143">
+        <is>
+          <t>Illuminates the area around you and removes the Hiding state from your enemies.</t>
+        </is>
+      </c>
     </row>
     <row r="2696" ht="15" hidden="0" customHeight="1">
       <c r="A2696" s="38" t="str">
@@ -67913,8 +70057,16 @@
       <c r="G2698" s="39" t="str">
         <v>每次受到攻擊時扣除一定的魔法值來抵消受到的物理傷害。</v>
       </c>
-      <c r="H2698" s="40" t="str"/>
-      <c r="I2698" s="143" t="str"/>
+      <c r="H2698" t="inlineStr" s="40">
+        <is>
+          <t>Снижается физический урон, вместо ОЗ за урон снимается ОМ.</t>
+        </is>
+      </c>
+      <c r="I2698" t="inlineStr" s="143">
+        <is>
+          <t>Causes you to lose MP every time an enemy strikes, but reduces the amount of physical damage taken.</t>
+        </is>
+      </c>
     </row>
     <row r="2699" ht="15" hidden="0" customHeight="1">
       <c r="A2699" s="38" t="str">
@@ -67988,8 +70140,16 @@
       <c r="G2701" s="39" t="str">
         <v>風包圍身體,降低被妨礙吟唱的機率</v>
       </c>
-      <c r="H2701" s="40" t="str"/>
-      <c r="I2701" s="143" t="str"/>
+      <c r="H2701" t="inlineStr" s="40">
+        <is>
+          <t>Тело игрока окутывает ветряной плащ, сильно понижающий вероятность прервать применение умения.</t>
+        </is>
+      </c>
+      <c r="I2701" t="inlineStr" s="143">
+        <is>
+          <t>Wraps your body in wind, making it harder for others to stop your casting.</t>
+        </is>
+      </c>
     </row>
     <row r="2702" ht="15" hidden="0" customHeight="1">
       <c r="A2702" s="38" t="str">
@@ -68063,8 +70223,16 @@
       <c r="G2704" s="39" t="str">
         <v>通過意念射出一把空之刃,目標物理防禦力將會降低傷害</v>
       </c>
-      <c r="H2704" s="40" t="str"/>
-      <c r="I2704" s="143" t="str"/>
+      <c r="H2704" t="inlineStr" s="40">
+        <is>
+          <t>Энергетический клинок, поражающий противника. Урон зависит от защиты цели.</t>
+        </is>
+      </c>
+      <c r="I2704" t="inlineStr" s="143">
+        <is>
+          <t>Sends a psychic wave of energy at your target. The amount of damage inflicted is dependent on their Defense.</t>
+        </is>
+      </c>
     </row>
     <row r="2705" ht="15" hidden="0" customHeight="1">
       <c r="A2705" s="38" t="str">
@@ -68138,8 +70306,16 @@
       <c r="G2707" s="39" t="str">
         <v>現出巨大的牆壁。所有玩家都不能通過</v>
       </c>
-      <c r="H2707" s="40" t="str"/>
-      <c r="I2707" s="143" t="str"/>
+      <c r="H2707" t="inlineStr" s="40">
+        <is>
+          <t>Огромная стена, которую не может преодолеть ни один игрок.</t>
+        </is>
+      </c>
+      <c r="I2707" t="inlineStr" s="143">
+        <is>
+          <t>Creates an impermeable wall that no player can pass through.</t>
+        </is>
+      </c>
     </row>
     <row r="2708" ht="15" hidden="0" customHeight="1">
       <c r="A2708" s="38" t="str">
@@ -68213,8 +70389,16 @@
       <c r="G2710" s="39" t="str">
         <v>召喚巨大的龍捲風進行傷害，能夠使對手睡眠</v>
       </c>
-      <c r="H2710" s="40" t="str"/>
-      <c r="I2710" s="143" t="str"/>
+      <c r="H2710" t="inlineStr" s="40">
+        <is>
+          <t>Огромный песчаный смерч налетает на врага и усыпляет его.</t>
+        </is>
+      </c>
+      <c r="I2710" t="inlineStr" s="143">
+        <is>
+          <t>Summons a giant tornado that inflicts damage and can put your opponent to Sleep.</t>
+        </is>
+      </c>
     </row>
     <row r="2711" ht="15" hidden="0" customHeight="1">
       <c r="A2711" s="38" t="str">
@@ -68288,8 +70472,16 @@
       <c r="G2713" s="39" t="str">
         <v>在指定地點召喚樹人，遠距離攻擊靠近的目標</v>
       </c>
-      <c r="H2713" s="40" t="str"/>
-      <c r="I2713" s="143" t="str"/>
+      <c r="H2713" t="inlineStr" s="40">
+        <is>
+          <t>Вызывает стреляющее во врагов растение.</t>
+        </is>
+      </c>
+      <c r="I2713" t="inlineStr" s="143">
+        <is>
+          <t>Summons a plant at the designated point. The plant will begin using ranged attacks on nearby enemies.</t>
+        </is>
+      </c>
     </row>
     <row r="2714" ht="15" hidden="0" customHeight="1">
       <c r="A2714" s="38" t="str">
@@ -68363,8 +70555,16 @@
       <c r="G2716" s="39" t="str">
         <v>減少暗黑屬性的反動傷害</v>
       </c>
-      <c r="H2716" s="40" t="str"/>
-      <c r="I2716" s="143" t="str"/>
+      <c r="H2716" t="inlineStr" s="40">
+        <is>
+          <t>Темная аура понижает урон и возвращает его противнику.</t>
+        </is>
+      </c>
+      <c r="I2716" t="inlineStr" s="143">
+        <is>
+          <t>Reduces the amount of Echo damage you take from Dark auras.</t>
+        </is>
+      </c>
     </row>
     <row r="2717" ht="15" hidden="0" customHeight="1">
       <c r="A2717" s="38" t="str">
@@ -68438,8 +70638,16 @@
       <c r="G2719" s="39" t="str">
         <v>範圍內小隊成員變為隱身狀態</v>
       </c>
-      <c r="H2719" s="40" t="str"/>
-      <c r="I2719" s="143" t="str"/>
+      <c r="H2719" t="inlineStr" s="40">
+        <is>
+          <t>Все игроки группы в радиусе действия умения становятся невидимыми.</t>
+        </is>
+      </c>
+      <c r="I2719" t="inlineStr" s="143">
+        <is>
+          <t>Grants the Hiding state to nearby party members.</t>
+        </is>
+      </c>
     </row>
     <row r="2720" ht="15" hidden="0" customHeight="1">
       <c r="A2720" s="38" t="str">
@@ -68513,8 +70721,16 @@
       <c r="G2722" s="39" t="str">
         <v>向目標體內送入毒素,使其變為中毒狀態</v>
       </c>
-      <c r="H2722" s="40" t="str"/>
-      <c r="I2722" s="143" t="str"/>
+      <c r="H2722" t="inlineStr" s="40">
+        <is>
+          <t>Отравляет организм жертвы ядом.</t>
+        </is>
+      </c>
+      <c r="I2722" t="inlineStr" s="143">
+        <is>
+          <t>Injects venom into your opponent, inflicting the Poison effect upon them.</t>
+        </is>
+      </c>
     </row>
     <row r="2723" ht="15" hidden="0" customHeight="1">
       <c r="A2723" s="38" t="str">
@@ -68588,8 +70804,16 @@
       <c r="G2725" s="39" t="str">
         <v>使武器帶有暗黑屬性。每次攻擊自身會受到傷害</v>
       </c>
-      <c r="H2725" s="40" t="str"/>
-      <c r="I2725" s="143" t="str"/>
+      <c r="H2725" t="inlineStr" s="40">
+        <is>
+          <t>Создает вокруг оружия ауру тьмы. При каждой атаке урон наносится самому игроку.</t>
+        </is>
+      </c>
+      <c r="I2725" t="inlineStr" s="143">
+        <is>
+          <t>Places a Dark aura on a weapon, causing it to inflict Echo damage.</t>
+        </is>
+      </c>
     </row>
     <row r="2726" ht="15" hidden="0" customHeight="1">
       <c r="A2726" s="38" t="str">
@@ -68663,8 +70887,16 @@
       <c r="G2728" s="39" t="str">
         <v>吸收對手的生命力,變為自己的</v>
       </c>
-      <c r="H2728" s="40" t="str"/>
-      <c r="I2728" s="143" t="str"/>
+      <c r="H2728" t="inlineStr" s="40">
+        <is>
+          <t>Перекачивает ОЗ из цели в игрока.</t>
+        </is>
+      </c>
+      <c r="I2728" t="inlineStr" s="143">
+        <is>
+          <t>Draws out your opponent's LP and makes it your own.</t>
+        </is>
+      </c>
     </row>
     <row r="2729" ht="15" hidden="0" customHeight="1">
       <c r="A2729" s="38" t="str">
@@ -68738,8 +70970,16 @@
       <c r="G2731" s="39" t="str">
         <v>由傷口向目標體內輸入毒素,使其變為腐蝕狀態</v>
       </c>
-      <c r="H2731" s="40" t="str"/>
-      <c r="I2731" s="143" t="str"/>
+      <c r="H2731" t="inlineStr" s="40">
+        <is>
+          <t>Вызывает гниение, мешающее восстановлению ОЗ и ОМ и постепенно снижающее количество жизни.</t>
+        </is>
+      </c>
+      <c r="I2731" t="inlineStr" s="143">
+        <is>
+          <t>Injects poison into your opponent via a small wound, inflicting the Addle effect on them.</t>
+        </is>
+      </c>
     </row>
     <row r="2732" ht="15" hidden="0" customHeight="1">
       <c r="A2732" s="38" t="str">
@@ -68813,8 +71053,16 @@
       <c r="G2734" s="39" t="str">
         <v>消除對象的強化魔法效果</v>
       </c>
-      <c r="H2734" s="40" t="str"/>
-      <c r="I2734" s="143" t="str"/>
+      <c r="H2734" t="inlineStr" s="40">
+        <is>
+          <t>Снимает с цели положительные магические эффекты.</t>
+        </is>
+      </c>
+      <c r="I2734" t="inlineStr" s="143">
+        <is>
+          <t>Removes one of your target's positive status effects.</t>
+        </is>
+      </c>
     </row>
     <row r="2735" ht="15" hidden="0" customHeight="1">
       <c r="A2735" s="38" t="str">
@@ -68888,8 +71136,16 @@
       <c r="G2737" s="39" t="str">
         <v>增加對象的毒系抗性、暗系抗性,減少魅惑抗性</v>
       </c>
-      <c r="H2737" s="40" t="str"/>
-      <c r="I2737" s="143" t="str"/>
+      <c r="H2737" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость цели к яду увеличивается, а к чарам - уменьшается.</t>
+        </is>
+      </c>
+      <c r="I2737" t="inlineStr" s="143">
+        <is>
+          <t>Increases your target's Poison and Dark Resistances, but reduces their Charm Resistance.</t>
+        </is>
+      </c>
     </row>
     <row r="2738" ht="15" hidden="0" customHeight="1">
       <c r="A2738" s="38" t="str">
@@ -68963,8 +71219,16 @@
       <c r="G2740" s="39" t="str">
         <v>目標下次受到的傷害大增</v>
       </c>
-      <c r="H2740" s="40" t="str"/>
-      <c r="I2740" s="143" t="str"/>
+      <c r="H2740" t="inlineStr" s="40">
+        <is>
+          <t>Увеличивает урон, наносимый цели следующей атакой.</t>
+        </is>
+      </c>
+      <c r="I2740" t="inlineStr" s="143">
+        <is>
+          <t>Increases the amount of damage your target takes from the next successful attack.</t>
+        </is>
+      </c>
     </row>
     <row r="2741" ht="15" hidden="0" customHeight="1">
       <c r="A2741" s="38" t="str">
@@ -69038,8 +71302,16 @@
       <c r="G2743" s="39" t="str">
         <v>由大地召喚負面屬性,給予目標毒性傷害。偶爾給與衰弱效果</v>
       </c>
-      <c r="H2743" s="40" t="str"/>
-      <c r="I2743" s="143" t="str"/>
+      <c r="H2743" t="inlineStr" s="40">
+        <is>
+          <t>Поднимает с земли ауру тьмы, наносящую урон ядом. Иногда противник при этом также ослабевает.</t>
+        </is>
+      </c>
+      <c r="I2743" t="inlineStr" s="143">
+        <is>
+          <t>Summons forth a malign aura from the ground, causing Poison damage. Sometimes causes the Weaken effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2744" ht="15" hidden="0" customHeight="1">
       <c r="A2744" s="38" t="str">
@@ -69113,8 +71385,16 @@
       <c r="G2746" s="39" t="str">
         <v>進行物理攻擊後，以一定機率消除物件的強化魔法效果</v>
       </c>
-      <c r="H2746" s="40" t="str"/>
-      <c r="I2746" s="143" t="str"/>
+      <c r="H2746" t="inlineStr" s="40">
+        <is>
+          <t>При физической атаке есть определенный шанс отменить положительный эффект врага.</t>
+        </is>
+      </c>
+      <c r="I2746" t="inlineStr" s="143">
+        <is>
+          <t>Grants a chance to dispel a positive status effect on your target when making a physical attack.</t>
+        </is>
+      </c>
     </row>
     <row r="2747" ht="15" hidden="0" customHeight="1">
       <c r="A2747" s="38" t="str">
@@ -69188,8 +71468,16 @@
       <c r="G2749" s="39" t="str">
         <v>使武器加上強大的暗黑屬性，攻擊時會出現擴散傷害</v>
       </c>
-      <c r="H2749" s="40" t="str"/>
-      <c r="I2749" s="143" t="str"/>
+      <c r="H2749" t="inlineStr" s="40">
+        <is>
+          <t>Оружие получает темную ауру, которая наносит урон окружающим противникам.</t>
+        </is>
+      </c>
+      <c r="I2749" t="inlineStr" s="143">
+        <is>
+          <t>Calls upon dark plumes that erupt from the ground, causing damage to surrounding enemies.</t>
+        </is>
+      </c>
     </row>
     <row r="2750" ht="15" hidden="0" customHeight="1">
       <c r="A2750" s="38" t="str">
@@ -69263,8 +71551,16 @@
       <c r="G2752" s="39" t="str">
         <v>停止負面魔法效果的時間，有減少HP恢復量的效果</v>
       </c>
-      <c r="H2752" s="40" t="str"/>
-      <c r="I2752" s="143" t="str"/>
+      <c r="H2752" t="inlineStr" s="40">
+        <is>
+          <t>Прерывает действие отрицательного магического эффекта. Снижает скорость восстановления ОЗ.</t>
+        </is>
+      </c>
+      <c r="I2752" t="inlineStr" s="143">
+        <is>
+          <t>Reduces your target's LP Recovery Rate and stops the clock on any debuffs, prolonging their suffering.</t>
+        </is>
+      </c>
     </row>
     <row r="2753" ht="15" hidden="0" customHeight="1">
       <c r="A2753" s="38" t="str">
@@ -69338,8 +71634,16 @@
       <c r="G2755" s="39" t="str">
         <v>看到幻覺，使騎手混亂，減少馬的腳力</v>
       </c>
-      <c r="H2755" s="40" t="str"/>
-      <c r="I2755" s="143" t="str"/>
+      <c r="H2755" t="inlineStr" s="40">
+        <is>
+          <t>Мираж, пугающий коня противника и понижающий его скорость.</t>
+        </is>
+      </c>
+      <c r="I2755" t="inlineStr" s="143">
+        <is>
+          <t>Reduces a horse's Trample capacity by sending its rider into a hallucinatory state.</t>
+        </is>
+      </c>
     </row>
     <row r="2756" ht="15" hidden="0" customHeight="1">
       <c r="A2756" s="38" t="str">
@@ -69413,8 +71717,16 @@
       <c r="G2758" s="39" t="str">
         <v>減少目標的攻擊力</v>
       </c>
-      <c r="H2758" s="40" t="str"/>
-      <c r="I2758" s="143" t="str"/>
+      <c r="H2758" t="inlineStr" s="40">
+        <is>
+          <t>Уменьшает урон, наносимый противником при атаке.</t>
+        </is>
+      </c>
+      <c r="I2758" t="inlineStr" s="143">
+        <is>
+          <t>Decreases your target's Attack Power.</t>
+        </is>
+      </c>
     </row>
     <row r="2759" ht="15" hidden="0" customHeight="1">
       <c r="A2759" s="38" t="str">
@@ -69488,8 +71800,16 @@
       <c r="G2761" s="39" t="str">
         <v>在附近刮起沙的龍捲風,傷害的同時有睡眠效果</v>
       </c>
-      <c r="H2761" s="40" t="str"/>
-      <c r="I2761" s="143" t="str"/>
+      <c r="H2761" t="inlineStr" s="40">
+        <is>
+          <t>Создает песчаный вихрь, который наносит противникам урон и усыпляет их.</t>
+        </is>
+      </c>
+      <c r="I2761" t="inlineStr" s="143">
+        <is>
+          <t>Raises a sand tornado from the ground that can cause the Sleep effect and damage your enemies.</t>
+        </is>
+      </c>
     </row>
     <row r="2762" ht="15" hidden="0" customHeight="1">
       <c r="A2762" s="38" t="str">
@@ -69563,8 +71883,16 @@
       <c r="G2764" s="39" t="str">
         <v>對目標精神以直接傷害,減少目標魔力</v>
       </c>
-      <c r="H2764" s="40" t="str"/>
-      <c r="I2764" s="143" t="str"/>
+      <c r="H2764" t="inlineStr" s="40">
+        <is>
+          <t>Удар по духу цели, уменьшающий количество ее ОМ.</t>
+        </is>
+      </c>
+      <c r="I2764" t="inlineStr" s="143">
+        <is>
+          <t>Directly damages your opponent's mind, reducing their MP.</t>
+        </is>
+      </c>
     </row>
     <row r="2765" ht="15" hidden="0" customHeight="1">
       <c r="A2765" s="38" t="str">
@@ -69638,8 +71966,16 @@
       <c r="G2767" s="39" t="str">
         <v>減少對象的防禦力</v>
       </c>
-      <c r="H2767" s="40" t="str"/>
-      <c r="I2767" s="143" t="str"/>
+      <c r="H2767" t="inlineStr" s="40">
+        <is>
+          <t>Понижает защиту цели.</t>
+        </is>
+      </c>
+      <c r="I2767" t="inlineStr" s="143">
+        <is>
+          <t>Reduces your target's Defense.</t>
+        </is>
+      </c>
     </row>
     <row r="2768" ht="15" hidden="0" customHeight="1">
       <c r="A2768" s="38" t="str">
@@ -69713,8 +72049,16 @@
       <c r="G2770" s="39" t="str">
         <v>減少對象的閃避</v>
       </c>
-      <c r="H2770" s="40" t="str"/>
-      <c r="I2770" s="143" t="str"/>
+      <c r="H2770" t="inlineStr" s="40">
+        <is>
+          <t>Понижает способность цели к уклонению.</t>
+        </is>
+      </c>
+      <c r="I2770" t="inlineStr" s="143">
+        <is>
+          <t>Reduces your target's Dodge.</t>
+        </is>
+      </c>
     </row>
     <row r="2771" ht="15" hidden="0" customHeight="1">
       <c r="A2771" s="38" t="str">
@@ -69788,8 +72132,16 @@
       <c r="G2773" s="39" t="str">
         <v>增加目標的魅惑抗性,減少毒系抗性、暗系抗性</v>
       </c>
-      <c r="H2773" s="40" t="str"/>
-      <c r="I2773" s="143" t="str"/>
+      <c r="H2773" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость цели к чарам повышается, а к яду и магии тьмы - понижается.</t>
+        </is>
+      </c>
+      <c r="I2773" t="inlineStr" s="143">
+        <is>
+          <t>Increases your target's Charm Resistance, but reduces their Poison and Dark Resistance.</t>
+        </is>
+      </c>
     </row>
     <row r="2774" ht="15" hidden="0" customHeight="1">
       <c r="A2774" s="38" t="str">
@@ -69863,8 +72215,16 @@
       <c r="G2776" s="39" t="str">
         <v>快速將冰系施展在目標上,變為凍傷狀態</v>
       </c>
-      <c r="H2776" s="40" t="str"/>
-      <c r="I2776" s="143" t="str"/>
+      <c r="H2776" t="inlineStr" s="40">
+        <is>
+          <t>Насылает на противника эффект заморозки.</t>
+        </is>
+      </c>
+      <c r="I2776" t="inlineStr" s="143">
+        <is>
+          <t>Quickly strikes your target with ice, inflicting them with the Freeze effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2777" ht="15" hidden="0" customHeight="1">
       <c r="A2777" s="38" t="str">
@@ -69938,8 +72298,16 @@
       <c r="G2779" s="39" t="str">
         <v>召喚劇毒沼澤,使目標變為中毒狀態、並且移動困難</v>
       </c>
-      <c r="H2779" s="40" t="str"/>
-      <c r="I2779" s="143" t="str"/>
+      <c r="H2779" t="inlineStr" s="40">
+        <is>
+          <t>Ядовитое болото, замедляющее и отравляющее противников.</t>
+        </is>
+      </c>
+      <c r="I2779" t="inlineStr" s="143">
+        <is>
+          <t>Creates a poisonous swamp that restricts Movement Speed and Poisons your enemies.</t>
+        </is>
+      </c>
     </row>
     <row r="2780" ht="15" hidden="0" customHeight="1">
       <c r="A2780" s="38" t="str">
@@ -70013,8 +72381,16 @@
       <c r="G2782" s="39" t="str">
         <v>傷害範圍內敵人的精神，使對手沉默</v>
       </c>
-      <c r="H2782" s="40" t="str"/>
-      <c r="I2782" s="143" t="str"/>
+      <c r="H2782" t="inlineStr" s="40">
+        <is>
+          <t>Наносит урон по мане противника. Существует вероятность немоты.</t>
+        </is>
+      </c>
+      <c r="I2782" t="inlineStr" s="143">
+        <is>
+          <t>Damages the MP of all enemies in the area of effect. It may also inflict Silence on them.</t>
+        </is>
+      </c>
     </row>
     <row r="2783" ht="15" hidden="0" customHeight="1">
       <c r="A2783" s="38" t="str">
@@ -70088,8 +72464,16 @@
       <c r="G2785" s="39" t="str">
         <v>向目標射出矢，命中敵人後，有一定機率對其周圍的敵人造成詛咒和疾病的效果</v>
       </c>
-      <c r="H2785" s="40" t="str"/>
-      <c r="I2785" s="143" t="str"/>
+      <c r="H2785" t="inlineStr" s="40">
+        <is>
+          <t>Стрела, с определенной вероятностью насылающая на противника проклятие или болезнь.</t>
+        </is>
+      </c>
+      <c r="I2785" t="inlineStr" s="143">
+        <is>
+          <t>Fires a bolt at your target. Has a chance to inflict Curse and Disease on the target and any enemies surrounding them.</t>
+        </is>
+      </c>
     </row>
     <row r="2786" ht="15" hidden="0" customHeight="1">
       <c r="A2786" s="38" t="str">
@@ -70163,8 +72547,16 @@
       <c r="G2788" s="39" t="str">
         <v>騎乘時能夠使用騎乘專用技能</v>
       </c>
-      <c r="H2788" s="40" t="str"/>
-      <c r="I2788" s="143" t="str"/>
+      <c r="H2788" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет использовать некоторые умения, даже когда игрок на коне.</t>
+        </is>
+      </c>
+      <c r="I2788" t="inlineStr" s="143">
+        <is>
+          <t>Allows you to use certain skills and charge attacks while on horseback.</t>
+        </is>
+      </c>
     </row>
     <row r="2789" ht="15" hidden="0" customHeight="1">
       <c r="A2789" s="38" t="str">
@@ -70238,8 +72630,16 @@
       <c r="G2791" s="39" t="str">
         <v>騎乘時能夠使用騎乘專用技能</v>
       </c>
-      <c r="H2791" s="40" t="str"/>
-      <c r="I2791" s="143" t="str"/>
+      <c r="H2791" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет использовать некоторые умения, даже когда игрок на коне.</t>
+        </is>
+      </c>
+      <c r="I2791" t="inlineStr" s="143">
+        <is>
+          <t>Allows you to use certain skills and charge attacks while on horseback.</t>
+        </is>
+      </c>
     </row>
     <row r="2792" ht="15" hidden="0" customHeight="1">
       <c r="A2792" s="38" t="str">
@@ -70313,8 +72713,16 @@
       <c r="G2794" s="39" t="str">
         <v>騎乘時能夠使用騎乘專用技能</v>
       </c>
-      <c r="H2794" s="40" t="str"/>
-      <c r="I2794" s="143" t="str"/>
+      <c r="H2794" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет использовать некоторые умения, даже когда игрок на коне.</t>
+        </is>
+      </c>
+      <c r="I2794" t="inlineStr" s="143">
+        <is>
+          <t>Allows you to use certain skills and charge attacks while on horseback.</t>
+        </is>
+      </c>
     </row>
     <row r="2795" ht="15" hidden="0" customHeight="1">
       <c r="A2795" s="38" t="str">
@@ -70388,8 +72796,16 @@
       <c r="G2797" s="39" t="str">
         <v>騎乘時能夠使用騎乘專用技能</v>
       </c>
-      <c r="H2797" s="40" t="str"/>
-      <c r="I2797" s="143" t="str"/>
+      <c r="H2797" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет использовать некоторые умения, даже когда игрок на коне.</t>
+        </is>
+      </c>
+      <c r="I2797" t="inlineStr" s="143">
+        <is>
+          <t>Allows you to use certain skills and charge attacks while on horseback.</t>
+        </is>
+      </c>
     </row>
     <row r="2798" ht="15" hidden="0" customHeight="1">
       <c r="A2798" s="38" t="str">
@@ -70463,8 +72879,16 @@
       <c r="G2800" s="39" t="str">
         <v>只要是能夠騎乘的場所，都能召喚馬</v>
       </c>
-      <c r="H2800" s="40" t="str"/>
-      <c r="I2800" s="143" t="str"/>
+      <c r="H2800" t="inlineStr" s="40">
+        <is>
+          <t>Позволяет вызвать коня в месте, где можно ездить верхом.</t>
+        </is>
+      </c>
+      <c r="I2800" t="inlineStr" s="143">
+        <is>
+          <t>Allows you to summon your horse if you are in an area suitable for riding.</t>
+        </is>
+      </c>
     </row>
     <row r="2801" ht="15" hidden="0" customHeight="1">
       <c r="A2801" s="38" t="str">
@@ -70538,8 +72962,16 @@
       <c r="G2803" s="42" t="str">
         <v>效果中，自身承受坐騎受到的傷害</v>
       </c>
-      <c r="H2803" s="43" t="str"/>
-      <c r="I2803" s="143" t="str"/>
+      <c r="H2803" t="inlineStr" s="43">
+        <is>
+          <t>Наездник принимает на себя урон, наносимый коню.</t>
+        </is>
+      </c>
+      <c r="I2803" t="inlineStr" s="143">
+        <is>
+          <t>While under this effect, you absorb all damage meant to be taken by your horse. Toggle on/off for effect.</t>
+        </is>
+      </c>
     </row>
     <row r="2804" ht="15" hidden="0" customHeight="1">
       <c r="A2804" s="50" t="str">
@@ -72569,6 +75001,194 @@
         <v>{name}: не меньше {points} очков</v>
       </c>
       <c r="I2900" s="143" t="str"/>
+    </row>
+    <row r="2901">
+      <c r="A2901" t="inlineStr">
+        <is>
+          <t>Интерфейс</t>
+        </is>
+      </c>
+      <c r="B2901" t="inlineStr">
+        <is>
+          <t>search.resetFilter</t>
+        </is>
+      </c>
+      <c r="C2901" t="inlineStr">
+        <is>
+          <t>Интерфейс сайта</t>
+        </is>
+      </c>
+      <c r="D2901" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E2901" t="inlineStr">
+        <is>
+          <t>Reset filter</t>
+        </is>
+      </c>
+      <c r="F2901" t="inlineStr">
+        <is>
+          <t>フィルターをリセット</t>
+        </is>
+      </c>
+      <c r="G2901" t="inlineStr">
+        <is>
+          <t>重設篩選條件</t>
+        </is>
+      </c>
+      <c r="H2901" t="inlineStr">
+        <is>
+          <t>Сбросить фильтр</t>
+        </is>
+      </c>
+      <c r="I2901" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="2902">
+      <c r="A2902" t="inlineStr">
+        <is>
+          <t>Интерфейс</t>
+        </is>
+      </c>
+      <c r="B2902" t="inlineStr">
+        <is>
+          <t>search.allTypes</t>
+        </is>
+      </c>
+      <c r="C2902" t="inlineStr">
+        <is>
+          <t>Интерфейс сайта</t>
+        </is>
+      </c>
+      <c r="D2902" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E2902" t="inlineStr">
+        <is>
+          <t>All types</t>
+        </is>
+      </c>
+      <c r="F2902" t="inlineStr">
+        <is>
+          <t>すべての種類</t>
+        </is>
+      </c>
+      <c r="G2902" t="inlineStr">
+        <is>
+          <t>所有類型</t>
+        </is>
+      </c>
+      <c r="H2902" t="inlineStr">
+        <is>
+          <t>Все типы</t>
+        </is>
+      </c>
+      <c r="I2902" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="2903">
+      <c r="A2903" t="inlineStr">
+        <is>
+          <t>Интерфейс</t>
+        </is>
+      </c>
+      <c r="B2903" t="inlineStr">
+        <is>
+          <t>search.typeFilter</t>
+        </is>
+      </c>
+      <c r="C2903" t="inlineStr">
+        <is>
+          <t>Интерфейс сайта</t>
+        </is>
+      </c>
+      <c r="D2903" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E2903" t="inlineStr">
+        <is>
+          <t>Filter by type</t>
+        </is>
+      </c>
+      <c r="F2903" t="inlineStr">
+        <is>
+          <t>種類で絞り込む</t>
+        </is>
+      </c>
+      <c r="G2903" t="inlineStr">
+        <is>
+          <t>依類型篩選</t>
+        </is>
+      </c>
+      <c r="H2903" t="inlineStr">
+        <is>
+          <t>Фильтр по типу</t>
+        </is>
+      </c>
+      <c r="I2903" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="2904">
+      <c r="A2904" t="inlineStr">
+        <is>
+          <t>Интерфейс</t>
+        </is>
+      </c>
+      <c r="B2904" t="inlineStr">
+        <is>
+          <t>builds.autosaveEnabled</t>
+        </is>
+      </c>
+      <c r="C2904" t="inlineStr">
+        <is>
+          <t>Интерфейс сайта</t>
+        </is>
+      </c>
+      <c r="D2904" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E2904" t="inlineStr">
+        <is>
+          <t>Autosave enabled</t>
+        </is>
+      </c>
+      <c r="F2904" t="inlineStr">
+        <is>
+          <t>自動保存が有効です</t>
+        </is>
+      </c>
+      <c r="G2904" t="inlineStr">
+        <is>
+          <t>自動儲存已啟用</t>
+        </is>
+      </c>
+      <c r="H2904" t="inlineStr">
+        <is>
+          <t>Автосохранение включено</t>
+        </is>
+      </c>
+      <c r="I2904" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/localization/translations.xlsx
+++ b/localization/translations.xlsx
@@ -913,8 +913,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2904" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I2904"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TranslationsTable" displayName="TranslationsTable" ref="A1:I2908" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I2908"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Раздел"/>
     <tableColumn id="2" name="ID (не менять)"/>
@@ -40334,7 +40334,11 @@
       <c r="G1557" s="24" t="str">
         <v>接近</v>
       </c>
-      <c r="H1557" s="25" t="str"/>
+      <c r="H1557" t="inlineStr" s="25">
+        <is>
+          <t>Ближний бой</t>
+        </is>
+      </c>
       <c r="I1557" s="143" t="str"/>
     </row>
     <row r="1558" ht="21" customHeight="1">
@@ -40359,7 +40363,11 @@
       <c r="G1558" s="24" t="str">
         <v>斬殺</v>
       </c>
-      <c r="H1558" s="25" t="str"/>
+      <c r="H1558" t="inlineStr" s="25">
+        <is>
+          <t>Секущий удар</t>
+        </is>
+      </c>
       <c r="I1558" s="143" t="str"/>
     </row>
     <row r="1559" ht="21" customHeight="1">
@@ -40384,7 +40392,11 @@
       <c r="G1559" s="24" t="str">
         <v>突刺</v>
       </c>
-      <c r="H1559" s="25" t="str"/>
+      <c r="H1559" t="inlineStr" s="25">
+        <is>
+          <t>Колющий удар</t>
+        </is>
+      </c>
       <c r="I1559" s="143" t="str"/>
     </row>
     <row r="1560" ht="21" customHeight="1">
@@ -40409,7 +40421,11 @@
       <c r="G1560" s="24" t="str">
         <v>揮砍</v>
       </c>
-      <c r="H1560" s="25" t="str"/>
+      <c r="H1560" t="inlineStr" s="25">
+        <is>
+          <t>Рубящий удар</t>
+        </is>
+      </c>
       <c r="I1560" s="143" t="str"/>
     </row>
     <row r="1561" ht="21" customHeight="1">
@@ -40434,7 +40450,11 @@
       <c r="G1561" s="24" t="str">
         <v>打擊</v>
       </c>
-      <c r="H1561" s="25" t="str"/>
+      <c r="H1561" t="inlineStr" s="25">
+        <is>
+          <t>Тяжелый удар</t>
+        </is>
+      </c>
       <c r="I1561" s="143" t="str"/>
     </row>
     <row r="1562" ht="21" customHeight="1">
@@ -40459,7 +40479,11 @@
       <c r="G1562" s="24" t="str">
         <v>防禦</v>
       </c>
-      <c r="H1562" s="25" t="str"/>
+      <c r="H1562" t="inlineStr" s="25">
+        <is>
+          <t>Оборона</t>
+        </is>
+      </c>
       <c r="I1562" s="143" t="str"/>
     </row>
     <row r="1563" ht="21" customHeight="1">
@@ -40484,7 +40508,11 @@
       <c r="G1563" s="24" t="str">
         <v>刺殺</v>
       </c>
-      <c r="H1563" s="25" t="str"/>
+      <c r="H1563" t="inlineStr" s="25">
+        <is>
+          <t>Тактика</t>
+        </is>
+      </c>
       <c r="I1563" s="143" t="str"/>
     </row>
     <row r="1564" ht="21" customHeight="1">
@@ -40509,7 +40537,11 @@
       <c r="G1564" s="24" t="str">
         <v>射擊</v>
       </c>
-      <c r="H1564" s="25" t="str"/>
+      <c r="H1564" t="inlineStr" s="25">
+        <is>
+          <t>Стрельба</t>
+        </is>
+      </c>
       <c r="I1564" s="143" t="str"/>
     </row>
     <row r="1565" ht="21" customHeight="1">
@@ -40534,7 +40566,11 @@
       <c r="G1565" s="24" t="str">
         <v>調合</v>
       </c>
-      <c r="H1565" s="25" t="str"/>
+      <c r="H1565" t="inlineStr" s="25">
+        <is>
+          <t>Ремесло</t>
+        </is>
+      </c>
       <c r="I1565" s="143" t="str"/>
     </row>
     <row r="1566" ht="21" customHeight="1">
@@ -40559,7 +40595,11 @@
       <c r="G1566" s="24" t="str">
         <v>暗殺</v>
       </c>
-      <c r="H1566" s="25" t="str"/>
+      <c r="H1566" t="inlineStr" s="25">
+        <is>
+          <t>Убийства</t>
+        </is>
+      </c>
       <c r="I1566" s="143" t="str"/>
     </row>
     <row r="1567" ht="21" customHeight="1">
@@ -40584,7 +40624,11 @@
       <c r="G1567" s="24" t="str">
         <v>機關</v>
       </c>
-      <c r="H1567" s="25" t="str"/>
+      <c r="H1567" t="inlineStr" s="25">
+        <is>
+          <t>Ловушки</t>
+        </is>
+      </c>
       <c r="I1567" s="143" t="str"/>
     </row>
     <row r="1568" ht="21" customHeight="1">
@@ -40609,7 +40653,11 @@
       <c r="G1568" s="24" t="str">
         <v>迴避</v>
       </c>
-      <c r="H1568" s="25" t="str"/>
+      <c r="H1568" t="inlineStr" s="25">
+        <is>
+          <t>Уклонение</t>
+        </is>
+      </c>
       <c r="I1568" s="143" t="str"/>
     </row>
     <row r="1569" ht="21" customHeight="1">
@@ -40634,7 +40682,11 @@
       <c r="G1569" s="24" t="str">
         <v>神聖</v>
       </c>
-      <c r="H1569" s="25" t="str"/>
+      <c r="H1569" t="inlineStr" s="25">
+        <is>
+          <t>Молитва</t>
+        </is>
+      </c>
       <c r="I1569" s="143" t="str"/>
     </row>
     <row r="1570" ht="21" customHeight="1">
@@ -40659,7 +40711,11 @@
       <c r="G1570" s="24" t="str">
         <v>慈愛</v>
       </c>
-      <c r="H1570" s="25" t="str"/>
+      <c r="H1570" t="inlineStr" s="25">
+        <is>
+          <t>Исцеление</t>
+        </is>
+      </c>
       <c r="I1570" s="143" t="str"/>
     </row>
     <row r="1571" ht="21" customHeight="1">
@@ -40684,7 +40740,11 @@
       <c r="G1571" s="24" t="str">
         <v>祝福</v>
       </c>
-      <c r="H1571" s="25" t="str"/>
+      <c r="H1571" t="inlineStr" s="25">
+        <is>
+          <t>Благословение</t>
+        </is>
+      </c>
       <c r="I1571" s="143" t="str"/>
     </row>
     <row r="1572" ht="21" customHeight="1">
@@ -40709,7 +40769,11 @@
       <c r="G1572" s="24" t="str">
         <v>退魔</v>
       </c>
-      <c r="H1572" s="25" t="str"/>
+      <c r="H1572" t="inlineStr" s="25">
+        <is>
+          <t>Экзорцизм</t>
+        </is>
+      </c>
       <c r="I1572" s="143" t="str"/>
     </row>
     <row r="1573" ht="21" customHeight="1">
@@ -40734,7 +40798,11 @@
       <c r="G1573" s="24" t="str">
         <v>聖歌</v>
       </c>
-      <c r="H1573" s="25" t="str"/>
+      <c r="H1573" t="inlineStr" s="25">
+        <is>
+          <t>Песнопения</t>
+        </is>
+      </c>
       <c r="I1573" s="143" t="str"/>
     </row>
     <row r="1574" ht="21" customHeight="1">
@@ -40759,7 +40827,11 @@
       <c r="G1574" s="24" t="str">
         <v>魔法</v>
       </c>
-      <c r="H1574" s="25" t="str"/>
+      <c r="H1574" t="inlineStr" s="25">
+        <is>
+          <t>Магия</t>
+        </is>
+      </c>
       <c r="I1574" s="143" t="str"/>
     </row>
     <row r="1575" ht="21" customHeight="1">
@@ -40784,7 +40856,11 @@
       <c r="G1575" s="24" t="str">
         <v>元素</v>
       </c>
-      <c r="H1575" s="25" t="str"/>
+      <c r="H1575" t="inlineStr" s="25">
+        <is>
+          <t>Магия стихий</t>
+        </is>
+      </c>
       <c r="I1575" s="143" t="str"/>
     </row>
     <row r="1576" ht="21" customHeight="1">
@@ -40809,7 +40885,11 @@
       <c r="G1576" s="24" t="str">
         <v>具現</v>
       </c>
-      <c r="H1576" s="25" t="str"/>
+      <c r="H1576" t="inlineStr" s="25">
+        <is>
+          <t>Воплощение</t>
+        </is>
+      </c>
       <c r="I1576" s="143" t="str"/>
     </row>
     <row r="1577" ht="21" customHeight="1">
@@ -40834,7 +40914,11 @@
       <c r="G1577" s="24" t="str">
         <v>暗黑</v>
       </c>
-      <c r="H1577" s="25" t="str"/>
+      <c r="H1577" t="inlineStr" s="25">
+        <is>
+          <t>Магия тьмы</t>
+        </is>
+      </c>
       <c r="I1577" s="143" t="str"/>
     </row>
     <row r="1578" ht="21" customHeight="1">
@@ -40859,7 +40943,11 @@
       <c r="G1578" s="24" t="str">
         <v>咒術</v>
       </c>
-      <c r="H1578" s="25" t="str"/>
+      <c r="H1578" t="inlineStr" s="25">
+        <is>
+          <t>Чары</t>
+        </is>
+      </c>
       <c r="I1578" s="143" t="str"/>
     </row>
     <row r="1579" ht="21" customHeight="1">
@@ -40884,7 +40972,11 @@
       <c r="G1579" s="24" t="str">
         <v>其他</v>
       </c>
-      <c r="H1579" s="25" t="str"/>
+      <c r="H1579" t="inlineStr" s="25">
+        <is>
+          <t>Особые</t>
+        </is>
+      </c>
       <c r="I1579" s="143" t="str"/>
     </row>
     <row r="1580" ht="21" customHeight="1">
@@ -40909,7 +41001,11 @@
       <c r="G1580" s="24" t="str">
         <v>種族</v>
       </c>
-      <c r="H1580" s="25" t="str"/>
+      <c r="H1580" t="inlineStr" s="25">
+        <is>
+          <t>Расовые</t>
+        </is>
+      </c>
       <c r="I1580" s="143" t="str"/>
     </row>
     <row r="1581" ht="21" customHeight="1">
@@ -40934,7 +41030,11 @@
       <c r="G1581" s="24" t="str">
         <v>騎乘</v>
       </c>
-      <c r="H1581" s="25" t="str"/>
+      <c r="H1581" t="inlineStr" s="25">
+        <is>
+          <t>Верховая езда</t>
+        </is>
+      </c>
       <c r="I1581" s="143" t="str"/>
     </row>
     <row r="1582" ht="21" customHeight="1">
@@ -52111,16 +52211,26 @@
       <c r="D2031" s="39" t="str">
         <v>Name.Text.Skill.Buff[5]</v>
       </c>
-      <c r="E2031" s="39" t="str">
-        <v>Enchantment (Magic attack)</v>
-      </c>
-      <c r="F2031" s="39" t="str">
-        <v>エンハンスエンチャント (魔法攻撃力)</v>
-      </c>
-      <c r="G2031" s="39" t="str">
-        <v>鋼力招來 (魔攻)</v>
-      </c>
-      <c r="H2031" s="40" t="str"/>
+      <c r="E2031" t="inlineStr" s="39">
+        <is>
+          <t>Enchant (MATK)</t>
+        </is>
+      </c>
+      <c r="F2031" t="inlineStr" s="39">
+        <is>
+          <t>エンハ (魔攻)</t>
+        </is>
+      </c>
+      <c r="G2031" t="inlineStr" s="39">
+        <is>
+          <t>鋼力招來 (魔攻)</t>
+        </is>
+      </c>
+      <c r="H2031" t="inlineStr" s="40">
+        <is>
+          <t>Усил МагАТК</t>
+        </is>
+      </c>
       <c r="I2031" s="143" t="str"/>
     </row>
     <row r="2032" ht="15" hidden="0" customHeight="1">
@@ -52136,16 +52246,26 @@
       <c r="D2032" s="39" t="str">
         <v>Name.Text.Skill.Buff[6]</v>
       </c>
-      <c r="E2032" s="39" t="str">
-        <v>Enchantment (Aura damage)</v>
-      </c>
-      <c r="F2032" s="39" t="str">
-        <v>エンハンスエンチャント (オーラダメージ)</v>
-      </c>
-      <c r="G2032" s="39" t="str">
-        <v>鋼力招來 (靈氣)</v>
-      </c>
-      <c r="H2032" s="40" t="str"/>
+      <c r="E2032" t="inlineStr" s="39">
+        <is>
+          <t>Enchant (Aura)</t>
+        </is>
+      </c>
+      <c r="F2032" t="inlineStr" s="39">
+        <is>
+          <t>エンハ (オーラ)</t>
+        </is>
+      </c>
+      <c r="G2032" t="inlineStr" s="39">
+        <is>
+          <t>鋼力招來 (靈氣)</t>
+        </is>
+      </c>
+      <c r="H2032" t="inlineStr" s="40">
+        <is>
+          <t>Усил Аура</t>
+        </is>
+      </c>
       <c r="I2032" s="143" t="str"/>
     </row>
     <row r="2033" ht="15" hidden="0" customHeight="1">
@@ -52161,16 +52281,26 @@
       <c r="D2033" s="39" t="str">
         <v>Name.Text.Skill.Buff[9]</v>
       </c>
-      <c r="E2033" s="39" t="str">
-        <v>Sage's Song (MATK)</v>
-      </c>
-      <c r="F2033" s="39" t="str">
-        <v>魔力の歌(魔攻)</v>
-      </c>
-      <c r="G2033" s="39" t="str">
-        <v>魔力之歌 (魔攻)</v>
-      </c>
-      <c r="H2033" s="40" t="str"/>
+      <c r="E2033" t="inlineStr" s="39">
+        <is>
+          <t>Sage's Son (MATK)</t>
+        </is>
+      </c>
+      <c r="F2033" t="inlineStr" s="39">
+        <is>
+          <t>魔力の歌(魔攻)</t>
+        </is>
+      </c>
+      <c r="G2033" t="inlineStr" s="39">
+        <is>
+          <t>魔力之歌 (魔攻)</t>
+        </is>
+      </c>
+      <c r="H2033" t="inlineStr" s="40">
+        <is>
+          <t>ПЕСН МагАТК</t>
+        </is>
+      </c>
       <c r="I2033" s="143" t="str"/>
     </row>
     <row r="2034" ht="15" hidden="0" customHeight="1">
@@ -52186,16 +52316,26 @@
       <c r="D2034" s="39" t="str">
         <v>Name.Text.Skill.Buff[10]</v>
       </c>
-      <c r="E2034" s="39" t="str">
-        <v>Sage's Song (Delay)</v>
-      </c>
-      <c r="F2034" s="39" t="str">
-        <v>魔力の歌(再使用)</v>
-      </c>
-      <c r="G2034" s="39" t="str">
-        <v>魔力之歌 (冷卻)</v>
-      </c>
-      <c r="H2034" s="40" t="str"/>
+      <c r="E2034" t="inlineStr" s="39">
+        <is>
+          <t>Sage's Son (Delay)</t>
+        </is>
+      </c>
+      <c r="F2034" t="inlineStr" s="39">
+        <is>
+          <t>魔力の歌(再使用)</t>
+        </is>
+      </c>
+      <c r="G2034" t="inlineStr" s="39">
+        <is>
+          <t>魔力之歌 (冷卻)</t>
+        </is>
+      </c>
+      <c r="H2034" t="inlineStr" s="40">
+        <is>
+          <t>ПЕСН Перезарядка</t>
+        </is>
+      </c>
       <c r="I2034" s="143" t="str"/>
     </row>
     <row r="2035" ht="15" hidden="0" customHeight="1">
@@ -52770,7 +52910,11 @@
       <c r="G2057" s="39" t="str">
         <v>HP</v>
       </c>
-      <c r="H2057" s="40" t="str"/>
+      <c r="H2057" t="inlineStr" s="40">
+        <is>
+          <t>ОЗ</t>
+        </is>
+      </c>
       <c r="I2057" s="143" t="str"/>
     </row>
     <row r="2058" ht="15" hidden="0" customHeight="1">
@@ -52795,7 +52939,11 @@
       <c r="G2058" s="39" t="str">
         <v>MP</v>
       </c>
-      <c r="H2058" s="40" t="str"/>
+      <c r="H2058" t="inlineStr" s="40">
+        <is>
+          <t>ОМ</t>
+        </is>
+      </c>
       <c r="I2058" s="143" t="str"/>
     </row>
     <row r="2059" ht="15" hidden="0" customHeight="1">
@@ -52820,7 +52968,11 @@
       <c r="G2059" s="39" t="str">
         <v>藥劑效果</v>
       </c>
-      <c r="H2059" s="40" t="str"/>
+      <c r="H2059" t="inlineStr" s="40">
+        <is>
+          <t>УВЕЛЗЕЛ</t>
+        </is>
+      </c>
       <c r="I2059" s="143" t="str"/>
     </row>
     <row r="2060" ht="15" hidden="0" customHeight="1">
@@ -52843,7 +52995,11 @@
         <v>ポーション回復量</v>
       </c>
       <c r="G2060" s="39" t="str"/>
-      <c r="H2060" s="40" t="str"/>
+      <c r="H2060" t="inlineStr" s="40">
+        <is>
+          <t>Восстанавливающее действие зелья</t>
+        </is>
+      </c>
       <c r="I2060" s="143" t="str"/>
     </row>
     <row r="2061" ht="15" hidden="0" customHeight="1">
@@ -52868,7 +53024,11 @@
       <c r="G2061" s="39" t="str">
         <v>HP技能</v>
       </c>
-      <c r="H2061" s="40" t="str"/>
+      <c r="H2061" t="inlineStr" s="40">
+        <is>
+          <t>% исцеления ОЗ</t>
+        </is>
+      </c>
       <c r="I2061" s="143" t="str"/>
     </row>
     <row r="2062" ht="15" hidden="0" customHeight="1">
@@ -52893,7 +53053,11 @@
       <c r="G2062" s="39" t="str">
         <v>HP恢復技能的效果</v>
       </c>
-      <c r="H2062" s="40" t="str"/>
+      <c r="H2062" t="inlineStr" s="40">
+        <is>
+          <t>% исцеленного ОЗ</t>
+        </is>
+      </c>
       <c r="I2062" s="143" t="str"/>
     </row>
     <row r="2063" ht="15" hidden="0" customHeight="1">
@@ -52918,7 +53082,11 @@
       <c r="G2063" s="39" t="str">
         <v>消耗MP</v>
       </c>
-      <c r="H2063" s="40" t="str"/>
+      <c r="H2063" t="inlineStr" s="40">
+        <is>
+          <t>Восст ОМ</t>
+        </is>
+      </c>
       <c r="I2063" s="143" t="str"/>
     </row>
     <row r="2064" ht="15" hidden="0" customHeight="1">
@@ -52939,7 +53107,11 @@
       </c>
       <c r="F2064" s="39" t="str"/>
       <c r="G2064" s="39" t="str"/>
-      <c r="H2064" s="40" t="str"/>
+      <c r="H2064" t="inlineStr" s="40">
+        <is>
+          <t>Восстановление ОМ</t>
+        </is>
+      </c>
       <c r="I2064" s="143" t="str"/>
     </row>
     <row r="2065" ht="15" hidden="0" customHeight="1">
@@ -52964,7 +53136,11 @@
       <c r="G2065" s="39" t="str">
         <v>攻/最大</v>
       </c>
-      <c r="H2065" s="40" t="str"/>
+      <c r="H2065" t="inlineStr" s="40">
+        <is>
+          <t>МаксАТК</t>
+        </is>
+      </c>
       <c r="I2065" s="143" t="str"/>
     </row>
     <row r="2066" ht="15" hidden="0" customHeight="1">
@@ -52989,7 +53165,11 @@
       <c r="G2066" s="39" t="str">
         <v>攻/前面</v>
       </c>
-      <c r="H2066" s="40" t="str"/>
+      <c r="H2066" t="inlineStr" s="40">
+        <is>
+          <t>Фронт+</t>
+        </is>
+      </c>
       <c r="I2066" s="143" t="str"/>
     </row>
     <row r="2067" ht="15" hidden="0" customHeight="1">
@@ -53014,7 +53194,11 @@
       <c r="G2067" s="39" t="str">
         <v>從正面進攻</v>
       </c>
-      <c r="H2067" s="40" t="str"/>
+      <c r="H2067" t="inlineStr" s="40">
+        <is>
+          <t>АТК / Фронтальная атака</t>
+        </is>
+      </c>
       <c r="I2067" s="143" t="str"/>
     </row>
     <row r="2068" ht="15" hidden="0" customHeight="1">
@@ -53039,7 +53223,11 @@
       <c r="G2068" s="39" t="str">
         <v>攻/後面</v>
       </c>
-      <c r="H2068" s="40" t="str"/>
+      <c r="H2068" t="inlineStr" s="40">
+        <is>
+          <t>Спин+</t>
+        </is>
+      </c>
       <c r="I2068" s="143" t="str"/>
     </row>
     <row r="2069" ht="15" hidden="0" customHeight="1">
@@ -53064,7 +53252,11 @@
       <c r="G2069" s="39" t="str">
         <v>從背後攻擊</v>
       </c>
-      <c r="H2069" s="40" t="str"/>
+      <c r="H2069" t="inlineStr" s="40">
+        <is>
+          <t>АТК / Атака в спину</t>
+        </is>
+      </c>
       <c r="I2069" s="143" t="str"/>
     </row>
     <row r="2070" ht="15" hidden="0" customHeight="1">
@@ -53089,7 +53281,11 @@
       <c r="G2070" s="39" t="str">
         <v>魔攻</v>
       </c>
-      <c r="H2070" s="40" t="str"/>
+      <c r="H2070" t="inlineStr" s="40">
+        <is>
+          <t>МагАТК</t>
+        </is>
+      </c>
       <c r="I2070" s="143" t="str"/>
     </row>
     <row r="2071" ht="15" hidden="0" customHeight="1">
@@ -53114,7 +53310,11 @@
       <c r="G2071" s="39" t="str">
         <v>魔法攻擊</v>
       </c>
-      <c r="H2071" s="40" t="str"/>
+      <c r="H2071" t="inlineStr" s="40">
+        <is>
+          <t>Магическая атака</t>
+        </is>
+      </c>
       <c r="I2071" s="143" t="str"/>
     </row>
     <row r="2072" ht="15" hidden="0" customHeight="1">
@@ -53139,7 +53339,11 @@
       <c r="G2072" s="39" t="str">
         <v>防禦</v>
       </c>
-      <c r="H2072" s="40" t="str"/>
+      <c r="H2072" t="inlineStr" s="40">
+        <is>
+          <t>ЗАЩИТА</t>
+        </is>
+      </c>
       <c r="I2072" s="143" t="str"/>
     </row>
     <row r="2073" ht="15" hidden="0" customHeight="1">
@@ -53164,7 +53368,11 @@
       <c r="G2073" s="39" t="str">
         <v>防/前面</v>
       </c>
-      <c r="H2073" s="40" t="str"/>
+      <c r="H2073" t="inlineStr" s="40">
+        <is>
+          <t>ФРОНТ Сопр</t>
+        </is>
+      </c>
       <c r="I2073" s="143" t="str"/>
     </row>
     <row r="2074" ht="15" hidden="0" customHeight="1">
@@ -53189,7 +53397,11 @@
       <c r="G2074" s="39" t="str">
         <v>從前面物理傷害</v>
       </c>
-      <c r="H2074" s="40" t="str"/>
+      <c r="H2074" t="inlineStr" s="40">
+        <is>
+          <t>Уменьшение получаемого урона от фронтальных атак</t>
+        </is>
+      </c>
       <c r="I2074" s="143" t="str"/>
     </row>
     <row r="2075" ht="15" hidden="0" customHeight="1">
@@ -53214,7 +53426,11 @@
       <c r="G2075" s="39" t="str">
         <v>防/後面</v>
       </c>
-      <c r="H2075" s="40" t="str"/>
+      <c r="H2075" t="inlineStr" s="40">
+        <is>
+          <t>СПИН Сопр</t>
+        </is>
+      </c>
       <c r="I2075" s="143" t="str"/>
     </row>
     <row r="2076" ht="15" hidden="0" customHeight="1">
@@ -53239,7 +53455,11 @@
       <c r="G2076" s="39" t="str">
         <v>從後面物理傷害</v>
       </c>
-      <c r="H2076" s="40" t="str"/>
+      <c r="H2076" t="inlineStr" s="40">
+        <is>
+          <t>Уменьшение получаемого урона от атак в спину</t>
+        </is>
+      </c>
       <c r="I2076" s="143" t="str"/>
     </row>
     <row r="2077" ht="15" hidden="0" customHeight="1">
@@ -53264,7 +53484,11 @@
       <c r="G2077" s="39" t="str">
         <v>物理傷害</v>
       </c>
-      <c r="H2077" s="40" t="str"/>
+      <c r="H2077" t="inlineStr" s="40">
+        <is>
+          <t>Физ СОПР</t>
+        </is>
+      </c>
       <c r="I2077" s="143" t="str"/>
     </row>
     <row r="2078" ht="15" hidden="0" customHeight="1">
@@ -53287,7 +53511,11 @@
         <v>被物理ダメージ</v>
       </c>
       <c r="G2078" s="39" t="str"/>
-      <c r="H2078" s="40" t="str"/>
+      <c r="H2078" t="inlineStr" s="40">
+        <is>
+          <t>Снижение получаемого физического урона</t>
+        </is>
+      </c>
       <c r="I2078" s="143" t="str"/>
     </row>
     <row r="2079" ht="15" hidden="0" customHeight="1">
@@ -53312,7 +53540,11 @@
       <c r="G2079" s="39" t="str">
         <v>物理傷害</v>
       </c>
-      <c r="H2079" s="40" t="str"/>
+      <c r="H2079" t="inlineStr" s="40">
+        <is>
+          <t>ФИЗ Сопр</t>
+        </is>
+      </c>
       <c r="I2079" s="143" t="str"/>
     </row>
     <row r="2080" ht="15" hidden="0" customHeight="1">
@@ -53335,7 +53567,11 @@
         <v>被物理ダメージ</v>
       </c>
       <c r="G2080" s="39" t="str"/>
-      <c r="H2080" s="40" t="str"/>
+      <c r="H2080" t="inlineStr" s="40">
+        <is>
+          <t>Уменьшение получаемого физического урона</t>
+        </is>
+      </c>
       <c r="I2080" s="143" t="str"/>
     </row>
     <row r="2081" ht="15" hidden="0" customHeight="1">
@@ -53360,7 +53596,11 @@
       <c r="G2081" s="39" t="str">
         <v>魔法傷害</v>
       </c>
-      <c r="H2081" s="40" t="str"/>
+      <c r="H2081" t="inlineStr" s="40">
+        <is>
+          <t>МАГ Сопр</t>
+        </is>
+      </c>
       <c r="I2081" s="143" t="str"/>
     </row>
     <row r="2082" ht="15" hidden="0" customHeight="1">
@@ -53383,7 +53623,11 @@
         <v>被魔法ダメージ</v>
       </c>
       <c r="G2082" s="39" t="str"/>
-      <c r="H2082" s="40" t="str"/>
+      <c r="H2082" t="inlineStr" s="40">
+        <is>
+          <t>Уменьшение получаемого магического урона</t>
+        </is>
+      </c>
       <c r="I2082" s="143" t="str"/>
     </row>
     <row r="2083" ht="15" hidden="0" customHeight="1">
@@ -53408,7 +53652,11 @@
       <c r="G2083" s="39" t="str">
         <v>命中</v>
       </c>
-      <c r="H2083" s="40" t="str"/>
+      <c r="H2083" t="inlineStr" s="40">
+        <is>
+          <t>Точность</t>
+        </is>
+      </c>
       <c r="I2083" s="143" t="str"/>
     </row>
     <row r="2084" ht="15" hidden="0" customHeight="1">
@@ -53433,7 +53681,11 @@
       <c r="G2084" s="39" t="str">
         <v>命/前面</v>
       </c>
-      <c r="H2084" s="40" t="str"/>
+      <c r="H2084" t="inlineStr" s="40">
+        <is>
+          <t>ТОЧН</t>
+        </is>
+      </c>
       <c r="I2084" s="143" t="str"/>
     </row>
     <row r="2085" ht="15" hidden="0" customHeight="1">
@@ -53458,7 +53710,11 @@
       <c r="G2085" s="39" t="str">
         <v>當從正面攻擊命中</v>
       </c>
-      <c r="H2085" s="40" t="str"/>
+      <c r="H2085" t="inlineStr" s="40">
+        <is>
+          <t>Точность</t>
+        </is>
+      </c>
       <c r="I2085" s="143" t="str"/>
     </row>
     <row r="2086" ht="15" hidden="0" customHeight="1">
@@ -53483,7 +53739,11 @@
       <c r="G2086" s="39" t="str">
         <v>暴擊率</v>
       </c>
-      <c r="H2086" s="40" t="str"/>
+      <c r="H2086" t="inlineStr" s="40">
+        <is>
+          <t>ШК</t>
+        </is>
+      </c>
       <c r="I2086" s="143" t="str"/>
     </row>
     <row r="2087" ht="15" hidden="0" customHeight="1">
@@ -53506,7 +53766,11 @@
         <v>クリティカル発生率</v>
       </c>
       <c r="G2087" s="39" t="str"/>
-      <c r="H2087" s="40" t="str"/>
+      <c r="H2087" t="inlineStr" s="40">
+        <is>
+          <t>Шанс критической атаки</t>
+        </is>
+      </c>
       <c r="I2087" s="143" t="str"/>
     </row>
     <row r="2088" ht="15" hidden="0" customHeight="1">
@@ -53531,7 +53795,11 @@
       <c r="G2088" s="39" t="str">
         <v>暴擊威力</v>
       </c>
-      <c r="H2088" s="40" t="str"/>
+      <c r="H2088" t="inlineStr" s="40">
+        <is>
+          <t>Крит УРОН</t>
+        </is>
+      </c>
       <c r="I2088" s="143" t="str"/>
     </row>
     <row r="2089" ht="15" hidden="0" customHeight="1">
@@ -53556,7 +53824,11 @@
       <c r="G2089" s="39" t="str">
         <v>暴擊威力</v>
       </c>
-      <c r="H2089" s="40" t="str"/>
+      <c r="H2089" t="inlineStr" s="40">
+        <is>
+          <t>Критический урон</t>
+        </is>
+      </c>
       <c r="I2089" s="143" t="str"/>
     </row>
     <row r="2090" ht="15" hidden="0" customHeight="1">
@@ -53581,7 +53853,11 @@
       <c r="G2090" s="39" t="str">
         <v>迴避</v>
       </c>
-      <c r="H2090" s="40" t="str"/>
+      <c r="H2090" t="inlineStr" s="40">
+        <is>
+          <t>Уклонение</t>
+        </is>
+      </c>
       <c r="I2090" s="143" t="str"/>
     </row>
     <row r="2091" ht="15" hidden="0" customHeight="1">
@@ -53606,7 +53882,11 @@
       <c r="G2091" s="39" t="str">
         <v>防/暴擊</v>
       </c>
-      <c r="H2091" s="40" t="str"/>
+      <c r="H2091" t="inlineStr" s="40">
+        <is>
+          <t>КРИТ Сопр</t>
+        </is>
+      </c>
       <c r="I2091" s="143" t="str"/>
     </row>
     <row r="2092" ht="15" hidden="0" customHeight="1">
@@ -53631,7 +53911,11 @@
       <c r="G2092" s="39" t="str">
         <v>防/暴擊率</v>
       </c>
-      <c r="H2092" s="40" t="str"/>
+      <c r="H2092" t="inlineStr" s="40">
+        <is>
+          <t>Шанс получить критический удар; 0 - стандарт</t>
+        </is>
+      </c>
       <c r="I2092" s="143" t="str"/>
     </row>
     <row r="2093" ht="15" hidden="0" customHeight="1">
@@ -53656,7 +53940,11 @@
       <c r="G2093" s="39" t="str">
         <v>防/暴威</v>
       </c>
-      <c r="H2093" s="40" t="str"/>
+      <c r="H2093" t="inlineStr" s="40">
+        <is>
+          <t>КУРОН СОПР</t>
+        </is>
+      </c>
       <c r="I2093" s="143" t="str"/>
     </row>
     <row r="2094" ht="15" hidden="0" customHeight="1">
@@ -53681,7 +53969,11 @@
       <c r="G2094" s="39" t="str">
         <v>防/暴擊威力</v>
       </c>
-      <c r="H2094" s="40" t="str"/>
+      <c r="H2094" t="inlineStr" s="40">
+        <is>
+          <t>Снижение получаемого критического урона</t>
+        </is>
+      </c>
       <c r="I2094" s="143" t="str"/>
     </row>
     <row r="2095" ht="15" hidden="0" customHeight="1">
@@ -53706,7 +53998,11 @@
       <c r="G2095" s="39" t="str">
         <v>迴/近戰</v>
       </c>
-      <c r="H2095" s="40" t="str"/>
+      <c r="H2095" t="inlineStr" s="40">
+        <is>
+          <t>Ближ УКЛОН</t>
+        </is>
+      </c>
       <c r="I2095" s="143" t="str"/>
     </row>
     <row r="2096" ht="15" hidden="0" customHeight="1">
@@ -53731,7 +54027,11 @@
       <c r="G2096" s="39" t="str">
         <v>近戰迴避</v>
       </c>
-      <c r="H2096" s="40" t="str"/>
+      <c r="H2096" t="inlineStr" s="40">
+        <is>
+          <t>Уклонение от атак ближнего боя</t>
+        </is>
+      </c>
       <c r="I2096" s="143" t="str"/>
     </row>
     <row r="2097" ht="15" hidden="0" customHeight="1">
@@ -53756,7 +54056,11 @@
       <c r="G2097" s="39" t="str">
         <v>迴/遠程</v>
       </c>
-      <c r="H2097" s="40" t="str"/>
+      <c r="H2097" t="inlineStr" s="40">
+        <is>
+          <t>Дальн АТК УКЛОН</t>
+        </is>
+      </c>
       <c r="I2097" s="143" t="str"/>
     </row>
     <row r="2098" ht="15" hidden="0" customHeight="1">
@@ -53781,7 +54085,11 @@
       <c r="G2098" s="39" t="str">
         <v>遠程迴避</v>
       </c>
-      <c r="H2098" s="40" t="str"/>
+      <c r="H2098" t="inlineStr" s="40">
+        <is>
+          <t>Шанс уклониться от атаки дальнего боя</t>
+        </is>
+      </c>
       <c r="I2098" s="143" t="str"/>
     </row>
     <row r="2099" ht="15" hidden="0" customHeight="1">
@@ -53806,7 +54114,11 @@
       <c r="G2099" s="39" t="str">
         <v>迴/魔法</v>
       </c>
-      <c r="H2099" s="40" t="str"/>
+      <c r="H2099" t="inlineStr" s="40">
+        <is>
+          <t>Маг УКЛОН</t>
+        </is>
+      </c>
       <c r="I2099" s="143" t="str"/>
     </row>
     <row r="2100" ht="15" hidden="0" customHeight="1">
@@ -53831,7 +54143,11 @@
       <c r="G2100" s="39" t="str">
         <v>魔法攻擊迴避</v>
       </c>
-      <c r="H2100" s="40" t="str"/>
+      <c r="H2100" t="inlineStr" s="40">
+        <is>
+          <t>Уклонение от магии</t>
+        </is>
+      </c>
       <c r="I2100" s="143" t="str"/>
     </row>
     <row r="2101" ht="15" hidden="0" customHeight="1">
@@ -53856,7 +54172,11 @@
       <c r="G2101" s="39" t="str">
         <v>範/近戰</v>
       </c>
-      <c r="H2101" s="40" t="str"/>
+      <c r="H2101" t="inlineStr" s="40">
+        <is>
+          <t>Дист ближ АТК</t>
+        </is>
+      </c>
       <c r="I2101" s="143" t="str"/>
     </row>
     <row r="2102" ht="15" hidden="0" customHeight="1">
@@ -53881,7 +54201,11 @@
       <c r="G2102" s="39" t="str">
         <v>近戰武器範圍</v>
       </c>
-      <c r="H2102" s="40" t="str"/>
+      <c r="H2102" t="inlineStr" s="40">
+        <is>
+          <t>Дальность атак ближнего боя</t>
+        </is>
+      </c>
       <c r="I2102" s="143" t="str"/>
     </row>
     <row r="2103" ht="15" hidden="0" customHeight="1">
@@ -53906,7 +54230,11 @@
       <c r="G2103" s="39" t="str">
         <v>範/遠程</v>
       </c>
-      <c r="H2103" s="40" t="str"/>
+      <c r="H2103" t="inlineStr" s="40">
+        <is>
+          <t>Дист дальн АТК</t>
+        </is>
+      </c>
       <c r="I2103" s="143" t="str"/>
     </row>
     <row r="2104" ht="15" hidden="0" customHeight="1">
@@ -53931,7 +54259,11 @@
       <c r="G2104" s="39" t="str">
         <v>遠程武器射程</v>
       </c>
-      <c r="H2104" s="40" t="str"/>
+      <c r="H2104" t="inlineStr" s="40">
+        <is>
+          <t>Дальность атак дальнего боя</t>
+        </is>
+      </c>
       <c r="I2104" s="143" t="str"/>
     </row>
     <row r="2105" ht="15" hidden="0" customHeight="1">
@@ -53956,7 +54288,11 @@
       <c r="G2105" s="39" t="str">
         <v>火抗性</v>
       </c>
-      <c r="H2105" s="40" t="str"/>
+      <c r="H2105" t="inlineStr" s="40">
+        <is>
+          <t>ОГН Сопр</t>
+        </is>
+      </c>
       <c r="I2105" s="143" t="str"/>
     </row>
     <row r="2106" ht="15" hidden="0" customHeight="1">
@@ -53977,7 +54313,11 @@
       </c>
       <c r="F2106" s="39" t="str"/>
       <c r="G2106" s="39" t="str"/>
-      <c r="H2106" s="40" t="str"/>
+      <c r="H2106" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость огню</t>
+        </is>
+      </c>
       <c r="I2106" s="143" t="str"/>
     </row>
     <row r="2107" ht="15" hidden="0" customHeight="1">
@@ -54002,7 +54342,11 @@
       <c r="G2107" s="39" t="str">
         <v>攻擊速度</v>
       </c>
-      <c r="H2107" s="40" t="str"/>
+      <c r="H2107" t="inlineStr" s="40">
+        <is>
+          <t>СКР АТК</t>
+        </is>
+      </c>
       <c r="I2107" s="143" t="str"/>
     </row>
     <row r="2108" ht="15" hidden="0" customHeight="1">
@@ -54023,7 +54367,11 @@
       </c>
       <c r="F2108" s="39" t="str"/>
       <c r="G2108" s="39" t="str"/>
-      <c r="H2108" s="40" t="str"/>
+      <c r="H2108" t="inlineStr" s="40">
+        <is>
+          <t>Скорость атаки</t>
+        </is>
+      </c>
       <c r="I2108" s="143" t="str"/>
     </row>
     <row r="2109" ht="15" hidden="0" customHeight="1">
@@ -54048,7 +54396,11 @@
       <c r="G2109" s="39" t="str">
         <v>冰抗性</v>
       </c>
-      <c r="H2109" s="40" t="str"/>
+      <c r="H2109" t="inlineStr" s="40">
+        <is>
+          <t>ЛЕД Сопр</t>
+        </is>
+      </c>
       <c r="I2109" s="143" t="str"/>
     </row>
     <row r="2110" ht="15" hidden="0" customHeight="1">
@@ -54069,7 +54421,11 @@
       </c>
       <c r="F2110" s="39" t="str"/>
       <c r="G2110" s="39" t="str"/>
-      <c r="H2110" s="40" t="str"/>
+      <c r="H2110" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость магии льда</t>
+        </is>
+      </c>
       <c r="I2110" s="143" t="str"/>
     </row>
     <row r="2111" ht="15" hidden="0" customHeight="1">
@@ -54094,7 +54450,11 @@
       <c r="G2111" s="39" t="str">
         <v>詠唱速度</v>
       </c>
-      <c r="H2111" s="40" t="str"/>
+      <c r="H2111" t="inlineStr" s="40">
+        <is>
+          <t>СКР Каста</t>
+        </is>
+      </c>
       <c r="I2111" s="143" t="str"/>
     </row>
     <row r="2112" ht="15" hidden="0" customHeight="1">
@@ -54115,7 +54475,11 @@
       </c>
       <c r="F2112" s="39" t="str"/>
       <c r="G2112" s="39" t="str"/>
-      <c r="H2112" s="40" t="str"/>
+      <c r="H2112" t="inlineStr" s="40">
+        <is>
+          <t>Скорость применения умений</t>
+        </is>
+      </c>
       <c r="I2112" s="143" t="str"/>
     </row>
     <row r="2113" ht="15" hidden="0" customHeight="1">
@@ -54140,7 +54504,11 @@
       <c r="G2113" s="39" t="str">
         <v>詠唱時間</v>
       </c>
-      <c r="H2113" s="40" t="str"/>
+      <c r="H2113" t="inlineStr" s="40">
+        <is>
+          <t>ВремяКаст</t>
+        </is>
+      </c>
       <c r="I2113" s="143" t="str"/>
     </row>
     <row r="2114" ht="15" hidden="0" customHeight="1">
@@ -54161,7 +54529,11 @@
       </c>
       <c r="F2114" s="39" t="str"/>
       <c r="G2114" s="39" t="str"/>
-      <c r="H2114" s="40" t="str"/>
+      <c r="H2114" t="inlineStr" s="40">
+        <is>
+          <t>Уменьшение времени применения умений</t>
+        </is>
+      </c>
       <c r="I2114" s="143" t="str"/>
     </row>
     <row r="2115" ht="15" hidden="0" customHeight="1">
@@ -54186,7 +54558,11 @@
       <c r="G2115" s="39" t="str">
         <v>雷抗性</v>
       </c>
-      <c r="H2115" s="40" t="str"/>
+      <c r="H2115" t="inlineStr" s="40">
+        <is>
+          <t>МОЛН Сопр</t>
+        </is>
+      </c>
       <c r="I2115" s="143" t="str"/>
     </row>
     <row r="2116" ht="15" hidden="0" customHeight="1">
@@ -54207,7 +54583,11 @@
       </c>
       <c r="F2116" s="39" t="str"/>
       <c r="G2116" s="39" t="str"/>
-      <c r="H2116" s="40" t="str"/>
+      <c r="H2116" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость магии молнии</t>
+        </is>
+      </c>
       <c r="I2116" s="143" t="str"/>
     </row>
     <row r="2117" ht="15" hidden="0" customHeight="1">
@@ -54232,7 +54612,11 @@
       <c r="G2117" s="39" t="str">
         <v>冷卻時間</v>
       </c>
-      <c r="H2117" s="40" t="str"/>
+      <c r="H2117" t="inlineStr" s="40">
+        <is>
+          <t>Перезарядка</t>
+        </is>
+      </c>
       <c r="I2117" s="143" t="str"/>
     </row>
     <row r="2118" ht="15" hidden="0" customHeight="1">
@@ -54257,7 +54641,11 @@
       <c r="G2118" s="39" t="str">
         <v>毒抗性</v>
       </c>
-      <c r="H2118" s="40" t="str"/>
+      <c r="H2118" t="inlineStr" s="40">
+        <is>
+          <t>ЯД Сопр</t>
+        </is>
+      </c>
       <c r="I2118" s="143" t="str"/>
     </row>
     <row r="2119" ht="15" hidden="0" customHeight="1">
@@ -54278,7 +54666,11 @@
       </c>
       <c r="F2119" s="39" t="str"/>
       <c r="G2119" s="39" t="str"/>
-      <c r="H2119" s="40" t="str"/>
+      <c r="H2119" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость магии яда</t>
+        </is>
+      </c>
       <c r="I2119" s="143" t="str"/>
     </row>
     <row r="2120" ht="15" hidden="0" customHeight="1">
@@ -54303,7 +54695,11 @@
       <c r="G2120" s="39" t="str">
         <v>行走速度</v>
       </c>
-      <c r="H2120" s="40" t="str"/>
+      <c r="H2120" t="inlineStr" s="40">
+        <is>
+          <t>СКР Движ</t>
+        </is>
+      </c>
       <c r="I2120" s="143" t="str"/>
     </row>
     <row r="2121" ht="15" hidden="0" customHeight="1">
@@ -54324,7 +54720,11 @@
       </c>
       <c r="F2121" s="39" t="str"/>
       <c r="G2121" s="39" t="str"/>
-      <c r="H2121" s="40" t="str"/>
+      <c r="H2121" t="inlineStr" s="40">
+        <is>
+          <t>Скорость передвижения</t>
+        </is>
+      </c>
       <c r="I2121" s="143" t="str"/>
     </row>
     <row r="2122" ht="15" hidden="0" customHeight="1">
@@ -54349,7 +54749,11 @@
       <c r="G2122" s="39" t="str">
         <v>市/行走</v>
       </c>
-      <c r="H2122" s="40" t="str"/>
+      <c r="H2122" t="inlineStr" s="40">
+        <is>
+          <t>ГородСКРП</t>
+        </is>
+      </c>
       <c r="I2122" s="143" t="str"/>
     </row>
     <row r="2123" ht="15" hidden="0" customHeight="1">
@@ -54374,7 +54778,11 @@
       <c r="G2123" s="39" t="str">
         <v>速度變化的城市</v>
       </c>
-      <c r="H2123" s="40" t="str"/>
+      <c r="H2123" t="inlineStr" s="40">
+        <is>
+          <t>Скорость передвижения по городу</t>
+        </is>
+      </c>
       <c r="I2123" s="143" t="str"/>
     </row>
     <row r="2124" ht="15" hidden="0" customHeight="1">
@@ -54399,7 +54807,11 @@
       <c r="G2124" s="39" t="str">
         <v>魅惑抗性</v>
       </c>
-      <c r="H2124" s="40" t="str"/>
+      <c r="H2124" t="inlineStr" s="40">
+        <is>
+          <t>ЧАР Сопр</t>
+        </is>
+      </c>
       <c r="I2124" s="143" t="str"/>
     </row>
     <row r="2125" ht="15" hidden="0" customHeight="1">
@@ -54420,7 +54832,11 @@
       </c>
       <c r="F2125" s="39" t="str"/>
       <c r="G2125" s="39" t="str"/>
-      <c r="H2125" s="40" t="str"/>
+      <c r="H2125" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость магии чар</t>
+        </is>
+      </c>
       <c r="I2125" s="143" t="str"/>
     </row>
     <row r="2126" ht="15" hidden="0" customHeight="1">
@@ -54445,7 +54861,11 @@
       <c r="G2126" s="39" t="str">
         <v>光抗性</v>
       </c>
-      <c r="H2126" s="40" t="str"/>
+      <c r="H2126" t="inlineStr" s="40">
+        <is>
+          <t>СВЕТ Сопр</t>
+        </is>
+      </c>
       <c r="I2126" s="143" t="str"/>
     </row>
     <row r="2127" ht="15" hidden="0" customHeight="1">
@@ -54466,7 +54886,11 @@
       </c>
       <c r="F2127" s="39" t="str"/>
       <c r="G2127" s="39" t="str"/>
-      <c r="H2127" s="40" t="str"/>
+      <c r="H2127" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость магии света</t>
+        </is>
+      </c>
       <c r="I2127" s="143" t="str"/>
     </row>
     <row r="2128" ht="15" hidden="0" customHeight="1">
@@ -54491,7 +54915,11 @@
       <c r="G2128" s="39" t="str">
         <v>黑暗抗性</v>
       </c>
-      <c r="H2128" s="40" t="str"/>
+      <c r="H2128" t="inlineStr" s="40">
+        <is>
+          <t>ТЬМ Сопр</t>
+        </is>
+      </c>
       <c r="I2128" s="143" t="str"/>
     </row>
     <row r="2129" ht="15" hidden="0" customHeight="1">
@@ -54512,7 +54940,11 @@
       </c>
       <c r="F2129" s="39" t="str"/>
       <c r="G2129" s="39" t="str"/>
-      <c r="H2129" s="40" t="str"/>
+      <c r="H2129" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость тьме</t>
+        </is>
+      </c>
       <c r="I2129" s="143" t="str"/>
     </row>
     <row r="2130" ht="15" hidden="0" customHeight="1">
@@ -54537,7 +54969,11 @@
       <c r="G2130" s="39" t="str">
         <v>體抗性</v>
       </c>
-      <c r="H2130" s="40" t="str"/>
+      <c r="H2130" t="inlineStr" s="40">
+        <is>
+          <t>АНМСОСТТЕЛ Сопр</t>
+        </is>
+      </c>
       <c r="I2130" s="143" t="str"/>
     </row>
     <row r="2131" ht="24" hidden="0" customHeight="1">
@@ -54562,7 +54998,11 @@
       <c r="G2131" s="39" t="str">
         <v>異常體抗性</v>
       </c>
-      <c r="H2131" s="40" t="str"/>
+      <c r="H2131" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость аномальных состояний тела</t>
+        </is>
+      </c>
       <c r="I2131" s="143" t="str"/>
     </row>
     <row r="2132" ht="15" hidden="0" customHeight="1">
@@ -54587,7 +55027,11 @@
       <c r="G2132" s="39" t="str">
         <v>精神抗性</v>
       </c>
-      <c r="H2132" s="40" t="str"/>
+      <c r="H2132" t="inlineStr" s="40">
+        <is>
+          <t>АНМСОСТДУХ Сопр</t>
+        </is>
+      </c>
       <c r="I2132" s="143" t="str"/>
     </row>
     <row r="2133" ht="24" hidden="0" customHeight="1">
@@ -54612,7 +55056,11 @@
       <c r="G2133" s="39" t="str">
         <v>精神錯亂抗性</v>
       </c>
-      <c r="H2133" s="40" t="str"/>
+      <c r="H2133" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость аномальных состояний духа</t>
+        </is>
+      </c>
       <c r="I2133" s="143" t="str"/>
     </row>
     <row r="2134" ht="15" hidden="0" customHeight="1">
@@ -54637,7 +55085,11 @@
       <c r="G2134" s="39" t="str">
         <v>秘法抗性</v>
       </c>
-      <c r="H2134" s="40" t="str"/>
+      <c r="H2134" t="inlineStr" s="40">
+        <is>
+          <t>МАГ Сопр</t>
+        </is>
+      </c>
       <c r="I2134" s="143" t="str"/>
     </row>
     <row r="2135" ht="15" hidden="0" customHeight="1">
@@ -54658,7 +55110,11 @@
       </c>
       <c r="F2135" s="39" t="str"/>
       <c r="G2135" s="39" t="str"/>
-      <c r="H2135" s="40" t="str"/>
+      <c r="H2135" t="inlineStr" s="40">
+        <is>
+          <t>Сопротивляемость магии</t>
+        </is>
+      </c>
       <c r="I2135" s="143" t="str"/>
     </row>
     <row r="2136" ht="15" hidden="0" customHeight="1">
@@ -55108,7 +55564,11 @@
       <c r="G2153" s="39" t="str">
         <v>體力</v>
       </c>
-      <c r="H2153" s="40" t="str"/>
+      <c r="H2153" t="inlineStr" s="40">
+        <is>
+          <t>ВЫН</t>
+        </is>
+      </c>
       <c r="I2153" s="143" t="str"/>
     </row>
     <row r="2154" ht="15" hidden="0" customHeight="1">
@@ -55133,7 +55593,11 @@
       <c r="G2154" s="39" t="str">
         <v>力量</v>
       </c>
-      <c r="H2154" s="40" t="str"/>
+      <c r="H2154" t="inlineStr" s="40">
+        <is>
+          <t>СИЛ</t>
+        </is>
+      </c>
       <c r="I2154" s="143" t="str"/>
     </row>
     <row r="2155" ht="15" hidden="0" customHeight="1">
@@ -55158,7 +55622,11 @@
       <c r="G2155" s="39" t="str">
         <v>敏捷</v>
       </c>
-      <c r="H2155" s="40" t="str"/>
+      <c r="H2155" t="inlineStr" s="40">
+        <is>
+          <t>ПРВ</t>
+        </is>
+      </c>
       <c r="I2155" s="143" t="str"/>
     </row>
     <row r="2156" ht="15" hidden="0" customHeight="1">
@@ -55183,7 +55651,11 @@
       <c r="G2156" s="39" t="str">
         <v>技巧</v>
       </c>
-      <c r="H2156" s="40" t="str"/>
+      <c r="H2156" t="inlineStr" s="40">
+        <is>
+          <t>ЛВК</t>
+        </is>
+      </c>
       <c r="I2156" s="143" t="str"/>
     </row>
     <row r="2157" ht="15" hidden="0" customHeight="1">
@@ -55208,7 +55680,11 @@
       <c r="G2157" s="39" t="str">
         <v>靈感</v>
       </c>
-      <c r="H2157" s="40" t="str"/>
+      <c r="H2157" t="inlineStr" s="40">
+        <is>
+          <t>СД</t>
+        </is>
+      </c>
       <c r="I2157" s="143" t="str"/>
     </row>
     <row r="2158" ht="15" hidden="0" customHeight="1">
@@ -55233,7 +55709,11 @@
       <c r="G2158" s="39" t="str">
         <v>智慧</v>
       </c>
-      <c r="H2158" s="40" t="str"/>
+      <c r="H2158" t="inlineStr" s="40">
+        <is>
+          <t>ИНТ</t>
+        </is>
+      </c>
       <c r="I2158" s="143" t="str"/>
     </row>
     <row r="2159" ht="15" hidden="0" customHeight="1">
@@ -75185,6 +75665,194 @@
         </is>
       </c>
       <c r="I2904" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="2905" ht="15" hidden="0" customHeight="1">
+      <c r="A2905" t="inlineStr" s="38">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
+      <c r="B2905" t="inlineStr" s="38">
+        <is>
+          <t>calculator.qualified_buff.5.hint</t>
+        </is>
+      </c>
+      <c r="C2905" t="inlineStr" s="38">
+        <is>
+          <t>Подсказка калькулятора</t>
+        </is>
+      </c>
+      <c r="D2905" t="inlineStr" s="39">
+        <is>
+          <t>Name.Text.Skill.Buff[5] @title</t>
+        </is>
+      </c>
+      <c r="E2905" t="inlineStr" s="39">
+        <is>
+          <t>Enchantment (Magic attack)</t>
+        </is>
+      </c>
+      <c r="F2905" t="inlineStr" s="39">
+        <is>
+          <t>エンハンスエンチャント (魔法攻撃力)</t>
+        </is>
+      </c>
+      <c r="G2905" t="inlineStr" s="39">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H2905" t="inlineStr" s="40">
+        <is>
+          <t>Усиление урона магией</t>
+        </is>
+      </c>
+      <c r="I2905" t="inlineStr" s="143">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="2906" ht="15" hidden="0" customHeight="1">
+      <c r="A2906" t="inlineStr" s="38">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
+      <c r="B2906" t="inlineStr" s="38">
+        <is>
+          <t>calculator.qualified_buff.6.hint</t>
+        </is>
+      </c>
+      <c r="C2906" t="inlineStr" s="38">
+        <is>
+          <t>Подсказка калькулятора</t>
+        </is>
+      </c>
+      <c r="D2906" t="inlineStr" s="39">
+        <is>
+          <t>Name.Text.Skill.Buff[6] @title</t>
+        </is>
+      </c>
+      <c r="E2906" t="inlineStr" s="39">
+        <is>
+          <t>Enchantment (Aura damage)</t>
+        </is>
+      </c>
+      <c r="F2906" t="inlineStr" s="39">
+        <is>
+          <t>エンハンスエンチャント (オーラダメージ)</t>
+        </is>
+      </c>
+      <c r="G2906" t="inlineStr" s="39">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H2906" t="inlineStr" s="40">
+        <is>
+          <t>Усиление урона аурой</t>
+        </is>
+      </c>
+      <c r="I2906" t="inlineStr" s="143">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="2907" ht="15" hidden="0" customHeight="1">
+      <c r="A2907" t="inlineStr" s="38">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
+      <c r="B2907" t="inlineStr" s="38">
+        <is>
+          <t>calculator.qualified_buff.9.hint</t>
+        </is>
+      </c>
+      <c r="C2907" t="inlineStr" s="38">
+        <is>
+          <t>Подсказка калькулятора</t>
+        </is>
+      </c>
+      <c r="D2907" t="inlineStr" s="39">
+        <is>
+          <t>Name.Text.Skill.Buff[9] @title</t>
+        </is>
+      </c>
+      <c r="E2907" t="inlineStr" s="39">
+        <is>
+          <t>Sage's Song (MATK)</t>
+        </is>
+      </c>
+      <c r="F2907" t="inlineStr" s="39">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2907" t="inlineStr" s="39">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H2907" t="inlineStr" s="40">
+        <is>
+          <t>Усиление урона магией</t>
+        </is>
+      </c>
+      <c r="I2907" t="inlineStr" s="143">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="2908" ht="15" hidden="0" customHeight="1">
+      <c r="A2908" t="inlineStr" s="38">
+        <is>
+          <t>Игра</t>
+        </is>
+      </c>
+      <c r="B2908" t="inlineStr" s="38">
+        <is>
+          <t>calculator.qualified_buff.10.hint</t>
+        </is>
+      </c>
+      <c r="C2908" t="inlineStr" s="38">
+        <is>
+          <t>Подсказка калькулятора</t>
+        </is>
+      </c>
+      <c r="D2908" t="inlineStr" s="39">
+        <is>
+          <t>Name.Text.Skill.Buff[10] @title</t>
+        </is>
+      </c>
+      <c r="E2908" t="inlineStr" s="39">
+        <is>
+          <t>Sage's Song (Delay)</t>
+        </is>
+      </c>
+      <c r="F2908" t="inlineStr" s="39">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2908" t="inlineStr" s="39">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H2908" t="inlineStr" s="40">
+        <is>
+          <t>Ускорение перезарядки умений</t>
+        </is>
+      </c>
+      <c r="I2908" t="inlineStr" s="143">
         <is>
           <t/>
         </is>
